--- a/data/bist_screener_2026-05-01.xlsx
+++ b/data/bist_screener_2026-05-01.xlsx
@@ -582,7 +582,11 @@
       <c r="J2" s="4" t="n">
         <v>-0.8592</v>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ</t>
@@ -623,7 +627,11 @@
       <c r="J3" s="8" t="n">
         <v>-0.4697</v>
       </c>
-      <c r="K3" s="6" t="inlineStr"/>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA, BIST DENİZLİ</t>
@@ -662,7 +670,11 @@
       <c r="J4" s="4" t="n">
         <v>-2.871</v>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -701,7 +713,11 @@
       <c r="J5" s="8" t="n">
         <v>-3.2783</v>
       </c>
-      <c r="K5" s="6" t="inlineStr"/>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST BURSA</t>
@@ -740,7 +756,11 @@
       <c r="J6" s="4" t="n">
         <v>-2.3084</v>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ</t>
@@ -779,7 +799,11 @@
         <v>0.1498</v>
       </c>
       <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
@@ -820,7 +844,11 @@
       <c r="J8" s="4" t="n">
         <v>-13.0614</v>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -859,7 +887,11 @@
         <v>0.0694</v>
       </c>
       <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
@@ -898,7 +930,11 @@
       <c r="J10" s="4" t="n">
         <v>-16.8098</v>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST YILDIZ</t>
@@ -935,7 +971,11 @@
         <v>-0.0291</v>
       </c>
       <c r="J11" s="6" t="inlineStr"/>
-      <c r="K11" s="6" t="inlineStr"/>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ</t>
@@ -974,7 +1014,11 @@
       <c r="J12" s="4" t="n">
         <v>-11.3175</v>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST MANİSA</t>
@@ -1015,7 +1059,11 @@
       <c r="J13" s="8" t="n">
         <v>0.1614</v>
       </c>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST TEMETTU</t>
@@ -1056,7 +1104,11 @@
       <c r="J14" s="4" t="n">
         <v>3376.9454</v>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
     </row>
@@ -1093,7 +1145,11 @@
       <c r="J15" s="8" t="n">
         <v>2.9159</v>
       </c>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK</t>
@@ -1132,7 +1188,11 @@
         <v>0.0132</v>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
@@ -1171,7 +1231,11 @@
       <c r="J17" s="8" t="n">
         <v>-1.4176</v>
       </c>
-      <c r="K17" s="6" t="inlineStr"/>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST MANİSA</t>
@@ -1210,7 +1274,11 @@
       <c r="J18" s="4" t="n">
         <v>-1.0115</v>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Sağlık teknolojisi</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST YILDIZ, BIST KURUMSAL YÖNETİM, BIST KAYSERİ</t>
@@ -1249,7 +1317,11 @@
       <c r="J19" s="8" t="n">
         <v>-0.2039</v>
       </c>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST İZMİR</t>
@@ -1288,7 +1360,11 @@
       <c r="J20" s="4" t="n">
         <v>0.6854</v>
       </c>
-      <c r="K20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST ANA, BIST ANTALYA</t>
@@ -1325,7 +1401,11 @@
       <c r="J21" s="8" t="n">
         <v>-13.2026</v>
       </c>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L21" s="6" t="inlineStr"/>
       <c r="M21" s="6" t="inlineStr"/>
     </row>
@@ -1360,7 +1440,11 @@
       <c r="J22" s="4" t="n">
         <v>0.07440000000000001</v>
       </c>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
@@ -1399,7 +1483,11 @@
       <c r="J23" s="8" t="n">
         <v>-0.87</v>
       </c>
-      <c r="K23" s="6" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST KURUMSAL YÖNETİM, BIST İZMİR</t>
@@ -1440,7 +1528,11 @@
       <c r="J24" s="4" t="n">
         <v>9.1807</v>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
@@ -1479,7 +1571,11 @@
         <v>0.1073</v>
       </c>
       <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
@@ -1520,7 +1616,11 @@
       <c r="J26" s="4" t="n">
         <v>-1.7377</v>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST KURUMSAL YÖNETİM, BIST İZMİR</t>
@@ -1559,7 +1659,11 @@
       <c r="J27" s="8" t="n">
         <v>-0.08259999999999999</v>
       </c>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK</t>
@@ -1600,7 +1704,11 @@
       <c r="J28" s="4" t="n">
         <v>13.5523</v>
       </c>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
@@ -1637,7 +1745,11 @@
         <v>-0.0512</v>
       </c>
       <c r="J29" s="6" t="inlineStr"/>
-      <c r="K29" s="6" t="inlineStr"/>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L29" s="6" t="inlineStr"/>
       <c r="M29" s="6" t="inlineStr"/>
     </row>
@@ -1674,7 +1786,11 @@
       <c r="J30" s="4" t="n">
         <v>6.4634</v>
       </c>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST İSTANBUL, BIST KATILIM TÜM, BIST KURUMSAL YÖNETİM</t>
@@ -1713,7 +1829,11 @@
       <c r="J31" s="8" t="n">
         <v>-5.725</v>
       </c>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
@@ -1754,7 +1874,11 @@
       <c r="J32" s="4" t="n">
         <v>28.4263</v>
       </c>
-      <c r="K32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ, BIST KURUMSAL YÖNETİM</t>
@@ -1793,7 +1917,11 @@
         <v>0.0426</v>
       </c>
       <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ</t>
@@ -1832,7 +1960,11 @@
       <c r="J34" s="4" t="n">
         <v>-3.2954</v>
       </c>
-      <c r="K34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST YILDIZ, BIST KONYA</t>
@@ -1873,7 +2005,11 @@
       <c r="J35" s="8" t="n">
         <v>27.4143</v>
       </c>
-      <c r="K35" s="6" t="inlineStr"/>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr"/>
     </row>
@@ -1908,7 +2044,11 @@
         <v>0.0118</v>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA, BIST KONYA</t>
@@ -1947,7 +2087,11 @@
       <c r="J37" s="8" t="n">
         <v>0.8924</v>
       </c>
-      <c r="K37" s="6" t="inlineStr"/>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ</t>
@@ -1988,7 +2132,11 @@
       <c r="J38" s="4" t="n">
         <v>-3.7063</v>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
     </row>
@@ -2025,7 +2173,11 @@
       <c r="J39" s="8" t="n">
         <v>-0.7025</v>
       </c>
-      <c r="K39" s="6" t="inlineStr"/>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -2064,7 +2216,11 @@
       <c r="J40" s="4" t="n">
         <v>-4.5264</v>
       </c>
-      <c r="K40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
@@ -2105,7 +2261,11 @@
       <c r="J41" s="8" t="n">
         <v>-0.6793</v>
       </c>
-      <c r="K41" s="6" t="inlineStr"/>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU</t>
@@ -2146,7 +2306,11 @@
       <c r="J42" s="4" t="n">
         <v>4.7406</v>
       </c>
-      <c r="K42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
@@ -2187,7 +2351,11 @@
       <c r="J43" s="8" t="n">
         <v>-0.5678</v>
       </c>
-      <c r="K43" s="6" t="inlineStr"/>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KURUMSAL YÖNETİM, BIST ANKARA</t>
@@ -2228,7 +2396,11 @@
       <c r="J44" s="4" t="n">
         <v>-0.3373</v>
       </c>
-      <c r="K44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST ULASTIRMA, BIST TÜM, BIST 50, BIST HİZMETLER, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST BANKA DISI LIKIT 10, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
@@ -2267,7 +2439,11 @@
       <c r="J45" s="8" t="n">
         <v>0.4484</v>
       </c>
-      <c r="K45" s="6" t="inlineStr"/>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST ANKARA</t>
@@ -2306,7 +2482,11 @@
       <c r="J46" s="4" t="n">
         <v>2.0381</v>
       </c>
-      <c r="K46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA</t>
@@ -2347,7 +2527,11 @@
       <c r="J47" s="8" t="n">
         <v>5.243200000000001</v>
       </c>
-      <c r="K47" s="6" t="inlineStr"/>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST ANKARA</t>
@@ -2386,7 +2570,11 @@
       <c r="J48" s="4" t="n">
         <v>-0.0625</v>
       </c>
-      <c r="K48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -2425,7 +2613,11 @@
       <c r="J49" s="8" t="n">
         <v>-0.4838</v>
       </c>
-      <c r="K49" s="6" t="inlineStr"/>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L49" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST İSTANBUL, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -2466,7 +2658,11 @@
       <c r="J50" s="4" t="n">
         <v>3.5434</v>
       </c>
-      <c r="K50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
@@ -2507,7 +2703,11 @@
       <c r="J51" s="8" t="n">
         <v>-0.9752</v>
       </c>
-      <c r="K51" s="6" t="inlineStr"/>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
@@ -2546,7 +2746,11 @@
       <c r="J52" s="4" t="n">
         <v>-63.5742</v>
       </c>
-      <c r="K52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Sağlık teknolojisi</t>
+        </is>
+      </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST YILDIZ, BIST TEKİRDAĞ</t>
@@ -2585,7 +2789,11 @@
       <c r="J53" s="8" t="n">
         <v>-1.5579</v>
       </c>
-      <c r="K53" s="6" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM, BIST ANA, BIST MANİSA</t>
@@ -2624,7 +2832,11 @@
       <c r="J54" s="4" t="n">
         <v>-356.4349</v>
       </c>
-      <c r="K54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
@@ -2665,7 +2877,11 @@
       <c r="J55" s="8" t="n">
         <v>-1.6389</v>
       </c>
-      <c r="K55" s="6" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST KAYSERİ</t>
@@ -2704,7 +2920,11 @@
       <c r="J56" s="4" t="n">
         <v>-0.0625</v>
       </c>
-      <c r="K56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST 50, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25</t>
@@ -2741,7 +2961,11 @@
         <v>-0.06150000000000001</v>
       </c>
       <c r="J57" s="6" t="inlineStr"/>
-      <c r="K57" s="6" t="inlineStr"/>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L57" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KURUMSAL YÖNETİM, BIST KATILIM 30, BIST 50-30, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -2780,7 +3004,11 @@
       <c r="J58" s="4" t="n">
         <v>0.1821</v>
       </c>
-      <c r="K58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
@@ -2819,7 +3047,11 @@
       <c r="J59" s="8" t="n">
         <v>-114.5083</v>
       </c>
-      <c r="K59" s="6" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L59" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST HALKA ARZ, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -2858,7 +3090,11 @@
       <c r="J60" s="4" t="n">
         <v>-4.4859</v>
       </c>
-      <c r="K60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST YILDIZ, BIST BURSA</t>
@@ -2899,7 +3135,11 @@
       <c r="J61" s="8" t="n">
         <v>14.2382</v>
       </c>
-      <c r="K61" s="6" t="inlineStr"/>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA, BIST KURUMSAL YÖNETİM</t>
@@ -2938,7 +3178,11 @@
       <c r="J62" s="4" t="n">
         <v>-19.4081</v>
       </c>
-      <c r="K62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST DENİZLİ</t>
@@ -2979,7 +3223,11 @@
       <c r="J63" s="8" t="n">
         <v>5.750299999999999</v>
       </c>
-      <c r="K63" s="6" t="inlineStr"/>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST 50, BIST MALİ, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
@@ -3018,7 +3266,11 @@
       <c r="J64" s="4" t="n">
         <v>-1.5785</v>
       </c>
-      <c r="K64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM</t>
@@ -3057,7 +3309,11 @@
       <c r="J65" s="8" t="n">
         <v>-1.2814</v>
       </c>
-      <c r="K65" s="6" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST 50, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -3098,7 +3354,11 @@
       <c r="J66" s="4" t="n">
         <v>7.844600000000001</v>
       </c>
-      <c r="K66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Sağlık teknolojisi</t>
+        </is>
+      </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOBİ SANAYİ, BIST KOCAELI</t>
@@ -3135,7 +3395,11 @@
         <v>-0.1067</v>
       </c>
       <c r="J67" s="6" t="inlineStr"/>
-      <c r="K67" s="6" t="inlineStr"/>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST YILDIZ</t>
@@ -3174,7 +3438,11 @@
       <c r="J68" s="4" t="n">
         <v>-2.8382</v>
       </c>
-      <c r="K68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST BURSA</t>
@@ -3215,7 +3483,11 @@
       <c r="J69" s="8" t="n">
         <v>9.006599999999999</v>
       </c>
-      <c r="K69" s="6" t="inlineStr"/>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA, BIST KURUMSAL YÖNETİM</t>
@@ -3254,7 +3526,11 @@
         <v>0.0143</v>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST KAYSERİ, BIST KATILIM TEMETTU</t>
@@ -3295,7 +3571,11 @@
       <c r="J71" s="8" t="n">
         <v>-23.3157</v>
       </c>
-      <c r="K71" s="6" t="inlineStr"/>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L71" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST GAYRİMENKUL YO, BIST 50, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST BANKA DISI LIKIT 10, BIST KATILIM 50, BIST KATILIM 30, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
@@ -3334,7 +3614,11 @@
       <c r="J72" s="4" t="n">
         <v>-13.642</v>
       </c>
-      <c r="K72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
@@ -3373,7 +3657,11 @@
       <c r="J73" s="8" t="n">
         <v>-24.3409</v>
       </c>
-      <c r="K73" s="6" t="inlineStr"/>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L73" s="6" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST ANKARA</t>
@@ -3412,7 +3700,11 @@
         <v>0.013</v>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST KATILIM TÜM, BIST ANA, BIST KAYSERİ</t>
@@ -3453,7 +3745,11 @@
       <c r="J75" s="8" t="n">
         <v>-1.1035</v>
       </c>
-      <c r="K75" s="6" t="inlineStr"/>
+      <c r="K75" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L75" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -3539,7 +3835,11 @@
       <c r="J77" s="8" t="n">
         <v>-1.9014</v>
       </c>
-      <c r="K77" s="6" t="inlineStr"/>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>Perakende satış</t>
+        </is>
+      </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -3578,7 +3878,11 @@
       <c r="J78" s="4" t="n">
         <v>-31.379</v>
       </c>
-      <c r="K78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA, BIST İZMİR</t>
@@ -3619,7 +3923,11 @@
       <c r="J79" s="8" t="n">
         <v>2.5571</v>
       </c>
-      <c r="K79" s="6" t="inlineStr"/>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L79" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST BURSA</t>
@@ -3656,7 +3964,11 @@
         <v>-0.07629999999999999</v>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA, BIST BALIKESİR</t>
@@ -3695,7 +4007,11 @@
       <c r="J81" s="8" t="n">
         <v>-9.4055</v>
       </c>
-      <c r="K81" s="6" t="inlineStr"/>
+      <c r="K81" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L81" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST MADENCİLİK, BIST KATILIM TÜM, BIST ANA, BIST KURUMSAL YÖNETİM</t>
@@ -3736,7 +4052,11 @@
       <c r="J82" s="4" t="n">
         <v>-1.5684</v>
       </c>
-      <c r="K82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ</t>
@@ -3775,7 +4095,11 @@
         <v>0.0435</v>
       </c>
       <c r="J83" s="6" t="inlineStr"/>
-      <c r="K83" s="6" t="inlineStr"/>
+      <c r="K83" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L83" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50</t>
@@ -3814,7 +4138,11 @@
       <c r="J84" s="4" t="n">
         <v>-7.1936</v>
       </c>
-      <c r="K84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
@@ -3855,7 +4183,11 @@
       <c r="J85" s="8" t="n">
         <v>11.6409</v>
       </c>
-      <c r="K85" s="6" t="inlineStr"/>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>Perakende satış</t>
+        </is>
+      </c>
       <c r="L85" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER</t>
@@ -3896,7 +4228,11 @@
       <c r="J86" s="4" t="n">
         <v>0.095</v>
       </c>
-      <c r="K86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KURUMSAL YÖNETİM</t>
@@ -3933,7 +4269,11 @@
         <v>0.004500000000000001</v>
       </c>
       <c r="J87" s="6" t="inlineStr"/>
-      <c r="K87" s="6" t="inlineStr"/>
+      <c r="K87" s="6" t="inlineStr">
+        <is>
+          <t>Çeşitli Hizmetler</t>
+        </is>
+      </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM TÜM, BIST ANA, BIST ANKARA</t>
@@ -3972,7 +4312,11 @@
         <v>0.0132</v>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST BALIKESİR</t>
@@ -4011,7 +4355,11 @@
       <c r="J89" s="8" t="n">
         <v>0.02</v>
       </c>
-      <c r="K89" s="6" t="inlineStr"/>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L89" s="6" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
@@ -4048,7 +4396,11 @@
         <v>-0.0034</v>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr"/>
     </row>
@@ -4083,7 +4435,11 @@
         <v>0.0222</v>
       </c>
       <c r="J91" s="6" t="inlineStr"/>
-      <c r="K91" s="6" t="inlineStr"/>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L91" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50</t>
@@ -4124,7 +4480,11 @@
       <c r="J92" s="4" t="n">
         <v>-0.2732</v>
       </c>
-      <c r="K92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA, BIST MANİSA</t>
@@ -4165,7 +4525,11 @@
       <c r="J93" s="8" t="n">
         <v>16.1168</v>
       </c>
-      <c r="K93" s="6" t="inlineStr"/>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>Perakende satış</t>
+        </is>
+      </c>
       <c r="L93" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
@@ -4206,7 +4570,11 @@
       <c r="J94" s="4" t="n">
         <v>1.93</v>
       </c>
-      <c r="K94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
@@ -4245,7 +4613,11 @@
       <c r="J95" s="8" t="n">
         <v>-1.7395</v>
       </c>
-      <c r="K95" s="6" t="inlineStr"/>
+      <c r="K95" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L95" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KAYSERİ</t>
@@ -4286,7 +4658,11 @@
       <c r="J96" s="4" t="n">
         <v>-1.5979</v>
       </c>
-      <c r="K96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, STOXX Emerging Markets 1500</t>
@@ -4325,7 +4701,11 @@
       <c r="J97" s="8" t="n">
         <v>-19.7854</v>
       </c>
-      <c r="K97" s="6" t="inlineStr"/>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L97" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST ANA, BIST ANTALYA</t>
@@ -4364,7 +4744,11 @@
       <c r="J98" s="4" t="n">
         <v>-1.5031</v>
       </c>
-      <c r="K98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA</t>
@@ -4405,7 +4789,11 @@
       <c r="J99" s="8" t="n">
         <v>2.8244</v>
       </c>
-      <c r="K99" s="6" t="inlineStr"/>
+      <c r="K99" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L99" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
@@ -4442,7 +4830,11 @@
         <v>-0.0406</v>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
-      <c r="K100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST KATILIM TÜM, BIST ANA</t>
@@ -4481,7 +4873,11 @@
       <c r="J101" s="8" t="n">
         <v>-12.0513</v>
       </c>
-      <c r="K101" s="6" t="inlineStr"/>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L101" s="6" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST ANKARA</t>
@@ -4518,7 +4914,11 @@
         <v>-0.1204</v>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
-      <c r="K102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -4557,7 +4957,11 @@
       <c r="J103" s="8" t="n">
         <v>-2.9215</v>
       </c>
-      <c r="K103" s="6" t="inlineStr"/>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L103" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST İZMİR, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
@@ -4596,7 +5000,11 @@
       <c r="J104" s="4" t="n">
         <v>-1.222</v>
       </c>
-      <c r="K104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA</t>
@@ -4633,7 +5041,11 @@
         <v>-0.0146</v>
       </c>
       <c r="J105" s="6" t="inlineStr"/>
-      <c r="K105" s="6" t="inlineStr"/>
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L105" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
@@ -4670,7 +5082,11 @@
       <c r="J106" s="4" t="n">
         <v>-2.7704</v>
       </c>
-      <c r="K106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST ANA, BIST İZMİR</t>
@@ -4711,7 +5127,11 @@
       <c r="J107" s="8" t="n">
         <v>8.0586</v>
       </c>
-      <c r="K107" s="6" t="inlineStr"/>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L107" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
@@ -4750,7 +5170,11 @@
       <c r="J108" s="4" t="n">
         <v>-1.5387</v>
       </c>
-      <c r="K108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA, BIST MANİSA</t>
@@ -4791,7 +5215,11 @@
       <c r="J109" s="8" t="n">
         <v>0.4181</v>
       </c>
-      <c r="K109" s="6" t="inlineStr"/>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L109" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST MALİ, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -4832,7 +5260,11 @@
       <c r="J110" s="4" t="n">
         <v>41.6796</v>
       </c>
-      <c r="K110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ</t>
@@ -4869,7 +5301,11 @@
         <v>0.0795</v>
       </c>
       <c r="J111" s="6" t="inlineStr"/>
-      <c r="K111" s="6" t="inlineStr"/>
+      <c r="K111" s="6" t="inlineStr">
+        <is>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
       <c r="L111" s="6" t="inlineStr">
         <is>
           <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
@@ -4910,7 +5346,11 @@
       <c r="J112" s="4" t="n">
         <v>1.1795</v>
       </c>
-      <c r="K112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST ANA, BIST TEMETTU</t>
@@ -4951,7 +5391,11 @@
       <c r="J113" s="8" t="n">
         <v>1.1742</v>
       </c>
-      <c r="K113" s="6" t="inlineStr"/>
+      <c r="K113" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L113" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST İZMİR</t>
@@ -4990,7 +5434,11 @@
         <v>0.0034</v>
       </c>
       <c r="J114" s="2" t="inlineStr"/>
-      <c r="K114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
@@ -5031,7 +5479,11 @@
       <c r="J115" s="8" t="n">
         <v>0.1293</v>
       </c>
-      <c r="K115" s="6" t="inlineStr"/>
+      <c r="K115" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L115" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
@@ -5072,7 +5524,11 @@
       <c r="J116" s="4" t="n">
         <v>-113.1382</v>
       </c>
-      <c r="K116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA, BIST ANKARA</t>
@@ -5111,7 +5567,11 @@
       <c r="J117" s="8" t="n">
         <v>0.7059000000000001</v>
       </c>
-      <c r="K117" s="6" t="inlineStr"/>
+      <c r="K117" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L117" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA</t>
@@ -5152,7 +5612,11 @@
       <c r="J118" s="4" t="n">
         <v>1.5477</v>
       </c>
-      <c r="K118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
           <t>BIST BANKA, BIST TUM-100, BIST TÜM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
@@ -5191,7 +5655,11 @@
       <c r="J119" s="8" t="n">
         <v>-2.4632</v>
       </c>
-      <c r="K119" s="6" t="inlineStr"/>
+      <c r="K119" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L119" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KURUMSAL YÖNETİM</t>
@@ -5230,7 +5698,11 @@
       <c r="J120" s="4" t="n">
         <v>-0.5884</v>
       </c>
-      <c r="K120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KOCAELI</t>
@@ -5271,7 +5743,11 @@
       <c r="J121" s="8" t="n">
         <v>5.5933</v>
       </c>
-      <c r="K121" s="6" t="inlineStr"/>
+      <c r="K121" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L121" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
@@ -5310,7 +5786,11 @@
       <c r="J122" s="4" t="n">
         <v>-4.7257</v>
       </c>
-      <c r="K122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA, BIST AYDIN</t>
@@ -5351,7 +5831,11 @@
       <c r="J123" s="8" t="n">
         <v>-0.5133</v>
       </c>
-      <c r="K123" s="6" t="inlineStr"/>
+      <c r="K123" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L123" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ, BIST TEMETTU</t>
@@ -5392,7 +5876,11 @@
       <c r="J124" s="4" t="n">
         <v>-0.0001</v>
       </c>
-      <c r="K124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>Enerji mineralleri</t>
+        </is>
+      </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST 50, BIST MALİ, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST BANKA DISI LIKIT 10, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
@@ -5431,7 +5919,11 @@
         <v>0.0926</v>
       </c>
       <c r="J125" s="6" t="inlineStr"/>
-      <c r="K125" s="6" t="inlineStr"/>
+      <c r="K125" s="6" t="inlineStr">
+        <is>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
       <c r="L125" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST KATILIM TEMETTU</t>
@@ -5470,7 +5962,11 @@
         <v>0.0159</v>
       </c>
       <c r="J126" s="2" t="inlineStr"/>
-      <c r="K126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA, ADANA</t>
@@ -5511,7 +6007,11 @@
       <c r="J127" s="8" t="n">
         <v>-0.9609000000000001</v>
       </c>
-      <c r="K127" s="6" t="inlineStr"/>
+      <c r="K127" s="6" t="inlineStr">
+        <is>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
       <c r="L127" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST ULASTIRMA, BIST TÜM, BIST 50, BIST HİZMETLER, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST BANKA DISI LIKIT 10, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
@@ -5552,7 +6052,11 @@
       <c r="J128" s="4" t="n">
         <v>5.0381</v>
       </c>
-      <c r="K128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST KATILIM TÜM, BIST ANA, ADANA</t>
@@ -5593,7 +6097,11 @@
       <c r="J129" s="8" t="n">
         <v>-3.3307</v>
       </c>
-      <c r="K129" s="6" t="inlineStr"/>
+      <c r="K129" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L129" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -5632,7 +6140,11 @@
       <c r="J130" s="4" t="n">
         <v>-8.579000000000001</v>
       </c>
-      <c r="K130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ</t>
@@ -5671,7 +6183,11 @@
       <c r="J131" s="8" t="n">
         <v>-0.3898</v>
       </c>
-      <c r="K131" s="6" t="inlineStr"/>
+      <c r="K131" s="6" t="inlineStr">
+        <is>
+          <t>Çeşitli Hizmetler</t>
+        </is>
+      </c>
       <c r="L131" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST HALKA ARZ, BIST MALİ, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST ANKARA</t>
@@ -5712,7 +6228,11 @@
       <c r="J132" s="4" t="n">
         <v>-8.504899999999999</v>
       </c>
-      <c r="K132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST YILDIZ, BIST KONYA</t>
@@ -5749,7 +6269,11 @@
       <c r="J133" s="8" t="n">
         <v>0.1822</v>
       </c>
-      <c r="K133" s="6" t="inlineStr"/>
+      <c r="K133" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L133" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA</t>
@@ -5788,7 +6312,11 @@
         <v>0.0017</v>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
-      <c r="K134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST 50, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST BANKA DISI LIKIT 10, BIST TEMETTU, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM 30, BIST KATILIM TEMETTU, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
@@ -5827,7 +6355,11 @@
       <c r="J135" s="8" t="n">
         <v>-2.6374</v>
       </c>
-      <c r="K135" s="6" t="inlineStr"/>
+      <c r="K135" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L135" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST ANA, BIST KONYA</t>
@@ -5866,7 +6398,11 @@
       <c r="J136" s="4" t="n">
         <v>-1.1066</v>
       </c>
-      <c r="K136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
@@ -5907,7 +6443,11 @@
       <c r="J137" s="8" t="n">
         <v>-1.4654</v>
       </c>
-      <c r="K137" s="6" t="inlineStr"/>
+      <c r="K137" s="6" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L137" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ, BIST KURUMSAL YÖNETİM</t>
@@ -5948,7 +6488,11 @@
       <c r="J138" s="4" t="n">
         <v>0.6855</v>
       </c>
-      <c r="K138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST LİKİT BANKA, BIST MALİ, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
@@ -5987,7 +6531,11 @@
       <c r="J139" s="8" t="n">
         <v>-18.3247</v>
       </c>
-      <c r="K139" s="6" t="inlineStr"/>
+      <c r="K139" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L139" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST BURSA</t>
@@ -6024,7 +6572,11 @@
         <v>-0.0447</v>
       </c>
       <c r="J140" s="2" t="inlineStr"/>
-      <c r="K140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>Çeşitli Hizmetler</t>
+        </is>
+      </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
@@ -6063,7 +6615,11 @@
       <c r="J141" s="8" t="n">
         <v>0.7347</v>
       </c>
-      <c r="K141" s="6" t="inlineStr"/>
+      <c r="K141" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L141" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
@@ -6102,7 +6658,11 @@
       <c r="J142" s="4" t="n">
         <v>-6.3558</v>
       </c>
-      <c r="K142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>Perakende satış</t>
+        </is>
+      </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK</t>
@@ -6141,7 +6701,11 @@
       <c r="J143" s="8" t="n">
         <v>-1.6467</v>
       </c>
-      <c r="K143" s="6" t="inlineStr"/>
+      <c r="K143" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L143" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
@@ -6180,7 +6744,11 @@
       <c r="J144" s="4" t="n">
         <v>-5.186900000000001</v>
       </c>
-      <c r="K144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>Çeşitli Hizmetler</t>
+        </is>
+      </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
           <t>BIST MENKUL KIYM YO</t>
@@ -6219,7 +6787,11 @@
       <c r="J145" s="8" t="n">
         <v>-5.5493</v>
       </c>
-      <c r="K145" s="6" t="inlineStr"/>
+      <c r="K145" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L145" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
@@ -6260,7 +6832,11 @@
       <c r="J146" s="4" t="n">
         <v>-2.7441</v>
       </c>
-      <c r="K146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST ANA</t>
@@ -6299,7 +6875,11 @@
       <c r="J147" s="8" t="n">
         <v>-18.749</v>
       </c>
-      <c r="K147" s="6" t="inlineStr"/>
+      <c r="K147" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L147" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST KİMYA PETROL PLASTİK, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST BANKA DISI LIKIT 10, BIST SÜRDÜRÜLEBİLİRLİK, ADANA, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
@@ -6338,7 +6918,11 @@
       <c r="J148" s="4" t="n">
         <v>-9.995900000000001</v>
       </c>
-      <c r="K148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST ANKARA</t>
@@ -6379,7 +6963,11 @@
       <c r="J149" s="8" t="n">
         <v>-0.5928</v>
       </c>
-      <c r="K149" s="6" t="inlineStr"/>
+      <c r="K149" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L149" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM TEMETTU, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST TEKİRDAĞ</t>
@@ -6420,7 +7008,11 @@
       <c r="J150" s="4" t="n">
         <v>0.3223</v>
       </c>
-      <c r="K150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST İSTANBUL, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
@@ -6459,7 +7051,11 @@
         <v>0.2405</v>
       </c>
       <c r="J151" s="6" t="inlineStr"/>
-      <c r="K151" s="6" t="inlineStr"/>
+      <c r="K151" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L151" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST BURSA</t>
@@ -6500,7 +7096,11 @@
       <c r="J152" s="4" t="n">
         <v>4.1559</v>
       </c>
-      <c r="K152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST YILDIZ</t>
@@ -6537,7 +7137,11 @@
         <v>-0.0213</v>
       </c>
       <c r="J153" s="6" t="inlineStr"/>
-      <c r="K153" s="6" t="inlineStr"/>
+      <c r="K153" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L153" s="6" t="inlineStr"/>
       <c r="M153" s="6" t="inlineStr"/>
     </row>
@@ -6570,7 +7174,11 @@
         <v>0.07679999999999999</v>
       </c>
       <c r="J154" s="2" t="inlineStr"/>
-      <c r="K154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L154" s="2" t="inlineStr"/>
       <c r="M154" s="2" t="inlineStr"/>
     </row>
@@ -6607,7 +7215,11 @@
       <c r="J155" s="8" t="n">
         <v>2.5571</v>
       </c>
-      <c r="K155" s="6" t="inlineStr"/>
+      <c r="K155" s="6" t="inlineStr">
+        <is>
+          <t>Perakende satış</t>
+        </is>
+      </c>
       <c r="L155" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA</t>
@@ -6644,7 +7256,11 @@
         <v>-0.1674</v>
       </c>
       <c r="J156" s="2" t="inlineStr"/>
-      <c r="K156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
@@ -6683,7 +7299,11 @@
       <c r="J157" s="8" t="n">
         <v>0.7471</v>
       </c>
-      <c r="K157" s="6" t="inlineStr"/>
+      <c r="K157" s="6" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L157" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -6722,7 +7342,11 @@
         <v>0.076</v>
       </c>
       <c r="J158" s="2" t="inlineStr"/>
-      <c r="K158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST YILDIZ, BIST KURUMSAL YÖNETİM</t>
@@ -6763,7 +7387,11 @@
       <c r="J159" s="8" t="n">
         <v>-0.2259</v>
       </c>
-      <c r="K159" s="6" t="inlineStr"/>
+      <c r="K159" s="6" t="inlineStr">
+        <is>
+          <t>İletişim</t>
+        </is>
+      </c>
       <c r="L159" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İLETİŞİM, BIST HİZMETLER, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
@@ -6802,7 +7430,11 @@
       <c r="J160" s="4" t="n">
         <v>-3.4952</v>
       </c>
-      <c r="K160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST KİMYA PETROL PLASTİK, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KATILIM 30, BIST İZMİR, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25</t>
@@ -6843,7 +7475,11 @@
       <c r="J161" s="8" t="n">
         <v>-0.068</v>
       </c>
-      <c r="K161" s="6" t="inlineStr"/>
+      <c r="K161" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L161" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM TEMETTU, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
@@ -6884,7 +7520,11 @@
       <c r="J162" s="4" t="n">
         <v>1.0588</v>
       </c>
-      <c r="K162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST LİKİT BANKA, BIST MALİ, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
@@ -6925,7 +7565,11 @@
       <c r="J163" s="8" t="n">
         <v>-1.9718</v>
       </c>
-      <c r="K163" s="6" t="inlineStr"/>
+      <c r="K163" s="6" t="inlineStr">
+        <is>
+          <t>Sağlık teknolojisi</t>
+        </is>
+      </c>
       <c r="L163" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU</t>
@@ -6966,7 +7610,11 @@
       <c r="J164" s="4" t="n">
         <v>-1.2862</v>
       </c>
-      <c r="K164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50</t>
@@ -7003,7 +7651,11 @@
         <v>-0.0042</v>
       </c>
       <c r="J165" s="6" t="inlineStr"/>
-      <c r="K165" s="6" t="inlineStr"/>
+      <c r="K165" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L165" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA</t>
@@ -7042,7 +7694,11 @@
       <c r="J166" s="4" t="n">
         <v>1.099</v>
       </c>
-      <c r="K166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
@@ -7081,7 +7737,11 @@
       <c r="J167" s="8" t="n">
         <v>-1.5758</v>
       </c>
-      <c r="K167" s="6" t="inlineStr"/>
+      <c r="K167" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L167" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
@@ -7120,7 +7780,11 @@
       <c r="J168" s="4" t="n">
         <v>0.8694</v>
       </c>
-      <c r="K168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST İZMİR</t>
@@ -7159,7 +7823,11 @@
       <c r="J169" s="8" t="n">
         <v>-0.5942000000000001</v>
       </c>
-      <c r="K169" s="6" t="inlineStr"/>
+      <c r="K169" s="6" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L169" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST YILDIZ</t>
@@ -7198,7 +7866,11 @@
       <c r="J170" s="4" t="n">
         <v>0.0537</v>
       </c>
-      <c r="K170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST METAL ESYA MAKİNA, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -7237,7 +7909,11 @@
       <c r="J171" s="8" t="n">
         <v>-4.305400000000001</v>
       </c>
-      <c r="K171" s="6" t="inlineStr"/>
+      <c r="K171" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L171" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA</t>
@@ -7278,7 +7954,11 @@
       <c r="J172" s="4" t="n">
         <v>2.0964</v>
       </c>
-      <c r="K172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA, BIST TEMETTU, BIST KURUMSAL YÖNETİM</t>
@@ -7319,7 +7999,11 @@
       <c r="J173" s="8" t="n">
         <v>-0.8391</v>
       </c>
-      <c r="K173" s="6" t="inlineStr"/>
+      <c r="K173" s="6" t="inlineStr">
+        <is>
+          <t>İletişim</t>
+        </is>
+      </c>
       <c r="L173" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İLETİŞİM, BIST HİZMETLER, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST ANKARA, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25</t>
@@ -7360,7 +8044,11 @@
       <c r="J174" s="4" t="n">
         <v>2.881</v>
       </c>
-      <c r="K174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST BURSA</t>
@@ -7399,7 +8087,11 @@
       <c r="J175" s="8" t="n">
         <v>-4.6418</v>
       </c>
-      <c r="K175" s="6" t="inlineStr"/>
+      <c r="K175" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L175" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM 30, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST AYDIN, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
@@ -7438,7 +8130,11 @@
       <c r="J176" s="4" t="n">
         <v>0.1112</v>
       </c>
-      <c r="K176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST YILDIZ, BIST KURUMSAL YÖNETİM</t>
@@ -7477,7 +8173,11 @@
       <c r="J177" s="8" t="n">
         <v>-4.419</v>
       </c>
-      <c r="K177" s="6" t="inlineStr"/>
+      <c r="K177" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L177" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST KURUMSAL YÖNETİM, BIST KONYA</t>
@@ -7518,7 +8218,11 @@
       <c r="J178" s="4" t="n">
         <v>-1.5011</v>
       </c>
-      <c r="K178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST 50, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
@@ -7559,7 +8263,11 @@
       <c r="J179" s="8" t="n">
         <v>0.6818000000000001</v>
       </c>
-      <c r="K179" s="6" t="inlineStr"/>
+      <c r="K179" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L179" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST BALIKESİR</t>
@@ -7598,7 +8306,11 @@
         <v>0.0323</v>
       </c>
       <c r="J180" s="2" t="inlineStr"/>
-      <c r="K180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST METAL ESYA MAKİNA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST ANKARA</t>
@@ -7639,7 +8351,11 @@
       <c r="J181" s="8" t="n">
         <v>0.1014</v>
       </c>
-      <c r="K181" s="6" t="inlineStr"/>
+      <c r="K181" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L181" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
@@ -7680,7 +8396,11 @@
       <c r="J182" s="4" t="n">
         <v>-0.8634000000000001</v>
       </c>
-      <c r="K182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
@@ -7721,7 +8441,11 @@
       <c r="J183" s="8" t="n">
         <v>2.3941</v>
       </c>
-      <c r="K183" s="6" t="inlineStr"/>
+      <c r="K183" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L183" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST TEKİRDAĞ</t>
@@ -7762,7 +8486,11 @@
       <c r="J184" s="4" t="n">
         <v>1.394</v>
       </c>
-      <c r="K184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA, BIST BALIKESİR</t>
@@ -7803,7 +8531,11 @@
       <c r="J185" s="8" t="n">
         <v>-0.7368000000000001</v>
       </c>
-      <c r="K185" s="6" t="inlineStr"/>
+      <c r="K185" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L185" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST 50, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST 50-30, BIST ANKARA, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -7842,7 +8574,11 @@
       <c r="J186" s="4" t="n">
         <v>-2.1476</v>
       </c>
-      <c r="K186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
@@ -7881,7 +8617,11 @@
       <c r="J187" s="8" t="n">
         <v>-7.0937</v>
       </c>
-      <c r="K187" s="6" t="inlineStr"/>
+      <c r="K187" s="6" t="inlineStr">
+        <is>
+          <t>Çeşitli Hizmetler</t>
+        </is>
+      </c>
       <c r="L187" s="6" t="inlineStr">
         <is>
           <t>BIST MENKUL KIYM YO</t>
@@ -7920,7 +8660,11 @@
       <c r="J188" s="4" t="n">
         <v>-5.3326</v>
       </c>
-      <c r="K188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA</t>
@@ -7959,7 +8703,11 @@
       <c r="J189" s="8" t="n">
         <v>-1.622</v>
       </c>
-      <c r="K189" s="6" t="inlineStr"/>
+      <c r="K189" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L189" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KOCAELI, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
@@ -7998,7 +8746,11 @@
       <c r="J190" s="4" t="n">
         <v>0.7206999999999999</v>
       </c>
-      <c r="K190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
@@ -8039,7 +8791,11 @@
       <c r="J191" s="8" t="n">
         <v>156.1426</v>
       </c>
-      <c r="K191" s="6" t="inlineStr"/>
+      <c r="K191" s="6" t="inlineStr">
+        <is>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
       <c r="L191" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST YILDIZ, BIST ANKARA</t>
@@ -8078,7 +8834,11 @@
       <c r="J192" s="4" t="n">
         <v>-0.3601</v>
       </c>
-      <c r="K192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L192" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST ANA, BIST İZMİR</t>
@@ -8119,7 +8879,11 @@
       <c r="J193" s="8" t="n">
         <v>-0.6119</v>
       </c>
-      <c r="K193" s="6" t="inlineStr"/>
+      <c r="K193" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L193" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST ANA, BIST TEMETTU</t>
@@ -8158,7 +8922,11 @@
         <v>0.03700000000000001</v>
       </c>
       <c r="J194" s="2" t="inlineStr"/>
-      <c r="K194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr">
+        <is>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
       <c r="L194" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST KOBİ SANAYİ, BIST ANKARA</t>
@@ -8197,7 +8965,11 @@
       <c r="J195" s="8" t="n">
         <v>-0.0447</v>
       </c>
-      <c r="K195" s="6" t="inlineStr"/>
+      <c r="K195" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L195" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
@@ -8236,7 +9008,11 @@
         <v>0.0508</v>
       </c>
       <c r="J196" s="2" t="inlineStr"/>
-      <c r="K196" s="2" t="inlineStr"/>
+      <c r="K196" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L196" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST ANA</t>
@@ -8277,7 +9053,11 @@
       <c r="J197" s="8" t="n">
         <v>-2.3862</v>
       </c>
-      <c r="K197" s="6" t="inlineStr"/>
+      <c r="K197" s="6" t="inlineStr">
+        <is>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
       <c r="L197" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL</t>
@@ -8316,7 +9096,11 @@
       <c r="J198" s="4" t="n">
         <v>0.1735</v>
       </c>
-      <c r="K198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L198" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA, BIST KAYSERİ</t>
@@ -8357,7 +9141,11 @@
       <c r="J199" s="8" t="n">
         <v>1.4774</v>
       </c>
-      <c r="K199" s="6" t="inlineStr"/>
+      <c r="K199" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L199" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA, BIST TEMETTU, BIST ANKARA</t>
@@ -8398,7 +9186,11 @@
       <c r="J200" s="4" t="n">
         <v>-6.6864</v>
       </c>
-      <c r="K200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
       <c r="L200" s="2" t="inlineStr">
         <is>
           <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA</t>
@@ -8437,7 +9229,11 @@
       <c r="J201" s="8" t="n">
         <v>-4.909800000000001</v>
       </c>
-      <c r="K201" s="6" t="inlineStr"/>
+      <c r="K201" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L201" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST KONYA</t>
@@ -8476,7 +9272,11 @@
       <c r="J202" s="4" t="n">
         <v>-2.2777</v>
       </c>
-      <c r="K202" s="2" t="inlineStr"/>
+      <c r="K202" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L202" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST İSTANBUL, BIST YILDIZ</t>
@@ -8517,7 +9317,11 @@
       <c r="J203" s="8" t="n">
         <v>-2.2043</v>
       </c>
-      <c r="K203" s="6" t="inlineStr"/>
+      <c r="K203" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L203" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
@@ -8556,7 +9360,11 @@
       <c r="J204" s="4" t="n">
         <v>0.4835</v>
       </c>
-      <c r="K204" s="2" t="inlineStr"/>
+      <c r="K204" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L204" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST KURUMSAL YÖNETİM</t>
@@ -8597,7 +9405,11 @@
       <c r="J205" s="8" t="n">
         <v>0.6942</v>
       </c>
-      <c r="K205" s="6" t="inlineStr"/>
+      <c r="K205" s="6" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L205" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -8634,7 +9446,11 @@
         <v>-0.4141</v>
       </c>
       <c r="J206" s="2" t="inlineStr"/>
-      <c r="K206" s="2" t="inlineStr"/>
+      <c r="K206" s="2" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L206" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
@@ -8673,7 +9489,11 @@
       <c r="J207" s="8" t="n">
         <v>-2.9048</v>
       </c>
-      <c r="K207" s="6" t="inlineStr"/>
+      <c r="K207" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L207" s="6" t="inlineStr"/>
       <c r="M207" s="6" t="inlineStr"/>
     </row>
@@ -8710,7 +9530,11 @@
       <c r="J208" s="4" t="n">
         <v>0.1967</v>
       </c>
-      <c r="K208" s="2" t="inlineStr"/>
+      <c r="K208" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L208" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
@@ -8751,7 +9575,11 @@
       <c r="J209" s="8" t="n">
         <v>1.1869</v>
       </c>
-      <c r="K209" s="6" t="inlineStr"/>
+      <c r="K209" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L209" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST LİKİT BANKA, BIST MALİ, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
@@ -8792,7 +9620,11 @@
       <c r="J210" s="4" t="n">
         <v>-0.6212</v>
       </c>
-      <c r="K210" s="2" t="inlineStr"/>
+      <c r="K210" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L210" s="2" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST BALIKESİR</t>
@@ -8831,7 +9663,11 @@
         <v>0.0579</v>
       </c>
       <c r="J211" s="6" t="inlineStr"/>
-      <c r="K211" s="6" t="inlineStr"/>
+      <c r="K211" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L211" s="6" t="inlineStr"/>
       <c r="M211" s="6" t="inlineStr"/>
     </row>
@@ -8866,7 +9702,11 @@
         <v>0.4621</v>
       </c>
       <c r="J212" s="2" t="inlineStr"/>
-      <c r="K212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="inlineStr">
+        <is>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
       <c r="L212" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -8907,7 +9747,11 @@
       <c r="J213" s="8" t="n">
         <v>2.8209</v>
       </c>
-      <c r="K213" s="6" t="inlineStr"/>
+      <c r="K213" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L213" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
@@ -8946,7 +9790,11 @@
       <c r="J214" s="4" t="n">
         <v>-8.9087</v>
       </c>
-      <c r="K214" s="2" t="inlineStr"/>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L214" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA, BIST BURSA</t>
@@ -8985,7 +9833,11 @@
       <c r="J215" s="8" t="n">
         <v>-1.2716</v>
       </c>
-      <c r="K215" s="6" t="inlineStr"/>
+      <c r="K215" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L215" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KURUMSAL YÖNETİM</t>
@@ -9024,7 +9876,11 @@
       <c r="J216" s="4" t="n">
         <v>-9.6821</v>
       </c>
-      <c r="K216" s="2" t="inlineStr"/>
+      <c r="K216" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L216" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KOCAELI, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
@@ -9061,7 +9917,11 @@
       <c r="J217" s="8" t="n">
         <v>68.1451</v>
       </c>
-      <c r="K217" s="6" t="inlineStr"/>
+      <c r="K217" s="6" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L217" s="6" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST YILDIZ, BIST DENİZLİ</t>
@@ -9102,7 +9962,11 @@
       <c r="J218" s="4" t="n">
         <v>2.5615</v>
       </c>
-      <c r="K218" s="2" t="inlineStr"/>
+      <c r="K218" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L218" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST ANA</t>
@@ -9141,7 +10005,11 @@
         <v>0.1781</v>
       </c>
       <c r="J219" s="6" t="inlineStr"/>
-      <c r="K219" s="6" t="inlineStr"/>
+      <c r="K219" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L219" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM</t>
@@ -9182,7 +10050,11 @@
       <c r="J220" s="4" t="n">
         <v>1.5318</v>
       </c>
-      <c r="K220" s="2" t="inlineStr"/>
+      <c r="K220" s="2" t="inlineStr">
+        <is>
+          <t>Sağlık teknolojisi</t>
+        </is>
+      </c>
       <c r="L220" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
@@ -9223,7 +10095,11 @@
       <c r="J221" s="8" t="n">
         <v>0.9056999999999999</v>
       </c>
-      <c r="K221" s="6" t="inlineStr"/>
+      <c r="K221" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L221" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ANA, BIST ANKARA</t>
@@ -9264,7 +10140,11 @@
       <c r="J222" s="4" t="n">
         <v>0.9412</v>
       </c>
-      <c r="K222" s="2" t="inlineStr"/>
+      <c r="K222" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L222" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST YILDIZ</t>
@@ -9303,7 +10183,11 @@
       <c r="J223" s="8" t="n">
         <v>-0.0625</v>
       </c>
-      <c r="K223" s="6" t="inlineStr"/>
+      <c r="K223" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L223" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -9344,7 +10228,11 @@
       <c r="J224" s="4" t="n">
         <v>16.3404</v>
       </c>
-      <c r="K224" s="2" t="inlineStr"/>
+      <c r="K224" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L224" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KOCAELI</t>
@@ -9385,7 +10273,11 @@
       <c r="J225" s="8" t="n">
         <v>-0.08199999999999999</v>
       </c>
-      <c r="K225" s="6" t="inlineStr"/>
+      <c r="K225" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L225" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST LİKİT BANKA, BIST MALİ, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -9426,7 +10318,11 @@
       <c r="J226" s="4" t="n">
         <v>1.3131</v>
       </c>
-      <c r="K226" s="2" t="inlineStr"/>
+      <c r="K226" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L226" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
@@ -9467,7 +10363,11 @@
       <c r="J227" s="8" t="n">
         <v>2.5821</v>
       </c>
-      <c r="K227" s="6" t="inlineStr"/>
+      <c r="K227" s="6" t="inlineStr">
+        <is>
+          <t>Sağlık hizmetleri</t>
+        </is>
+      </c>
       <c r="L227" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST İZMİR</t>
@@ -9508,7 +10408,11 @@
       <c r="J228" s="4" t="n">
         <v>-0.3902</v>
       </c>
-      <c r="K228" s="2" t="inlineStr"/>
+      <c r="K228" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L228" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
@@ -9549,7 +10453,11 @@
       <c r="J229" s="8" t="n">
         <v>0.0447</v>
       </c>
-      <c r="K229" s="6" t="inlineStr"/>
+      <c r="K229" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L229" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST LİKİT BANKA, BIST MALİ, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
@@ -9590,7 +10498,11 @@
       <c r="J230" s="4" t="n">
         <v>0.2344</v>
       </c>
-      <c r="K230" s="2" t="inlineStr"/>
+      <c r="K230" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L230" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST ANA, BIST KURUMSAL YÖNETİM</t>
@@ -9631,7 +10543,11 @@
       <c r="J231" s="8" t="n">
         <v>-0.1339</v>
       </c>
-      <c r="K231" s="6" t="inlineStr"/>
+      <c r="K231" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L231" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST LİKİT BANKA, BIST MALİ, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
@@ -9672,7 +10588,11 @@
       <c r="J232" s="4" t="n">
         <v>-1.203</v>
       </c>
-      <c r="K232" s="2" t="inlineStr"/>
+      <c r="K232" s="2" t="inlineStr">
+        <is>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
       <c r="L232" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST 50, BIST MALİ, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
@@ -9711,7 +10631,11 @@
       <c r="J233" s="8" t="n">
         <v>-105.9833</v>
       </c>
-      <c r="K233" s="6" t="inlineStr"/>
+      <c r="K233" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L233" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA</t>
@@ -9752,7 +10676,11 @@
       <c r="J234" s="4" t="n">
         <v>-0.2881</v>
       </c>
-      <c r="K234" s="2" t="inlineStr"/>
+      <c r="K234" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L234" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ORMAN KAĞIT BASIM, BIST YILDIZ, BIST TEMETTU, BIST KURUMSAL YÖNETİM, BIST TEKİRDAĞ</t>
@@ -9793,7 +10721,11 @@
       <c r="J235" s="8" t="n">
         <v>-0.8061</v>
       </c>
-      <c r="K235" s="6" t="inlineStr"/>
+      <c r="K235" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L235" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST ULASTIRMA, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
@@ -9832,7 +10764,11 @@
       <c r="J236" s="4" t="n">
         <v>-2.3758</v>
       </c>
-      <c r="K236" s="2" t="inlineStr"/>
+      <c r="K236" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L236" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST ANA</t>
@@ -9871,7 +10807,11 @@
       <c r="J237" s="8" t="n">
         <v>-16.4677</v>
       </c>
-      <c r="K237" s="6" t="inlineStr"/>
+      <c r="K237" s="6" t="inlineStr">
+        <is>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
       <c r="L237" s="6" t="inlineStr">
         <is>
           <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -9910,7 +10850,11 @@
         <v>0.4857</v>
       </c>
       <c r="J238" s="2" t="inlineStr"/>
-      <c r="K238" s="2" t="inlineStr"/>
+      <c r="K238" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L238" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
@@ -9951,7 +10895,11 @@
       <c r="J239" s="8" t="n">
         <v>11.4715</v>
       </c>
-      <c r="K239" s="6" t="inlineStr"/>
+      <c r="K239" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L239" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ, BIST TEMETTU</t>
@@ -9992,7 +10940,11 @@
       <c r="J240" s="4" t="n">
         <v>-5.5053</v>
       </c>
-      <c r="K240" s="2" t="inlineStr"/>
+      <c r="K240" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L240" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST ANA</t>
@@ -10031,7 +10983,11 @@
         <v>0.0173</v>
       </c>
       <c r="J241" s="6" t="inlineStr"/>
-      <c r="K241" s="6" t="inlineStr"/>
+      <c r="K241" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L241" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL</t>
@@ -10072,7 +11028,11 @@
       <c r="J242" s="4" t="n">
         <v>0.2388</v>
       </c>
-      <c r="K242" s="2" t="inlineStr"/>
+      <c r="K242" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L242" s="2" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
@@ -10113,7 +11073,11 @@
       <c r="J243" s="8" t="n">
         <v>-1.8749</v>
       </c>
-      <c r="K243" s="6" t="inlineStr"/>
+      <c r="K243" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L243" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -10150,7 +11114,11 @@
       <c r="J244" s="4" t="n">
         <v>-4.2686</v>
       </c>
-      <c r="K244" s="2" t="inlineStr"/>
+      <c r="K244" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KOBİ SANAYİ</t>
@@ -10191,7 +11159,11 @@
       <c r="J245" s="8" t="n">
         <v>8.42</v>
       </c>
-      <c r="K245" s="6" t="inlineStr"/>
+      <c r="K245" s="6" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L245" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
@@ -10232,7 +11204,11 @@
       <c r="J246" s="4" t="n">
         <v>-2.0563</v>
       </c>
-      <c r="K246" s="2" t="inlineStr"/>
+      <c r="K246" s="2" t="inlineStr">
+        <is>
+          <t>Sağlık hizmetleri</t>
+        </is>
+      </c>
       <c r="L246" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
@@ -10273,7 +11249,11 @@
       <c r="J247" s="8" t="n">
         <v>0.008699999999999999</v>
       </c>
-      <c r="K247" s="6" t="inlineStr"/>
+      <c r="K247" s="6" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L247" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -10314,7 +11294,11 @@
       <c r="J248" s="4" t="n">
         <v>-1.293</v>
       </c>
-      <c r="K248" s="2" t="inlineStr"/>
+      <c r="K248" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L248" s="2" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST KURUMSAL YÖNETİM, BIST İZMİR</t>
@@ -10355,7 +11339,11 @@
       <c r="J249" s="8" t="n">
         <v>328.5973</v>
       </c>
-      <c r="K249" s="6" t="inlineStr"/>
+      <c r="K249" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L249" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
@@ -10396,7 +11384,11 @@
       <c r="J250" s="4" t="n">
         <v>0.0314</v>
       </c>
-      <c r="K250" s="2" t="inlineStr"/>
+      <c r="K250" s="2" t="inlineStr">
+        <is>
+          <t>Sağlık hizmetleri</t>
+        </is>
+      </c>
       <c r="L250" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST KATILIM TEMETTU, BIST ANKARA</t>
@@ -10437,7 +11429,11 @@
       <c r="J251" s="8" t="n">
         <v>3.3313</v>
       </c>
-      <c r="K251" s="6" t="inlineStr"/>
+      <c r="K251" s="6" t="inlineStr">
+        <is>
+          <t>Perakende satış</t>
+        </is>
+      </c>
       <c r="L251" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA</t>
@@ -10476,7 +11472,11 @@
       <c r="J252" s="4" t="n">
         <v>-5.3873</v>
       </c>
-      <c r="K252" s="2" t="inlineStr"/>
+      <c r="K252" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST ANA</t>
@@ -10513,7 +11513,11 @@
         <v>-0.0683</v>
       </c>
       <c r="J253" s="6" t="inlineStr"/>
-      <c r="K253" s="6" t="inlineStr"/>
+      <c r="K253" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L253" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST KATILIM 50, BIST KAYSERİ</t>
@@ -10554,7 +11558,11 @@
       <c r="J254" s="4" t="n">
         <v>13.7151</v>
       </c>
-      <c r="K254" s="2" t="inlineStr"/>
+      <c r="K254" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L254" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST YILDIZ</t>
@@ -10593,7 +11601,11 @@
       <c r="J255" s="8" t="n">
         <v>0.7664</v>
       </c>
-      <c r="K255" s="6" t="inlineStr"/>
+      <c r="K255" s="6" t="inlineStr">
+        <is>
+          <t>Sağlık teknolojisi</t>
+        </is>
+      </c>
       <c r="L255" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
@@ -10632,7 +11644,11 @@
       <c r="J256" s="4" t="n">
         <v>-5.8898</v>
       </c>
-      <c r="K256" s="2" t="inlineStr"/>
+      <c r="K256" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L256" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST ANA</t>
@@ -10673,7 +11689,11 @@
       <c r="J257" s="8" t="n">
         <v>-1.456</v>
       </c>
-      <c r="K257" s="6" t="inlineStr"/>
+      <c r="K257" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L257" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ, BIST TEMETTU</t>
@@ -10714,7 +11734,11 @@
       <c r="J258" s="4" t="n">
         <v>-0.3668</v>
       </c>
-      <c r="K258" s="2" t="inlineStr"/>
+      <c r="K258" s="2" t="inlineStr">
+        <is>
+          <t>Enerji mineralleri</t>
+        </is>
+      </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST KİMYA PETROL PLASTİK, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST BANKA DISI LIKIT 10, BIST TEMETTU, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM 30, BIST KATILIM TEMETTU, BIST KOCAELI, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
@@ -10753,7 +11777,11 @@
         <v>0.0344</v>
       </c>
       <c r="J259" s="6" t="inlineStr"/>
-      <c r="K259" s="6" t="inlineStr"/>
+      <c r="K259" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L259" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST BURSA, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
@@ -10790,7 +11818,11 @@
       <c r="J260" s="4" t="n">
         <v>-0.5714</v>
       </c>
-      <c r="K260" s="2" t="inlineStr"/>
+      <c r="K260" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L260" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST SİGORTA, BIST MALİ, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK</t>
@@ -10831,7 +11863,11 @@
       <c r="J261" s="8" t="n">
         <v>-0.722</v>
       </c>
-      <c r="K261" s="6" t="inlineStr"/>
+      <c r="K261" s="6" t="inlineStr">
+        <is>
+          <t>Perakende satış</t>
+        </is>
+      </c>
       <c r="L261" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST TİCARET, BIST HİZMETLER, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
@@ -10872,7 +11908,11 @@
       <c r="J262" s="4" t="n">
         <v>0.8454</v>
       </c>
-      <c r="K262" s="2" t="inlineStr"/>
+      <c r="K262" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L262" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
@@ -10911,7 +11951,11 @@
       <c r="J263" s="8" t="n">
         <v>-2.2139</v>
       </c>
-      <c r="K263" s="6" t="inlineStr"/>
+      <c r="K263" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L263" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST BALIKESİR</t>
@@ -10950,7 +11994,11 @@
       <c r="J264" s="4" t="n">
         <v>-1.3459</v>
       </c>
-      <c r="K264" s="2" t="inlineStr"/>
+      <c r="K264" s="2" t="inlineStr">
+        <is>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
       <c r="L264" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST HALKA ARZ, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM, BIST ANKARA</t>
@@ -10987,7 +12035,11 @@
       <c r="J265" s="8" t="n">
         <v>0.8834000000000001</v>
       </c>
-      <c r="K265" s="6" t="inlineStr"/>
+      <c r="K265" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L265" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST ANA</t>
@@ -11028,7 +12080,11 @@
       <c r="J266" s="4" t="n">
         <v>0.701</v>
       </c>
-      <c r="K266" s="2" t="inlineStr"/>
+      <c r="K266" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L266" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU, BIST İZMİR</t>
@@ -11069,7 +12125,11 @@
       <c r="J267" s="8" t="n">
         <v>2.6888</v>
       </c>
-      <c r="K267" s="6" t="inlineStr"/>
+      <c r="K267" s="6" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L267" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
@@ -11110,7 +12170,11 @@
       <c r="J268" s="4" t="n">
         <v>-0.05889999999999999</v>
       </c>
-      <c r="K268" s="2" t="inlineStr"/>
+      <c r="K268" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L268" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
@@ -11151,7 +12215,11 @@
       <c r="J269" s="8" t="n">
         <v>-0.6236999999999999</v>
       </c>
-      <c r="K269" s="6" t="inlineStr"/>
+      <c r="K269" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L269" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KOCAELI</t>
@@ -11190,7 +12258,11 @@
         <v>0.4496</v>
       </c>
       <c r="J270" s="2" t="inlineStr"/>
-      <c r="K270" s="2" t="inlineStr"/>
+      <c r="K270" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L270" s="2" t="inlineStr"/>
       <c r="M270" s="2" t="inlineStr"/>
     </row>
@@ -11225,7 +12297,11 @@
       <c r="J271" s="8" t="n">
         <v>0.5267000000000001</v>
       </c>
-      <c r="K271" s="6" t="inlineStr"/>
+      <c r="K271" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L271" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
@@ -11264,7 +12340,11 @@
         <v>0.009000000000000001</v>
       </c>
       <c r="J272" s="2" t="inlineStr"/>
-      <c r="K272" s="2" t="inlineStr"/>
+      <c r="K272" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L272" s="2" t="inlineStr"/>
       <c r="M272" s="2" t="inlineStr"/>
     </row>
@@ -11295,7 +12375,11 @@
         <v>-0.0272</v>
       </c>
       <c r="J273" s="6" t="inlineStr"/>
-      <c r="K273" s="6" t="inlineStr"/>
+      <c r="K273" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L273" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST KAYSERİ</t>
@@ -11336,7 +12420,11 @@
       <c r="J274" s="4" t="n">
         <v>-0.2381</v>
       </c>
-      <c r="K274" s="2" t="inlineStr"/>
+      <c r="K274" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L274" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST İZMİR</t>
@@ -11373,7 +12461,11 @@
       <c r="J275" s="8" t="n">
         <v>-3.2771</v>
       </c>
-      <c r="K275" s="6" t="inlineStr"/>
+      <c r="K275" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L275" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA, BIST MANİSA</t>
@@ -11414,7 +12506,11 @@
       <c r="J276" s="4" t="n">
         <v>6.779</v>
       </c>
-      <c r="K276" s="2" t="inlineStr"/>
+      <c r="K276" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L276" s="2" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -11498,7 +12594,11 @@
       <c r="J278" s="4" t="n">
         <v>-1.3921</v>
       </c>
-      <c r="K278" s="2" t="inlineStr"/>
+      <c r="K278" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L278" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST İZMİR</t>
@@ -11537,7 +12637,11 @@
       <c r="J279" s="8" t="n">
         <v>-17.9959</v>
       </c>
-      <c r="K279" s="6" t="inlineStr"/>
+      <c r="K279" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L279" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
@@ -11578,7 +12682,11 @@
       <c r="J280" s="4" t="n">
         <v>0.2796</v>
       </c>
-      <c r="K280" s="2" t="inlineStr"/>
+      <c r="K280" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L280" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST MALİ, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
@@ -11617,7 +12725,11 @@
       <c r="J281" s="8" t="n">
         <v>6.849</v>
       </c>
-      <c r="K281" s="6" t="inlineStr"/>
+      <c r="K281" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L281" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST İSTANBUL, BIST ANA</t>
@@ -11658,7 +12770,11 @@
       <c r="J282" s="4" t="n">
         <v>-3.2424</v>
       </c>
-      <c r="K282" s="2" t="inlineStr"/>
+      <c r="K282" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L282" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST TAŞ TOPRAK, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST İZMİR, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -11697,7 +12813,11 @@
       <c r="J283" s="8" t="n">
         <v>-18.5072</v>
       </c>
-      <c r="K283" s="6" t="inlineStr"/>
+      <c r="K283" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L283" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA, BIST KOCAELI</t>
@@ -11738,7 +12858,11 @@
       <c r="J284" s="4" t="n">
         <v>35.4728</v>
       </c>
-      <c r="K284" s="2" t="inlineStr"/>
+      <c r="K284" s="2" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L284" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -11777,7 +12901,11 @@
       <c r="J285" s="8" t="n">
         <v>0.233</v>
       </c>
-      <c r="K285" s="6" t="inlineStr"/>
+      <c r="K285" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L285" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST HALKA ARZ, BIST MALİ, BIST ANA</t>
@@ -11818,7 +12946,11 @@
       <c r="J286" s="4" t="n">
         <v>4.8334</v>
       </c>
-      <c r="K286" s="2" t="inlineStr"/>
+      <c r="K286" s="2" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L286" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST ANA, BIST ANTALYA</t>
@@ -11857,7 +12989,11 @@
       <c r="J287" s="8" t="n">
         <v>1.6493</v>
       </c>
-      <c r="K287" s="6" t="inlineStr"/>
+      <c r="K287" s="6" t="inlineStr">
+        <is>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
       <c r="L287" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
@@ -11898,7 +13034,11 @@
       <c r="J288" s="4" t="n">
         <v>-0.4633</v>
       </c>
-      <c r="K288" s="2" t="inlineStr"/>
+      <c r="K288" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L288" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
@@ -11939,7 +13079,11 @@
       <c r="J289" s="8" t="n">
         <v>0.197</v>
       </c>
-      <c r="K289" s="6" t="inlineStr"/>
+      <c r="K289" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L289" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST SİGORTA, BIST MALİ, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
@@ -12025,7 +13169,11 @@
       <c r="J291" s="8" t="n">
         <v>-0.4064</v>
       </c>
-      <c r="K291" s="6" t="inlineStr"/>
+      <c r="K291" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L291" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST TAŞ TOPRAK, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KATILIM 30, BIST 50-30, BIST KATILIM TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -12066,7 +13214,11 @@
       <c r="J292" s="4" t="n">
         <v>-0.07519999999999999</v>
       </c>
-      <c r="K292" s="2" t="inlineStr"/>
+      <c r="K292" s="2" t="inlineStr">
+        <is>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
       <c r="L292" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İNŞAAT, BIST HİZMETLER, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
@@ -12107,7 +13259,11 @@
       <c r="J293" s="8" t="n">
         <v>7.5378</v>
       </c>
-      <c r="K293" s="6" t="inlineStr"/>
+      <c r="K293" s="6" t="inlineStr">
+        <is>
+          <t>Çeşitli Hizmetler</t>
+        </is>
+      </c>
       <c r="L293" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU</t>
@@ -12146,7 +13302,11 @@
       <c r="J294" s="4" t="n">
         <v>-1.1628</v>
       </c>
-      <c r="K294" s="2" t="inlineStr"/>
+      <c r="K294" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L294" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST İSTANBUL, BIST ANA</t>
@@ -12187,7 +13347,11 @@
       <c r="J295" s="8" t="n">
         <v>2.5488</v>
       </c>
-      <c r="K295" s="6" t="inlineStr"/>
+      <c r="K295" s="6" t="inlineStr">
+        <is>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
       <c r="L295" s="6" t="inlineStr">
         <is>
           <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
@@ -12226,7 +13390,11 @@
       <c r="J296" s="4" t="n">
         <v>0.0693</v>
       </c>
-      <c r="K296" s="2" t="inlineStr"/>
+      <c r="K296" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L296" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA</t>
@@ -12265,7 +13433,11 @@
       <c r="J297" s="8" t="n">
         <v>-5.3684</v>
       </c>
-      <c r="K297" s="6" t="inlineStr"/>
+      <c r="K297" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L297" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
@@ -12304,7 +13476,11 @@
       <c r="J298" s="4" t="n">
         <v>-2.9114</v>
       </c>
-      <c r="K298" s="2" t="inlineStr"/>
+      <c r="K298" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L298" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -12343,7 +13519,11 @@
       <c r="J299" s="8" t="n">
         <v>-11.2933</v>
       </c>
-      <c r="K299" s="6" t="inlineStr"/>
+      <c r="K299" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L299" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -12384,7 +13564,11 @@
       <c r="J300" s="4" t="n">
         <v>-0.8568000000000001</v>
       </c>
-      <c r="K300" s="2" t="inlineStr"/>
+      <c r="K300" s="2" t="inlineStr">
+        <is>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
       <c r="L300" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST ANKARA</t>
@@ -12425,7 +13609,11 @@
       <c r="J301" s="8" t="n">
         <v>0.2988</v>
       </c>
-      <c r="K301" s="6" t="inlineStr"/>
+      <c r="K301" s="6" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L301" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
@@ -12466,7 +13654,11 @@
       <c r="J302" s="4" t="n">
         <v>1.5455</v>
       </c>
-      <c r="K302" s="2" t="inlineStr"/>
+      <c r="K302" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L302" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST YILDIZ, BIST TEMETTU</t>
@@ -12505,7 +13697,11 @@
       <c r="J303" s="8" t="n">
         <v>-1.8265</v>
       </c>
-      <c r="K303" s="6" t="inlineStr"/>
+      <c r="K303" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L303" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST ANKARA</t>
@@ -12546,7 +13742,11 @@
       <c r="J304" s="4" t="n">
         <v>0.8362999999999999</v>
       </c>
-      <c r="K304" s="2" t="inlineStr"/>
+      <c r="K304" s="2" t="inlineStr">
+        <is>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
       <c r="L304" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -12587,7 +13787,11 @@
       <c r="J305" s="8" t="n">
         <v>4.1859</v>
       </c>
-      <c r="K305" s="6" t="inlineStr"/>
+      <c r="K305" s="6" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L305" s="6" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KURUMSAL YÖNETİM, BIST KATILIM TEMETTU</t>
@@ -12626,7 +13830,11 @@
       <c r="J306" s="4" t="n">
         <v>0.3825</v>
       </c>
-      <c r="K306" s="2" t="inlineStr"/>
+      <c r="K306" s="2" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L306" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -12665,7 +13873,11 @@
       <c r="J307" s="8" t="n">
         <v>-0.0438</v>
       </c>
-      <c r="K307" s="6" t="inlineStr"/>
+      <c r="K307" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L307" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST YILDIZ</t>
@@ -12706,7 +13918,11 @@
       <c r="J308" s="4" t="n">
         <v>5.7455</v>
       </c>
-      <c r="K308" s="2" t="inlineStr"/>
+      <c r="K308" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L308" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -12745,7 +13961,11 @@
       <c r="J309" s="8" t="n">
         <v>0.0576</v>
       </c>
-      <c r="K309" s="6" t="inlineStr"/>
+      <c r="K309" s="6" t="inlineStr">
+        <is>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
       <c r="L309" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HİZMETLER, BIST ANA, BIST ANKARA</t>
@@ -12782,7 +14002,11 @@
         <v>0.0235</v>
       </c>
       <c r="J310" s="2" t="inlineStr"/>
-      <c r="K310" s="2" t="inlineStr"/>
+      <c r="K310" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L310" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST ANA, BIST KOBİ SANAYİ, BIST İZMİR</t>
@@ -12823,7 +14047,11 @@
       <c r="J311" s="8" t="n">
         <v>-0.0863</v>
       </c>
-      <c r="K311" s="6" t="inlineStr"/>
+      <c r="K311" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L311" s="6" t="inlineStr"/>
       <c r="M311" s="6" t="inlineStr"/>
     </row>
@@ -12860,7 +14088,11 @@
       <c r="J312" s="4" t="n">
         <v>-3.014</v>
       </c>
-      <c r="K312" s="2" t="inlineStr"/>
+      <c r="K312" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L312" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
@@ -12901,7 +14133,11 @@
       <c r="J313" s="8" t="n">
         <v>0.6712</v>
       </c>
-      <c r="K313" s="6" t="inlineStr"/>
+      <c r="K313" s="6" t="inlineStr">
+        <is>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
       <c r="L313" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST TEMETTU</t>
@@ -12942,7 +14178,11 @@
       <c r="J314" s="4" t="n">
         <v>-0.3443</v>
       </c>
-      <c r="K314" s="2" t="inlineStr"/>
+      <c r="K314" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L314" s="2" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST KATILIM TEMETTU, BIST ANKARA</t>
@@ -12983,7 +14223,11 @@
       <c r="J315" s="8" t="n">
         <v>0.8176000000000001</v>
       </c>
-      <c r="K315" s="6" t="inlineStr"/>
+      <c r="K315" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L315" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA</t>
@@ -13018,7 +14262,11 @@
         <v>-0.0403</v>
       </c>
       <c r="J316" s="2" t="inlineStr"/>
-      <c r="K316" s="2" t="inlineStr"/>
+      <c r="K316" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L316" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST ANA</t>
@@ -13059,7 +14307,11 @@
       <c r="J317" s="8" t="n">
         <v>-0.2047</v>
       </c>
-      <c r="K317" s="6" t="inlineStr"/>
+      <c r="K317" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L317" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA, BIST ANKARA</t>
@@ -13098,7 +14350,11 @@
       <c r="J318" s="4" t="n">
         <v>0.0029</v>
       </c>
-      <c r="K318" s="2" t="inlineStr"/>
+      <c r="K318" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L318" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
@@ -13135,7 +14391,11 @@
       <c r="J319" s="8" t="n">
         <v>-0.2884</v>
       </c>
-      <c r="K319" s="6" t="inlineStr"/>
+      <c r="K319" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L319" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST ANA</t>
@@ -13174,7 +14434,11 @@
       <c r="J320" s="4" t="n">
         <v>-1.6584</v>
       </c>
-      <c r="K320" s="2" t="inlineStr"/>
+      <c r="K320" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L320" s="2" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST YILDIZ, BIST ANKARA</t>
@@ -13215,7 +14479,11 @@
       <c r="J321" s="8" t="n">
         <v>0.0506</v>
       </c>
-      <c r="K321" s="6" t="inlineStr"/>
+      <c r="K321" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L321" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM 50, BIST KATILIM TEMETTU, BIST İZMİR</t>
@@ -13256,7 +14524,11 @@
       <c r="J322" s="4" t="n">
         <v>-0.5638000000000001</v>
       </c>
-      <c r="K322" s="2" t="inlineStr"/>
+      <c r="K322" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L322" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST TAŞ TOPRAK, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST ANKARA, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -13295,7 +14567,11 @@
       <c r="J323" s="8" t="n">
         <v>0.2025</v>
       </c>
-      <c r="K323" s="6" t="inlineStr"/>
+      <c r="K323" s="6" t="inlineStr">
+        <is>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
       <c r="L323" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM, BIST ANA, BIST ANKARA</t>
@@ -13332,7 +14608,11 @@
         <v>-0.3044</v>
       </c>
       <c r="J324" s="2" t="inlineStr"/>
-      <c r="K324" s="2" t="inlineStr"/>
+      <c r="K324" s="2" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L324" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
@@ -13373,7 +14653,11 @@
       <c r="J325" s="8" t="n">
         <v>0.2738</v>
       </c>
-      <c r="K325" s="6" t="inlineStr"/>
+      <c r="K325" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L325" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST DENİZLİ</t>
@@ -13412,7 +14696,11 @@
       <c r="J326" s="4" t="n">
         <v>0.3541</v>
       </c>
-      <c r="K326" s="2" t="inlineStr"/>
+      <c r="K326" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L326" s="2" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST AYDIN</t>
@@ -13451,7 +14739,11 @@
       <c r="J327" s="8" t="n">
         <v>-3.104</v>
       </c>
-      <c r="K327" s="6" t="inlineStr"/>
+      <c r="K327" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L327" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST KATILIM TEMETTU, BIST AYDIN</t>
@@ -13492,7 +14784,11 @@
       <c r="J328" s="4" t="n">
         <v>-1.3787</v>
       </c>
-      <c r="K328" s="2" t="inlineStr"/>
+      <c r="K328" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L328" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST MADENCİLİK, BIST 50, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST 50-30, BIST ANKARA, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -13531,7 +14827,11 @@
       <c r="J329" s="8" t="n">
         <v>-313.1914</v>
       </c>
-      <c r="K329" s="6" t="inlineStr"/>
+      <c r="K329" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L329" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST TİCARET, BIST HİZMETLER, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -13572,7 +14872,11 @@
       <c r="J330" s="4" t="n">
         <v>-0.9063</v>
       </c>
-      <c r="K330" s="2" t="inlineStr"/>
+      <c r="K330" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L330" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
@@ -13613,7 +14917,11 @@
       <c r="J331" s="8" t="n">
         <v>3.7407</v>
       </c>
-      <c r="K331" s="6" t="inlineStr"/>
+      <c r="K331" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L331" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST ANKARA</t>
@@ -13654,7 +14962,11 @@
       <c r="J332" s="4" t="n">
         <v>-1.4265</v>
       </c>
-      <c r="K332" s="2" t="inlineStr"/>
+      <c r="K332" s="2" t="inlineStr">
+        <is>
+          <t>Enerji mineralleri</t>
+        </is>
+      </c>
       <c r="L332" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST MADENCİLİK, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST ANKARA</t>
@@ -13693,7 +15005,11 @@
         <v>0.0283</v>
       </c>
       <c r="J333" s="6" t="inlineStr"/>
-      <c r="K333" s="6" t="inlineStr"/>
+      <c r="K333" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L333" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA, BIST KOBİ SANAYİ, BIST KAYSERİ</t>
@@ -13734,7 +15050,11 @@
       <c r="J334" s="4" t="n">
         <v>0.7472</v>
       </c>
-      <c r="K334" s="2" t="inlineStr"/>
+      <c r="K334" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L334" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK</t>
@@ -13775,7 +15095,11 @@
       <c r="J335" s="8" t="n">
         <v>-1.2844</v>
       </c>
-      <c r="K335" s="6" t="inlineStr"/>
+      <c r="K335" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L335" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST İZMİR</t>
@@ -13814,7 +15138,11 @@
       <c r="J336" s="4" t="n">
         <v>-2.2684</v>
       </c>
-      <c r="K336" s="2" t="inlineStr"/>
+      <c r="K336" s="2" t="inlineStr">
+        <is>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
       <c r="L336" s="2" t="inlineStr">
         <is>
           <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
@@ -13855,7 +15183,11 @@
       <c r="J337" s="8" t="n">
         <v>0.1882</v>
       </c>
-      <c r="K337" s="6" t="inlineStr"/>
+      <c r="K337" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L337" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST ANKARA</t>
@@ -13894,7 +15226,11 @@
       <c r="J338" s="4" t="n">
         <v>-53.3143</v>
       </c>
-      <c r="K338" s="2" t="inlineStr"/>
+      <c r="K338" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L338" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
@@ -13933,7 +15269,11 @@
       <c r="J339" s="8" t="n">
         <v>0.9261</v>
       </c>
-      <c r="K339" s="6" t="inlineStr"/>
+      <c r="K339" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L339" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST ANA</t>
@@ -13974,7 +15314,11 @@
       <c r="J340" s="4" t="n">
         <v>4.7457</v>
       </c>
-      <c r="K340" s="2" t="inlineStr"/>
+      <c r="K340" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L340" s="2" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ANA, BIST ANKARA</t>
@@ -14009,7 +15353,11 @@
         <v>-0.2194</v>
       </c>
       <c r="J341" s="6" t="inlineStr"/>
-      <c r="K341" s="6" t="inlineStr"/>
+      <c r="K341" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L341" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST BURSA</t>
@@ -14050,7 +15398,11 @@
       <c r="J342" s="4" t="n">
         <v>-1.2803</v>
       </c>
-      <c r="K342" s="2" t="inlineStr"/>
+      <c r="K342" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L342" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST 50, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST 50-30, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -14089,7 +15441,11 @@
       <c r="J343" s="8" t="n">
         <v>-0.3658</v>
       </c>
-      <c r="K343" s="6" t="inlineStr"/>
+      <c r="K343" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L343" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST KİMYA PETROL PLASTİK, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST 50-30, BIST KOCAELI, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -14130,7 +15486,11 @@
       <c r="J344" s="4" t="n">
         <v>3.6517</v>
       </c>
-      <c r="K344" s="2" t="inlineStr"/>
+      <c r="K344" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L344" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
@@ -14167,7 +15527,11 @@
         <v>-4.0666</v>
       </c>
       <c r="J345" s="6" t="inlineStr"/>
-      <c r="K345" s="6" t="inlineStr"/>
+      <c r="K345" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L345" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
@@ -14206,7 +15570,11 @@
       <c r="J346" s="4" t="n">
         <v>-3.7217</v>
       </c>
-      <c r="K346" s="2" t="inlineStr"/>
+      <c r="K346" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L346" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ</t>
@@ -14243,7 +15611,11 @@
         <v>0.0438</v>
       </c>
       <c r="J347" s="6" t="inlineStr"/>
-      <c r="K347" s="6" t="inlineStr"/>
+      <c r="K347" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L347" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA</t>
@@ -14282,7 +15654,11 @@
       <c r="J348" s="4" t="n">
         <v>-0.2257</v>
       </c>
-      <c r="K348" s="2" t="inlineStr"/>
+      <c r="K348" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L348" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
@@ -14323,7 +15699,11 @@
       <c r="J349" s="8" t="n">
         <v>-0.121</v>
       </c>
-      <c r="K349" s="6" t="inlineStr"/>
+      <c r="K349" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L349" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST ANA, BIST KURUMSAL YÖNETİM</t>
@@ -14362,7 +15742,11 @@
       <c r="J350" s="4" t="n">
         <v>-0.5023</v>
       </c>
-      <c r="K350" s="2" t="inlineStr"/>
+      <c r="K350" s="2" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L350" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
@@ -14401,7 +15785,11 @@
       <c r="J351" s="8" t="n">
         <v>-19.6193</v>
       </c>
-      <c r="K351" s="6" t="inlineStr"/>
+      <c r="K351" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L351" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ</t>
@@ -14438,7 +15826,11 @@
       <c r="J352" s="4" t="n">
         <v>-0.8992</v>
       </c>
-      <c r="K352" s="2" t="inlineStr"/>
+      <c r="K352" s="2" t="inlineStr">
+        <is>
+          <t>Sağlık teknolojisi</t>
+        </is>
+      </c>
       <c r="L352" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KOBİ SANAYİ, BIST MANİSA</t>
@@ -14475,7 +15867,11 @@
         <v>-0.0133</v>
       </c>
       <c r="J353" s="6" t="inlineStr"/>
-      <c r="K353" s="6" t="inlineStr"/>
+      <c r="K353" s="6" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L353" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -14514,7 +15910,11 @@
       <c r="J354" s="4" t="n">
         <v>-0.0043</v>
       </c>
-      <c r="K354" s="2" t="inlineStr"/>
+      <c r="K354" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L354" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
@@ -14551,7 +15951,11 @@
         <v>-0.09710000000000001</v>
       </c>
       <c r="J355" s="6" t="inlineStr"/>
-      <c r="K355" s="6" t="inlineStr"/>
+      <c r="K355" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L355" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
@@ -14592,7 +15996,11 @@
       <c r="J356" s="4" t="n">
         <v>6.3451</v>
       </c>
-      <c r="K356" s="2" t="inlineStr"/>
+      <c r="K356" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L356" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ</t>
@@ -14631,7 +16039,11 @@
       <c r="J357" s="8" t="n">
         <v>-6.582100000000001</v>
       </c>
-      <c r="K357" s="6" t="inlineStr"/>
+      <c r="K357" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L357" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST SPOR, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
@@ -14672,7 +16084,11 @@
       <c r="J358" s="4" t="n">
         <v>0.3834</v>
       </c>
-      <c r="K358" s="2" t="inlineStr"/>
+      <c r="K358" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L358" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST METAL ESYA MAKİNA, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KOCAELI, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
@@ -14711,7 +16127,11 @@
       <c r="J359" s="8" t="n">
         <v>-4.6508</v>
       </c>
-      <c r="K359" s="6" t="inlineStr"/>
+      <c r="K359" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L359" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA, BIST BALIKESİR</t>
@@ -14752,7 +16172,11 @@
       <c r="J360" s="4" t="n">
         <v>-0.2432</v>
       </c>
-      <c r="K360" s="2" t="inlineStr"/>
+      <c r="K360" s="2" t="inlineStr">
+        <is>
+          <t>Perakende satış</t>
+        </is>
+      </c>
       <c r="L360" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST TİCARET, BIST HİZMETLER, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -14791,7 +16215,11 @@
       <c r="J361" s="8" t="n">
         <v>0.5871999999999999</v>
       </c>
-      <c r="K361" s="6" t="inlineStr"/>
+      <c r="K361" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L361" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KOBİ SANAYİ, BIST KONYA</t>
@@ -14830,7 +16258,11 @@
       <c r="J362" s="4" t="n">
         <v>0.7595999999999999</v>
       </c>
-      <c r="K362" s="2" t="inlineStr"/>
+      <c r="K362" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L362" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST ANA, BIST DENİZLİ</t>
@@ -14869,7 +16301,11 @@
       <c r="J363" s="8" t="n">
         <v>-2.3054</v>
       </c>
-      <c r="K363" s="6" t="inlineStr"/>
+      <c r="K363" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L363" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
@@ -14908,7 +16344,11 @@
       <c r="J364" s="4" t="n">
         <v>-1.1923</v>
       </c>
-      <c r="K364" s="2" t="inlineStr"/>
+      <c r="K364" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L364" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST ANA, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
@@ -14949,7 +16389,11 @@
       <c r="J365" s="8" t="n">
         <v>-2.2136</v>
       </c>
-      <c r="K365" s="6" t="inlineStr"/>
+      <c r="K365" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L365" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU, BIST KATILIM 50, BIST KATILIM TEMETTU, BIST KOCAELI</t>
@@ -14990,7 +16434,11 @@
       <c r="J366" s="4" t="n">
         <v>0.2596</v>
       </c>
-      <c r="K366" s="2" t="inlineStr"/>
+      <c r="K366" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L366" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
@@ -15027,7 +16475,11 @@
         <v>-0.0452</v>
       </c>
       <c r="J367" s="6" t="inlineStr"/>
-      <c r="K367" s="6" t="inlineStr"/>
+      <c r="K367" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L367" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM, BIST ANA, BIST ANKARA</t>
@@ -15066,7 +16518,11 @@
       <c r="J368" s="4" t="n">
         <v>0.5029</v>
       </c>
-      <c r="K368" s="2" t="inlineStr"/>
+      <c r="K368" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L368" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -15105,7 +16561,11 @@
       <c r="J369" s="8" t="n">
         <v>-1.9324</v>
       </c>
-      <c r="K369" s="6" t="inlineStr"/>
+      <c r="K369" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L369" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
@@ -15144,7 +16604,11 @@
       <c r="J370" s="4" t="n">
         <v>-22.838</v>
       </c>
-      <c r="K370" s="2" t="inlineStr"/>
+      <c r="K370" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L370" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST BURSA</t>
@@ -15183,7 +16647,11 @@
       <c r="J371" s="8" t="n">
         <v>-2.0753</v>
       </c>
-      <c r="K371" s="6" t="inlineStr"/>
+      <c r="K371" s="6" t="inlineStr">
+        <is>
+          <t>Sağlık teknolojisi</t>
+        </is>
+      </c>
       <c r="L371" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST ANKARA</t>
@@ -15222,7 +16690,11 @@
       <c r="J372" s="4" t="n">
         <v>-2.2369</v>
       </c>
-      <c r="K372" s="2" t="inlineStr"/>
+      <c r="K372" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L372" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST İSTANBUL, BIST ANA</t>
@@ -15263,7 +16735,11 @@
       <c r="J373" s="8" t="n">
         <v>-0.1093</v>
       </c>
-      <c r="K373" s="6" t="inlineStr"/>
+      <c r="K373" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L373" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST YILDIZ, BIST TEMETTU</t>
@@ -15302,7 +16778,11 @@
         <v>0.0318</v>
       </c>
       <c r="J374" s="2" t="inlineStr"/>
-      <c r="K374" s="2" t="inlineStr"/>
+      <c r="K374" s="2" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L374" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
@@ -15343,7 +16823,11 @@
       <c r="J375" s="8" t="n">
         <v>-0.2312</v>
       </c>
-      <c r="K375" s="6" t="inlineStr"/>
+      <c r="K375" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L375" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM TEMETTU, BIST İZMİR, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
@@ -15384,7 +16868,11 @@
       <c r="J376" s="4" t="n">
         <v>0.5552</v>
       </c>
-      <c r="K376" s="2" t="inlineStr"/>
+      <c r="K376" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L376" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST İSTANBUL, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
@@ -15423,7 +16911,11 @@
       <c r="J377" s="8" t="n">
         <v>-3.8066</v>
       </c>
-      <c r="K377" s="6" t="inlineStr"/>
+      <c r="K377" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L377" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST MADENCİLİK, BIST ANA, BIST KOBİ SANAYİ, BIST TEKİRDAĞ</t>
@@ -15464,7 +16956,11 @@
       <c r="J378" s="4" t="n">
         <v>-0.09699999999999999</v>
       </c>
-      <c r="K378" s="2" t="inlineStr"/>
+      <c r="K378" s="2" t="inlineStr">
+        <is>
+          <t>Sağlık hizmetleri</t>
+        </is>
+      </c>
       <c r="L378" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, STOXX Emerging Markets 1500</t>
@@ -15505,7 +17001,11 @@
       <c r="J379" s="8" t="n">
         <v>0.7249</v>
       </c>
-      <c r="K379" s="6" t="inlineStr"/>
+      <c r="K379" s="6" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L379" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -15546,7 +17046,11 @@
       <c r="J380" s="4" t="n">
         <v>-0.9131999999999999</v>
       </c>
-      <c r="K380" s="2" t="inlineStr"/>
+      <c r="K380" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L380" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST TİCARET, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KATILIM 30, BIST 50-30, BIST KATILIM TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -15632,7 +17136,11 @@
       <c r="J382" s="4" t="n">
         <v>0.1229</v>
       </c>
-      <c r="K382" s="2" t="inlineStr"/>
+      <c r="K382" s="2" t="inlineStr">
+        <is>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
       <c r="L382" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANTALYA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
@@ -15671,7 +17179,11 @@
       <c r="J383" s="8" t="n">
         <v>-0.3059</v>
       </c>
-      <c r="K383" s="6" t="inlineStr"/>
+      <c r="K383" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L383" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
@@ -15708,7 +17220,11 @@
         <v>-0.0267</v>
       </c>
       <c r="J384" s="2" t="inlineStr"/>
-      <c r="K384" s="2" t="inlineStr"/>
+      <c r="K384" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L384" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM</t>
@@ -15747,7 +17263,11 @@
         <v>0.0114</v>
       </c>
       <c r="J385" s="6" t="inlineStr"/>
-      <c r="K385" s="6" t="inlineStr"/>
+      <c r="K385" s="6" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L385" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -15784,7 +17304,11 @@
       <c r="J386" s="4" t="n">
         <v>-19.3798</v>
       </c>
-      <c r="K386" s="2" t="inlineStr"/>
+      <c r="K386" s="2" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L386" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -15870,7 +17394,11 @@
       <c r="J388" s="4" t="n">
         <v>-0.1897</v>
       </c>
-      <c r="K388" s="2" t="inlineStr"/>
+      <c r="K388" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L388" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -15907,7 +17435,11 @@
       <c r="J389" s="8" t="n">
         <v>-0.3689</v>
       </c>
-      <c r="K389" s="6" t="inlineStr"/>
+      <c r="K389" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L389" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR</t>
@@ -15946,7 +17478,11 @@
       <c r="J390" s="4" t="n">
         <v>-13.2704</v>
       </c>
-      <c r="K390" s="2" t="inlineStr"/>
+      <c r="K390" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L390" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST YILDIZ, BIST İZMİR</t>
@@ -15987,7 +17523,11 @@
       <c r="J391" s="8" t="n">
         <v>-0.716</v>
       </c>
-      <c r="K391" s="6" t="inlineStr"/>
+      <c r="K391" s="6" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L391" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
@@ -16028,7 +17568,11 @@
       <c r="J392" s="4" t="n">
         <v>0.2616</v>
       </c>
-      <c r="K392" s="2" t="inlineStr"/>
+      <c r="K392" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L392" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST SİGORTA, BIST 50, BIST MALİ, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -16069,7 +17613,11 @@
       <c r="J393" s="8" t="n">
         <v>-0.9066</v>
       </c>
-      <c r="K393" s="6" t="inlineStr"/>
+      <c r="K393" s="6" t="inlineStr">
+        <is>
+          <t>Perakende satış</t>
+        </is>
+      </c>
       <c r="L393" s="6" t="inlineStr">
         <is>
           <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA, BIST BALIKESİR</t>
@@ -16110,7 +17658,11 @@
       <c r="J394" s="4" t="n">
         <v>0.399</v>
       </c>
-      <c r="K394" s="2" t="inlineStr"/>
+      <c r="K394" s="2" t="inlineStr">
+        <is>
+          <t>Perakende satış</t>
+        </is>
+      </c>
       <c r="L394" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST TİCARET, BIST HİZMETLER, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST BANKA DISI LIKIT 10, BIST TEMETTU, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KATILIM 30, BIST KATILIM TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
@@ -16151,7 +17703,11 @@
       <c r="J395" s="8" t="n">
         <v>-2.6291</v>
       </c>
-      <c r="K395" s="6" t="inlineStr"/>
+      <c r="K395" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L395" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST ANKARA</t>
@@ -16190,7 +17746,11 @@
       <c r="J396" s="4" t="n">
         <v>-0.9540000000000001</v>
       </c>
-      <c r="K396" s="2" t="inlineStr"/>
+      <c r="K396" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L396" s="2" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST BALIKESİR</t>
@@ -16227,7 +17787,11 @@
       <c r="J397" s="8" t="n">
         <v>-15.5087</v>
       </c>
-      <c r="K397" s="6" t="inlineStr"/>
+      <c r="K397" s="6" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L397" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -16264,7 +17828,11 @@
       <c r="J398" s="4" t="n">
         <v>-528.8446</v>
       </c>
-      <c r="K398" s="2" t="inlineStr"/>
+      <c r="K398" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L398" s="2" t="inlineStr"/>
       <c r="M398" s="2" t="inlineStr"/>
     </row>
@@ -16301,7 +17869,11 @@
       <c r="J399" s="8" t="n">
         <v>0.7060999999999999</v>
       </c>
-      <c r="K399" s="6" t="inlineStr"/>
+      <c r="K399" s="6" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L399" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
@@ -16342,7 +17914,11 @@
       <c r="J400" s="4" t="n">
         <v>0.0143</v>
       </c>
-      <c r="K400" s="2" t="inlineStr"/>
+      <c r="K400" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L400" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU, BIST İZMİR</t>
@@ -16381,7 +17957,11 @@
         <v>0.2008</v>
       </c>
       <c r="J401" s="6" t="inlineStr"/>
-      <c r="K401" s="6" t="inlineStr"/>
+      <c r="K401" s="6" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L401" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -16420,7 +18000,11 @@
         <v>0.0209</v>
       </c>
       <c r="J402" s="2" t="inlineStr"/>
-      <c r="K402" s="2" t="inlineStr"/>
+      <c r="K402" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L402" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST MADENCİLİK, BIST HALKA ARZ, BIST ANA, ADANA</t>
@@ -16461,7 +18045,11 @@
       <c r="J403" s="8" t="n">
         <v>-0.9989</v>
       </c>
-      <c r="K403" s="6" t="inlineStr"/>
+      <c r="K403" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L403" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST 50, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10, STOXX Emerging Markets 1500</t>
@@ -16500,7 +18088,11 @@
       <c r="J404" s="4" t="n">
         <v>1.7569</v>
       </c>
-      <c r="K404" s="2" t="inlineStr"/>
+      <c r="K404" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L404" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
@@ -16541,7 +18133,11 @@
       <c r="J405" s="8" t="n">
         <v>0.07490000000000001</v>
       </c>
-      <c r="K405" s="6" t="inlineStr"/>
+      <c r="K405" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L405" s="6" t="inlineStr"/>
       <c r="M405" s="6" t="inlineStr"/>
     </row>
@@ -16578,7 +18174,11 @@
       <c r="J406" s="4" t="n">
         <v>1.0199</v>
       </c>
-      <c r="K406" s="2" t="inlineStr"/>
+      <c r="K406" s="2" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L406" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
@@ -16615,7 +18215,11 @@
         <v>-0.0027</v>
       </c>
       <c r="J407" s="6" t="inlineStr"/>
-      <c r="K407" s="6" t="inlineStr"/>
+      <c r="K407" s="6" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L407" s="6" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -16656,7 +18260,11 @@
       <c r="J408" s="4" t="n">
         <v>0.6006</v>
       </c>
-      <c r="K408" s="2" t="inlineStr"/>
+      <c r="K408" s="2" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L408" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST ULASTIRMA, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KATILIM TEMETTU, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
@@ -16695,7 +18303,11 @@
       <c r="J409" s="8" t="n">
         <v>2.4746</v>
       </c>
-      <c r="K409" s="6" t="inlineStr"/>
+      <c r="K409" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L409" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KOCAELI, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
@@ -16736,7 +18348,11 @@
       <c r="J410" s="4" t="n">
         <v>-0.9328</v>
       </c>
-      <c r="K410" s="2" t="inlineStr"/>
+      <c r="K410" s="2" t="inlineStr">
+        <is>
+          <t>Perakende satış</t>
+        </is>
+      </c>
       <c r="L410" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
@@ -16773,7 +18389,11 @@
       <c r="J411" s="8" t="n">
         <v>-193.4008</v>
       </c>
-      <c r="K411" s="6" t="inlineStr"/>
+      <c r="K411" s="6" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L411" s="6" t="inlineStr"/>
       <c r="M411" s="6" t="inlineStr"/>
     </row>
@@ -16808,7 +18428,11 @@
         <v>0.2337</v>
       </c>
       <c r="J412" s="2" t="inlineStr"/>
-      <c r="K412" s="2" t="inlineStr"/>
+      <c r="K412" s="2" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L412" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -16845,7 +18469,11 @@
         <v>-0.09390000000000001</v>
       </c>
       <c r="J413" s="6" t="inlineStr"/>
-      <c r="K413" s="6" t="inlineStr"/>
+      <c r="K413" s="6" t="inlineStr">
+        <is>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
       <c r="L413" s="6" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KOCAELI</t>
@@ -16884,7 +18512,11 @@
       <c r="J414" s="4" t="n">
         <v>-1.6177</v>
       </c>
-      <c r="K414" s="2" t="inlineStr"/>
+      <c r="K414" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L414" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST ANA, BIST KOCAELI</t>
@@ -16923,7 +18555,11 @@
       <c r="J415" s="8" t="n">
         <v>0.4473</v>
       </c>
-      <c r="K415" s="6" t="inlineStr"/>
+      <c r="K415" s="6" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L415" s="6" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA</t>
@@ -16962,7 +18598,11 @@
         <v>0.0177</v>
       </c>
       <c r="J416" s="2" t="inlineStr"/>
-      <c r="K416" s="2" t="inlineStr"/>
+      <c r="K416" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L416" s="2" t="inlineStr">
         <is>
           <t>BIST BANKA, BIST TUM-100, BIST TÜM, BIST MALİ, BIST ANA</t>
@@ -17003,7 +18643,11 @@
       <c r="J417" s="8" t="n">
         <v>-1.1669</v>
       </c>
-      <c r="K417" s="6" t="inlineStr"/>
+      <c r="K417" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L417" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST MADENCİLİK, BIST 50, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST BANKA DISI LIKIT 10, BIST İZMİR, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
@@ -17044,7 +18688,11 @@
       <c r="J418" s="4" t="n">
         <v>-0.7215</v>
       </c>
-      <c r="K418" s="2" t="inlineStr"/>
+      <c r="K418" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L418" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
@@ -17085,7 +18733,11 @@
       <c r="J419" s="8" t="n">
         <v>-0.7884</v>
       </c>
-      <c r="K419" s="6" t="inlineStr"/>
+      <c r="K419" s="6" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L419" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -17126,7 +18778,11 @@
       <c r="J420" s="4" t="n">
         <v>-0.5128</v>
       </c>
-      <c r="K420" s="2" t="inlineStr"/>
+      <c r="K420" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L420" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST İZMİR</t>
@@ -17167,7 +18823,11 @@
       <c r="J421" s="8" t="n">
         <v>-1.5523</v>
       </c>
-      <c r="K421" s="6" t="inlineStr"/>
+      <c r="K421" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L421" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
@@ -17208,7 +18868,11 @@
       <c r="J422" s="4" t="n">
         <v>-0.1442</v>
       </c>
-      <c r="K422" s="2" t="inlineStr"/>
+      <c r="K422" s="2" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L422" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
@@ -17249,7 +18913,11 @@
       <c r="J423" s="8" t="n">
         <v>6.844600000000001</v>
       </c>
-      <c r="K423" s="6" t="inlineStr"/>
+      <c r="K423" s="6" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L423" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
@@ -17286,7 +18954,11 @@
         <v>-0.0482</v>
       </c>
       <c r="J424" s="2" t="inlineStr"/>
-      <c r="K424" s="2" t="inlineStr"/>
+      <c r="K424" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L424" s="2" t="inlineStr"/>
       <c r="M424" s="2" t="inlineStr"/>
     </row>
@@ -17321,7 +18993,11 @@
       <c r="J425" s="8" t="n">
         <v>-4.0218</v>
       </c>
-      <c r="K425" s="6" t="inlineStr"/>
+      <c r="K425" s="6" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L425" s="6" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
@@ -17362,7 +19038,11 @@
       <c r="J426" s="4" t="n">
         <v>-1.0812</v>
       </c>
-      <c r="K426" s="2" t="inlineStr"/>
+      <c r="K426" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L426" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
@@ -17399,7 +19079,11 @@
         <v>0.0377</v>
       </c>
       <c r="J427" s="6" t="inlineStr"/>
-      <c r="K427" s="6" t="inlineStr"/>
+      <c r="K427" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L427" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ</t>
@@ -17438,7 +19122,11 @@
       <c r="J428" s="4" t="n">
         <v>8.039199999999999</v>
       </c>
-      <c r="K428" s="2" t="inlineStr"/>
+      <c r="K428" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L428" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST İSTANBUL, BIST ANA</t>
@@ -17477,7 +19165,11 @@
       <c r="J429" s="8" t="n">
         <v>0.1053</v>
       </c>
-      <c r="K429" s="6" t="inlineStr"/>
+      <c r="K429" s="6" t="inlineStr">
+        <is>
+          <t>Perakende satış</t>
+        </is>
+      </c>
       <c r="L429" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -17516,7 +19208,11 @@
       <c r="J430" s="4" t="n">
         <v>-0.45</v>
       </c>
-      <c r="K430" s="2" t="inlineStr"/>
+      <c r="K430" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L430" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST KOBİ SANAYİ</t>
@@ -17555,7 +19251,11 @@
       <c r="J431" s="8" t="n">
         <v>-2.2418</v>
       </c>
-      <c r="K431" s="6" t="inlineStr"/>
+      <c r="K431" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L431" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA, BIST ANTALYA</t>
@@ -17594,7 +19294,11 @@
       <c r="J432" s="4" t="n">
         <v>-44.8491</v>
       </c>
-      <c r="K432" s="2" t="inlineStr"/>
+      <c r="K432" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L432" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST MANİSA</t>
@@ -17635,7 +19339,11 @@
       <c r="J433" s="8" t="n">
         <v>2.7171</v>
       </c>
-      <c r="K433" s="6" t="inlineStr"/>
+      <c r="K433" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L433" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST HALKA ARZ, BIST YILDIZ, BIST BURSA</t>
@@ -17674,7 +19382,11 @@
         <v>-0.0039</v>
       </c>
       <c r="J434" s="2" t="inlineStr"/>
-      <c r="K434" s="2" t="inlineStr"/>
+      <c r="K434" s="2" t="inlineStr">
+        <is>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
       <c r="L434" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TEKNOLOJİ, BIST HALKA ARZ, BIST İSTANBUL, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM 30, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
@@ -17715,7 +19427,11 @@
       <c r="J435" s="8" t="n">
         <v>-2.8727</v>
       </c>
-      <c r="K435" s="6" t="inlineStr"/>
+      <c r="K435" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L435" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST YILDIZ, BIST ANKARA</t>
@@ -17756,7 +19472,11 @@
       <c r="J436" s="4" t="n">
         <v>0.2386</v>
       </c>
-      <c r="K436" s="2" t="inlineStr"/>
+      <c r="K436" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L436" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST SİGORTA, BIST MALİ, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK</t>
@@ -17797,7 +19517,11 @@
       <c r="J437" s="8" t="n">
         <v>5.585199999999999</v>
       </c>
-      <c r="K437" s="6" t="inlineStr"/>
+      <c r="K437" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L437" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST ANA</t>
@@ -17838,7 +19562,11 @@
       <c r="J438" s="4" t="n">
         <v>1.037</v>
       </c>
-      <c r="K438" s="2" t="inlineStr"/>
+      <c r="K438" s="2" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L438" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50</t>
@@ -17877,7 +19605,11 @@
       <c r="J439" s="8" t="n">
         <v>-4.4402</v>
       </c>
-      <c r="K439" s="6" t="inlineStr"/>
+      <c r="K439" s="6" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L439" s="6" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST İZMİR</t>
@@ -17916,7 +19648,11 @@
       <c r="J440" s="4" t="n">
         <v>0.5216</v>
       </c>
-      <c r="K440" s="2" t="inlineStr"/>
+      <c r="K440" s="2" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L440" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST 50, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST 50-30, BIST ANKARA, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -17957,7 +19693,11 @@
       <c r="J441" s="8" t="n">
         <v>0.8172</v>
       </c>
-      <c r="K441" s="6" t="inlineStr"/>
+      <c r="K441" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L441" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA</t>
@@ -17996,7 +19736,11 @@
       <c r="J442" s="4" t="n">
         <v>-0.7101999999999999</v>
       </c>
-      <c r="K442" s="2" t="inlineStr"/>
+      <c r="K442" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L442" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST YILDIZ, BIST İZMİR</t>
@@ -18037,7 +19781,11 @@
       <c r="J443" s="8" t="n">
         <v>-0.4521</v>
       </c>
-      <c r="K443" s="6" t="inlineStr"/>
+      <c r="K443" s="6" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L443" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM TEMETTU, BIST KOCAELI, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
@@ -18076,7 +19824,11 @@
         <v>0.0352</v>
       </c>
       <c r="J444" s="2" t="inlineStr"/>
-      <c r="K444" s="2" t="inlineStr"/>
+      <c r="K444" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L444" s="2" t="inlineStr"/>
       <c r="M444" s="2" t="inlineStr"/>
     </row>
@@ -18113,7 +19865,11 @@
       <c r="J445" s="8" t="n">
         <v>-0.4549</v>
       </c>
-      <c r="K445" s="6" t="inlineStr"/>
+      <c r="K445" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L445" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST SİGORTA, BIST MALİ, BIST ANA</t>
@@ -18152,7 +19908,11 @@
       <c r="J446" s="4" t="n">
         <v>-7.241000000000001</v>
       </c>
-      <c r="K446" s="2" t="inlineStr"/>
+      <c r="K446" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L446" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
@@ -18191,7 +19951,11 @@
       <c r="J447" s="8" t="n">
         <v>-2.2771</v>
       </c>
-      <c r="K447" s="6" t="inlineStr"/>
+      <c r="K447" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L447" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA, BIST ANKARA</t>
@@ -18232,7 +19996,11 @@
       <c r="J448" s="4" t="n">
         <v>-0.3022</v>
       </c>
-      <c r="K448" s="2" t="inlineStr"/>
+      <c r="K448" s="2" t="inlineStr">
+        <is>
+          <t>Sağlık teknolojisi</t>
+        </is>
+      </c>
       <c r="L448" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU, BIST KATILIM 50, BIST KATILIM 30, BIST KATILIM TEMETTU, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
@@ -18271,7 +20039,11 @@
       <c r="J449" s="8" t="n">
         <v>-0.3881</v>
       </c>
-      <c r="K449" s="6" t="inlineStr"/>
+      <c r="K449" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L449" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
@@ -18310,7 +20082,11 @@
       <c r="J450" s="4" t="n">
         <v>-8.8185</v>
       </c>
-      <c r="K450" s="2" t="inlineStr"/>
+      <c r="K450" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L450" s="2" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA</t>
@@ -18351,7 +20127,11 @@
       <c r="J451" s="8" t="n">
         <v>0.1278</v>
       </c>
-      <c r="K451" s="6" t="inlineStr"/>
+      <c r="K451" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L451" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ANA, BIST TEMETTU</t>
@@ -18392,7 +20172,11 @@
       <c r="J452" s="4" t="n">
         <v>0.2955</v>
       </c>
-      <c r="K452" s="2" t="inlineStr"/>
+      <c r="K452" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L452" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
@@ -18431,7 +20215,11 @@
         <v>0.0042</v>
       </c>
       <c r="J453" s="6" t="inlineStr"/>
-      <c r="K453" s="6" t="inlineStr"/>
+      <c r="K453" s="6" t="inlineStr">
+        <is>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
       <c r="L453" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST İSTANBUL, BIST ANA, BIST KOBİ SANAYİ</t>
@@ -18468,7 +20256,11 @@
       <c r="J454" s="4" t="n">
         <v>-3.512</v>
       </c>
-      <c r="K454" s="2" t="inlineStr"/>
+      <c r="K454" s="2" t="inlineStr">
+        <is>
+          <t>Çeşitli Hizmetler</t>
+        </is>
+      </c>
       <c r="L454" s="2" t="inlineStr"/>
       <c r="M454" s="2" t="inlineStr"/>
     </row>
@@ -18505,7 +20297,11 @@
       <c r="J455" s="8" t="n">
         <v>-0.0185</v>
       </c>
-      <c r="K455" s="6" t="inlineStr"/>
+      <c r="K455" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L455" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST SİGORTA, BIST MALİ, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK</t>
@@ -18546,7 +20342,11 @@
       <c r="J456" s="4" t="n">
         <v>-0.1008</v>
       </c>
-      <c r="K456" s="2" t="inlineStr"/>
+      <c r="K456" s="2" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L456" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
@@ -18587,7 +20387,11 @@
       <c r="J457" s="8" t="n">
         <v>0.2085</v>
       </c>
-      <c r="K457" s="6" t="inlineStr"/>
+      <c r="K457" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L457" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST ANA, BIST SÜRDÜRÜLEBİLİRLİK</t>
@@ -18626,7 +20430,11 @@
       <c r="J458" s="4" t="n">
         <v>-1.7771</v>
       </c>
-      <c r="K458" s="2" t="inlineStr"/>
+      <c r="K458" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L458" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ</t>
@@ -18665,7 +20473,11 @@
       <c r="J459" s="8" t="n">
         <v>-0.3973</v>
       </c>
-      <c r="K459" s="6" t="inlineStr"/>
+      <c r="K459" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L459" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HALKA ARZ, BIST HİZMETLER, BIST YILDIZ</t>
@@ -18704,7 +20516,11 @@
       <c r="J460" s="4" t="n">
         <v>-1.2976</v>
       </c>
-      <c r="K460" s="2" t="inlineStr"/>
+      <c r="K460" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L460" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST ANA, BIST BURSA</t>
@@ -18743,7 +20559,11 @@
       <c r="J461" s="8" t="n">
         <v>-3.2624</v>
       </c>
-      <c r="K461" s="6" t="inlineStr"/>
+      <c r="K461" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L461" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST İSTANBUL, BIST ANA</t>
@@ -18780,7 +20600,11 @@
       <c r="J462" s="4" t="n">
         <v>-2.3315</v>
       </c>
-      <c r="K462" s="2" t="inlineStr"/>
+      <c r="K462" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L462" s="2" t="inlineStr">
         <is>
           <t>BIST MENKUL KIYM YO</t>
@@ -18817,7 +20641,11 @@
       <c r="J463" s="8" t="n">
         <v>0.9449</v>
       </c>
-      <c r="K463" s="6" t="inlineStr"/>
+      <c r="K463" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L463" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ</t>
@@ -18856,7 +20684,11 @@
       <c r="J464" s="4" t="n">
         <v>-0.2029</v>
       </c>
-      <c r="K464" s="2" t="inlineStr"/>
+      <c r="K464" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L464" s="2" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
@@ -18895,7 +20727,11 @@
         <v>0.2536</v>
       </c>
       <c r="J465" s="6" t="inlineStr"/>
-      <c r="K465" s="6" t="inlineStr"/>
+      <c r="K465" s="6" t="inlineStr">
+        <is>
+          <t>İletişim</t>
+        </is>
+      </c>
       <c r="L465" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -18932,7 +20768,11 @@
       <c r="J466" s="4" t="n">
         <v>0.3441</v>
       </c>
-      <c r="K466" s="2" t="inlineStr"/>
+      <c r="K466" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L466" s="2" t="inlineStr"/>
       <c r="M466" s="2" t="inlineStr"/>
     </row>
@@ -18967,7 +20807,11 @@
       <c r="J467" s="8" t="n">
         <v>-14.5611</v>
       </c>
-      <c r="K467" s="6" t="inlineStr"/>
+      <c r="K467" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L467" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -19008,7 +20852,11 @@
       <c r="J468" s="4" t="n">
         <v>-0.0176</v>
       </c>
-      <c r="K468" s="2" t="inlineStr"/>
+      <c r="K468" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L468" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST YILDIZ, BIST KONYA</t>
@@ -19049,7 +20897,11 @@
       <c r="J469" s="8" t="n">
         <v>-0.4052</v>
       </c>
-      <c r="K469" s="6" t="inlineStr"/>
+      <c r="K469" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L469" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM</t>
@@ -19088,7 +20940,11 @@
       <c r="J470" s="4" t="n">
         <v>0.6631</v>
       </c>
-      <c r="K470" s="2" t="inlineStr"/>
+      <c r="K470" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L470" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
@@ -19127,7 +20983,11 @@
       <c r="J471" s="8" t="n">
         <v>-105.8416</v>
       </c>
-      <c r="K471" s="6" t="inlineStr"/>
+      <c r="K471" s="6" t="inlineStr">
+        <is>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
       <c r="L471" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST ANA, BIST KOBİ SANAYİ</t>
@@ -19168,7 +21028,11 @@
       <c r="J472" s="4" t="n">
         <v>0.2476</v>
       </c>
-      <c r="K472" s="2" t="inlineStr"/>
+      <c r="K472" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L472" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İZMİR</t>
@@ -19207,7 +21071,11 @@
         <v>0.68</v>
       </c>
       <c r="J473" s="6" t="inlineStr"/>
-      <c r="K473" s="6" t="inlineStr"/>
+      <c r="K473" s="6" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L473" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST KOBİ SANAYİ</t>
@@ -19248,7 +21116,11 @@
       <c r="J474" s="4" t="n">
         <v>-0.06860000000000001</v>
       </c>
-      <c r="K474" s="2" t="inlineStr"/>
+      <c r="K474" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L474" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
@@ -19289,7 +21161,11 @@
       <c r="J475" s="8" t="n">
         <v>1.3847</v>
       </c>
-      <c r="K475" s="6" t="inlineStr"/>
+      <c r="K475" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L475" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST İSTANBUL, BIST ANA</t>
@@ -19328,7 +21204,11 @@
       <c r="J476" s="4" t="n">
         <v>-0.4155</v>
       </c>
-      <c r="K476" s="2" t="inlineStr"/>
+      <c r="K476" s="2" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L476" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA</t>
@@ -19367,7 +21247,11 @@
       <c r="J477" s="8" t="n">
         <v>0.6581999999999999</v>
       </c>
-      <c r="K477" s="6" t="inlineStr"/>
+      <c r="K477" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L477" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM 30, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST AYDIN, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
@@ -19408,7 +21292,11 @@
       <c r="J478" s="4" t="n">
         <v>-3.1045</v>
       </c>
-      <c r="K478" s="2" t="inlineStr"/>
+      <c r="K478" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L478" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST TEKİRDAĞ</t>
@@ -19447,7 +21335,11 @@
         <v>0.0017</v>
       </c>
       <c r="J479" s="6" t="inlineStr"/>
-      <c r="K479" s="6" t="inlineStr"/>
+      <c r="K479" s="6" t="inlineStr">
+        <is>
+          <t>Sağlık hizmetleri</t>
+        </is>
+      </c>
       <c r="L479" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
@@ -19486,7 +21378,11 @@
       <c r="J480" s="4" t="n">
         <v>0.9714</v>
       </c>
-      <c r="K480" s="2" t="inlineStr"/>
+      <c r="K480" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L480" s="2" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST KAYSERİ</t>
@@ -19525,7 +21421,11 @@
       <c r="J481" s="8" t="n">
         <v>0.7116</v>
       </c>
-      <c r="K481" s="6" t="inlineStr"/>
+      <c r="K481" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L481" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -19566,7 +21466,11 @@
       <c r="J482" s="4" t="n">
         <v>2.6213</v>
       </c>
-      <c r="K482" s="2" t="inlineStr"/>
+      <c r="K482" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L482" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, STOXX Emerging Markets 1500</t>
@@ -19607,7 +21511,11 @@
       <c r="J483" s="8" t="n">
         <v>-0.7998000000000001</v>
       </c>
-      <c r="K483" s="6" t="inlineStr"/>
+      <c r="K483" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L483" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST ANA, STOXX Emerging Markets 1500</t>
@@ -19644,7 +21552,11 @@
         <v>-0.0561</v>
       </c>
       <c r="J484" s="2" t="inlineStr"/>
-      <c r="K484" s="2" t="inlineStr"/>
+      <c r="K484" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L484" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA</t>
@@ -19685,7 +21597,11 @@
       <c r="J485" s="8" t="n">
         <v>-0.009399999999999999</v>
       </c>
-      <c r="K485" s="6" t="inlineStr"/>
+      <c r="K485" s="6" t="inlineStr">
+        <is>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
       <c r="L485" s="6" t="inlineStr">
         <is>
           <t>BIST ULASTIRMA, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ, BIST TEMETTU</t>
@@ -19726,7 +21642,11 @@
       <c r="J486" s="4" t="n">
         <v>-0.6491</v>
       </c>
-      <c r="K486" s="2" t="inlineStr"/>
+      <c r="K486" s="2" t="inlineStr">
+        <is>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
       <c r="L486" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
@@ -19765,7 +21685,11 @@
       <c r="J487" s="8" t="n">
         <v>-2.4711</v>
       </c>
-      <c r="K487" s="6" t="inlineStr"/>
+      <c r="K487" s="6" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L487" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -19804,7 +21728,11 @@
       <c r="J488" s="4" t="n">
         <v>-10.4842</v>
       </c>
-      <c r="K488" s="2" t="inlineStr"/>
+      <c r="K488" s="2" t="inlineStr">
+        <is>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
       <c r="L488" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
@@ -19843,7 +21771,11 @@
       <c r="J489" s="8" t="n">
         <v>-1.9167</v>
       </c>
-      <c r="K489" s="6" t="inlineStr"/>
+      <c r="K489" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L489" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
@@ -19884,7 +21816,11 @@
       <c r="J490" s="4" t="n">
         <v>0.1363</v>
       </c>
-      <c r="K490" s="2" t="inlineStr"/>
+      <c r="K490" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L490" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KAYSERİ</t>
@@ -19923,7 +21859,11 @@
       <c r="J491" s="8" t="n">
         <v>-12.5699</v>
       </c>
-      <c r="K491" s="6" t="inlineStr"/>
+      <c r="K491" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L491" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA</t>
@@ -19962,7 +21902,11 @@
         <v>-0.0005999999999999999</v>
       </c>
       <c r="J492" s="2" t="inlineStr"/>
-      <c r="K492" s="2" t="inlineStr"/>
+      <c r="K492" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L492" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST GIDA ICECEK, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
@@ -20001,7 +21945,11 @@
       <c r="J493" s="8" t="n">
         <v>-2.6951</v>
       </c>
-      <c r="K493" s="6" t="inlineStr"/>
+      <c r="K493" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L493" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST ANA, BIST İZMİR</t>
@@ -20042,7 +21990,11 @@
       <c r="J494" s="4" t="n">
         <v>-0.9906</v>
       </c>
-      <c r="K494" s="2" t="inlineStr"/>
+      <c r="K494" s="2" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L494" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
@@ -20083,7 +22035,11 @@
       <c r="J495" s="8" t="n">
         <v>-0.8634000000000001</v>
       </c>
-      <c r="K495" s="6" t="inlineStr"/>
+      <c r="K495" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L495" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST MADENCİLİK, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST BURSA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
@@ -20122,7 +22078,11 @@
       <c r="J496" s="4" t="n">
         <v>-10.8224</v>
       </c>
-      <c r="K496" s="2" t="inlineStr"/>
+      <c r="K496" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L496" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA, BIST TEKİRDAĞ</t>
@@ -20161,7 +22121,11 @@
       <c r="J497" s="8" t="n">
         <v>0.0757</v>
       </c>
-      <c r="K497" s="6" t="inlineStr"/>
+      <c r="K497" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L497" s="6" t="inlineStr">
         <is>
           <t>BIST MENKUL KIYM YO</t>
@@ -20202,7 +22166,11 @@
       <c r="J498" s="4" t="n">
         <v>-0.5074000000000001</v>
       </c>
-      <c r="K498" s="2" t="inlineStr"/>
+      <c r="K498" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L498" s="2" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST YILDIZ</t>
@@ -20241,7 +22209,11 @@
       <c r="J499" s="8" t="n">
         <v>-7.040900000000001</v>
       </c>
-      <c r="K499" s="6" t="inlineStr"/>
+      <c r="K499" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L499" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST ANA, BIST KOBİ SANAYİ</t>
@@ -20282,7 +22254,11 @@
       <c r="J500" s="4" t="n">
         <v>-0.4614</v>
       </c>
-      <c r="K500" s="2" t="inlineStr"/>
+      <c r="K500" s="2" t="inlineStr">
+        <is>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
       <c r="L500" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST TEMETTU</t>
@@ -20323,7 +22299,11 @@
       <c r="J501" s="8" t="n">
         <v>-0.336</v>
       </c>
-      <c r="K501" s="6" t="inlineStr"/>
+      <c r="K501" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L501" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST KİMYA PETROL PLASTİK, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25</t>
@@ -20362,7 +22342,11 @@
       <c r="J502" s="4" t="n">
         <v>-2.0132</v>
       </c>
-      <c r="K502" s="2" t="inlineStr"/>
+      <c r="K502" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L502" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM, BIST ANA</t>
@@ -20401,7 +22385,11 @@
       <c r="J503" s="8" t="n">
         <v>-1.3835</v>
       </c>
-      <c r="K503" s="6" t="inlineStr"/>
+      <c r="K503" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L503" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST METAL ESYA MAKİNA, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
@@ -20440,7 +22428,11 @@
         <v>0.0366</v>
       </c>
       <c r="J504" s="2" t="inlineStr"/>
-      <c r="K504" s="2" t="inlineStr"/>
+      <c r="K504" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L504" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST TEMETTU, BIST KOBİ SANAYİ, BIST BALIKESİR</t>
@@ -20479,7 +22471,11 @@
       <c r="J505" s="8" t="n">
         <v>0.0278</v>
       </c>
-      <c r="K505" s="6" t="inlineStr"/>
+      <c r="K505" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L505" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
@@ -20518,7 +22514,11 @@
       <c r="J506" s="4" t="n">
         <v>-3.178</v>
       </c>
-      <c r="K506" s="2" t="inlineStr"/>
+      <c r="K506" s="2" t="inlineStr">
+        <is>
+          <t>Perakende satış</t>
+        </is>
+      </c>
       <c r="L506" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST SÜRDÜRÜLEBİLİRLİK, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
@@ -20559,7 +22559,11 @@
       <c r="J507" s="8" t="n">
         <v>-0.4854</v>
       </c>
-      <c r="K507" s="6" t="inlineStr"/>
+      <c r="K507" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L507" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA, BIST KOCAELI</t>
@@ -20598,7 +22602,11 @@
         <v>0.1656</v>
       </c>
       <c r="J508" s="2" t="inlineStr"/>
-      <c r="K508" s="2" t="inlineStr"/>
+      <c r="K508" s="2" t="inlineStr">
+        <is>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
       <c r="L508" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -20639,7 +22647,11 @@
       <c r="J509" s="8" t="n">
         <v>-0.9779000000000001</v>
       </c>
-      <c r="K509" s="6" t="inlineStr"/>
+      <c r="K509" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L509" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
@@ -20678,7 +22690,11 @@
       <c r="J510" s="4" t="n">
         <v>-3.335</v>
       </c>
-      <c r="K510" s="2" t="inlineStr"/>
+      <c r="K510" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L510" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
@@ -20715,7 +22731,11 @@
       <c r="J511" s="8" t="n">
         <v>-0.9567</v>
       </c>
-      <c r="K511" s="6" t="inlineStr"/>
+      <c r="K511" s="6" t="inlineStr">
+        <is>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
       <c r="L511" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
@@ -20754,7 +22774,11 @@
       <c r="J512" s="4" t="n">
         <v>0.507</v>
       </c>
-      <c r="K512" s="2" t="inlineStr"/>
+      <c r="K512" s="2" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L512" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST KATILIM 50, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
@@ -20795,7 +22819,11 @@
       <c r="J513" s="8" t="n">
         <v>2.8984</v>
       </c>
-      <c r="K513" s="6" t="inlineStr"/>
+      <c r="K513" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L513" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST KURUMSAL YÖNETİM</t>
@@ -20834,7 +22862,11 @@
       <c r="J514" s="4" t="n">
         <v>1.1582</v>
       </c>
-      <c r="K514" s="2" t="inlineStr"/>
+      <c r="K514" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L514" s="2" t="inlineStr">
         <is>
           <t>BIST MENKUL KIYM YO</t>
@@ -20871,7 +22903,11 @@
         <v>-1.089</v>
       </c>
       <c r="J515" s="6" t="inlineStr"/>
-      <c r="K515" s="6" t="inlineStr"/>
+      <c r="K515" s="6" t="inlineStr">
+        <is>
+          <t>Perakende satış</t>
+        </is>
+      </c>
       <c r="L515" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA, BIST SÜRDÜRÜLEBİLİRLİK</t>
@@ -20912,7 +22948,11 @@
       <c r="J516" s="4" t="n">
         <v>-0.6973</v>
       </c>
-      <c r="K516" s="2" t="inlineStr"/>
+      <c r="K516" s="2" t="inlineStr">
+        <is>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
       <c r="L516" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TEKNOLOJİ, BIST 50, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST BANKA DISI LIKIT 10, BIST TEMETTU, BIST KATILIM 50, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST KATILIM 30, BIST KATILIM TEMETTU, BIST ANKARA, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
@@ -20949,7 +22989,11 @@
         <v>-0.2148</v>
       </c>
       <c r="J517" s="6" t="inlineStr"/>
-      <c r="K517" s="6" t="inlineStr"/>
+      <c r="K517" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L517" s="6" t="inlineStr"/>
       <c r="M517" s="6" t="inlineStr"/>
     </row>
@@ -20982,7 +23026,11 @@
       <c r="J518" s="4" t="n">
         <v>-0.6470999999999999</v>
       </c>
-      <c r="K518" s="2" t="inlineStr"/>
+      <c r="K518" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L518" s="2" t="inlineStr">
         <is>
           <t>BIST MENKUL KIYM YO</t>
@@ -21021,7 +23069,11 @@
       <c r="J519" s="8" t="n">
         <v>-7.7801</v>
       </c>
-      <c r="K519" s="6" t="inlineStr"/>
+      <c r="K519" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L519" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST BALIKESİR</t>
@@ -21060,7 +23112,11 @@
       <c r="J520" s="4" t="n">
         <v>-5.0791</v>
       </c>
-      <c r="K520" s="2" t="inlineStr"/>
+      <c r="K520" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L520" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
@@ -21099,7 +23155,11 @@
       <c r="J521" s="8" t="n">
         <v>0.8837999999999999</v>
       </c>
-      <c r="K521" s="6" t="inlineStr"/>
+      <c r="K521" s="6" t="inlineStr">
+        <is>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
       <c r="L521" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
@@ -21138,7 +23198,11 @@
       <c r="J522" s="4" t="n">
         <v>0.8517</v>
       </c>
-      <c r="K522" s="2" t="inlineStr"/>
+      <c r="K522" s="2" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L522" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST TEMETTU</t>
@@ -21179,7 +23243,11 @@
       <c r="J523" s="8" t="n">
         <v>0.1497</v>
       </c>
-      <c r="K523" s="6" t="inlineStr"/>
+      <c r="K523" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L523" s="6" t="inlineStr"/>
       <c r="M523" s="6" t="inlineStr"/>
     </row>
@@ -21214,7 +23282,11 @@
       <c r="J524" s="4" t="n">
         <v>-5.4758</v>
       </c>
-      <c r="K524" s="2" t="inlineStr"/>
+      <c r="K524" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L524" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İZMİR</t>
@@ -21253,7 +23325,11 @@
       <c r="J525" s="8" t="n">
         <v>-12.8747</v>
       </c>
-      <c r="K525" s="6" t="inlineStr"/>
+      <c r="K525" s="6" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L525" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
@@ -21292,7 +23368,11 @@
       <c r="J526" s="4" t="n">
         <v>0.1259</v>
       </c>
-      <c r="K526" s="2" t="inlineStr"/>
+      <c r="K526" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L526" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST KOBİ SANAYİ, BIST KOCAELI</t>
@@ -21333,7 +23413,11 @@
       <c r="J527" s="8" t="n">
         <v>546.9397</v>
       </c>
-      <c r="K527" s="6" t="inlineStr"/>
+      <c r="K527" s="6" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L527" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -21372,7 +23456,11 @@
       <c r="J528" s="4" t="n">
         <v>-0.586</v>
       </c>
-      <c r="K528" s="2" t="inlineStr"/>
+      <c r="K528" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L528" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST ANA, BIST KAYSERİ</t>
@@ -21413,7 +23501,11 @@
       <c r="J529" s="8" t="n">
         <v>0.0601</v>
       </c>
-      <c r="K529" s="6" t="inlineStr"/>
+      <c r="K529" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L529" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST 50, BIST METAL ESYA MAKİNA, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU, BIST KURUMSAL YÖNETİM, BIST ANKARA, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
@@ -21452,7 +23544,11 @@
         <v>0.794</v>
       </c>
       <c r="J530" s="2" t="inlineStr"/>
-      <c r="K530" s="2" t="inlineStr"/>
+      <c r="K530" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L530" s="2" t="inlineStr">
         <is>
           <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST ANA</t>
@@ -21491,7 +23587,11 @@
       <c r="J531" s="8" t="n">
         <v>-0.6662</v>
       </c>
-      <c r="K531" s="6" t="inlineStr"/>
+      <c r="K531" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L531" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST ANA, BIST İZMİR</t>
@@ -21530,7 +23630,11 @@
       <c r="J532" s="4" t="n">
         <v>0.9349</v>
       </c>
-      <c r="K532" s="2" t="inlineStr"/>
+      <c r="K532" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L532" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST ANA, BIST KURUMSAL YÖNETİM, BIST BURSA</t>
@@ -21569,7 +23673,11 @@
       <c r="J533" s="8" t="n">
         <v>-6.502000000000001</v>
       </c>
-      <c r="K533" s="6" t="inlineStr"/>
+      <c r="K533" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L533" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA</t>
@@ -21608,7 +23716,11 @@
         <v>0.2387</v>
       </c>
       <c r="J534" s="2" t="inlineStr"/>
-      <c r="K534" s="2" t="inlineStr"/>
+      <c r="K534" s="2" t="inlineStr">
+        <is>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
       <c r="L534" s="2" t="inlineStr"/>
       <c r="M534" s="2" t="inlineStr"/>
     </row>
@@ -21643,7 +23755,11 @@
       <c r="J535" s="8" t="n">
         <v>-59.0748</v>
       </c>
-      <c r="K535" s="6" t="inlineStr"/>
+      <c r="K535" s="6" t="inlineStr">
+        <is>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
       <c r="L535" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
@@ -21682,7 +23798,11 @@
       <c r="J536" s="4" t="n">
         <v>-9.398999999999999</v>
       </c>
-      <c r="K536" s="2" t="inlineStr"/>
+      <c r="K536" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L536" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL</t>
@@ -21721,7 +23841,11 @@
       <c r="J537" s="8" t="n">
         <v>-0.1747</v>
       </c>
-      <c r="K537" s="6" t="inlineStr"/>
+      <c r="K537" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L537" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST KATILIM 50, BIST KOCAELI</t>
@@ -21760,7 +23884,11 @@
       <c r="J538" s="4" t="n">
         <v>-9.0931</v>
       </c>
-      <c r="K538" s="2" t="inlineStr"/>
+      <c r="K538" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L538" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST İSTANBUL, BIST ANA</t>
@@ -21801,7 +23929,11 @@
       <c r="J539" s="8" t="n">
         <v>0.1902</v>
       </c>
-      <c r="K539" s="6" t="inlineStr"/>
+      <c r="K539" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L539" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ, BIST TEMETTU</t>
@@ -21840,7 +23972,11 @@
       <c r="J540" s="4" t="n">
         <v>-0.7524</v>
       </c>
-      <c r="K540" s="2" t="inlineStr"/>
+      <c r="K540" s="2" t="inlineStr">
+        <is>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
       <c r="L540" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -21879,7 +24015,11 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="J541" s="6" t="inlineStr"/>
-      <c r="K541" s="6" t="inlineStr"/>
+      <c r="K541" s="6" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L541" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ</t>
@@ -21918,7 +24058,11 @@
       <c r="J542" s="4" t="n">
         <v>7.1809</v>
       </c>
-      <c r="K542" s="2" t="inlineStr"/>
+      <c r="K542" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L542" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -21959,7 +24103,11 @@
       <c r="J543" s="8" t="n">
         <v>-0.3923</v>
       </c>
-      <c r="K543" s="6" t="inlineStr"/>
+      <c r="K543" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L543" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST YILDIZ, BIST KOCAELI</t>
@@ -22000,7 +24148,11 @@
       <c r="J544" s="4" t="n">
         <v>-0.9726</v>
       </c>
-      <c r="K544" s="2" t="inlineStr"/>
+      <c r="K544" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L544" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST İSTANBUL, BIST KATILIM TÜM, BIST KOBİ SANAYİ</t>
@@ -22041,7 +24193,11 @@
       <c r="J545" s="8" t="n">
         <v>-2.1441</v>
       </c>
-      <c r="K545" s="6" t="inlineStr"/>
+      <c r="K545" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L545" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST ANA</t>
@@ -22082,7 +24238,11 @@
       <c r="J546" s="4" t="n">
         <v>-1.5645</v>
       </c>
-      <c r="K546" s="2" t="inlineStr"/>
+      <c r="K546" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L546" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST ANA, STOXX Emerging Markets 1500</t>
@@ -22121,7 +24281,11 @@
       <c r="J547" s="8" t="n">
         <v>-28.3244</v>
       </c>
-      <c r="K547" s="6" t="inlineStr"/>
+      <c r="K547" s="6" t="inlineStr">
+        <is>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
       <c r="L547" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL</t>
@@ -22160,7 +24324,11 @@
       <c r="J548" s="4" t="n">
         <v>-11.9636</v>
       </c>
-      <c r="K548" s="2" t="inlineStr"/>
+      <c r="K548" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L548" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST SÜRDÜRÜLEBİLİRLİK, BIST ANKARA, BIST KATILIM SÜRDÜRÜLEBİLİRLİİK</t>
@@ -22199,7 +24367,11 @@
       <c r="J549" s="8" t="n">
         <v>-6790.5101</v>
       </c>
-      <c r="K549" s="6" t="inlineStr"/>
+      <c r="K549" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L549" s="6" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST KATILIM 50, BIST KATILIM 30, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
@@ -22236,7 +24408,11 @@
       <c r="J550" s="4" t="n">
         <v>-0.9651999999999999</v>
       </c>
-      <c r="K550" s="2" t="inlineStr"/>
+      <c r="K550" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L550" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST ANKARA</t>
@@ -22277,7 +24453,11 @@
       <c r="J551" s="8" t="n">
         <v>0.1253</v>
       </c>
-      <c r="K551" s="6" t="inlineStr"/>
+      <c r="K551" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L551" s="6" t="inlineStr"/>
       <c r="M551" s="6" t="inlineStr"/>
     </row>
@@ -22312,7 +24492,11 @@
         <v>0.1129</v>
       </c>
       <c r="J552" s="2" t="inlineStr"/>
-      <c r="K552" s="2" t="inlineStr"/>
+      <c r="K552" s="2" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L552" s="2" t="inlineStr"/>
       <c r="M552" s="2" t="inlineStr"/>
     </row>
@@ -22349,7 +24533,11 @@
       <c r="J553" s="8" t="n">
         <v>0.4836</v>
       </c>
-      <c r="K553" s="6" t="inlineStr"/>
+      <c r="K553" s="6" t="inlineStr">
+        <is>
+          <t>Sağlık teknolojisi</t>
+        </is>
+      </c>
       <c r="L553" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST ANA, BIST KOBİ SANAYİ, BIST ANKARA</t>
@@ -22386,7 +24574,11 @@
       <c r="J554" s="4" t="n">
         <v>-67.1895</v>
       </c>
-      <c r="K554" s="2" t="inlineStr"/>
+      <c r="K554" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L554" s="2" t="inlineStr"/>
       <c r="M554" s="2" t="inlineStr"/>
     </row>
@@ -22423,7 +24615,11 @@
       <c r="J555" s="8" t="n">
         <v>2.6125</v>
       </c>
-      <c r="K555" s="6" t="inlineStr"/>
+      <c r="K555" s="6" t="inlineStr">
+        <is>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
       <c r="L555" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
@@ -22462,7 +24658,11 @@
       <c r="J556" s="4" t="n">
         <v>-0.7162999999999999</v>
       </c>
-      <c r="K556" s="2" t="inlineStr"/>
+      <c r="K556" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L556" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST ANA, BIST İZMİR</t>
@@ -22499,7 +24699,11 @@
       <c r="J557" s="8" t="n">
         <v>0.4908</v>
       </c>
-      <c r="K557" s="6" t="inlineStr"/>
+      <c r="K557" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L557" s="6" t="inlineStr">
         <is>
           <t>BIST MENKUL KIYM YO</t>
@@ -22538,7 +24742,11 @@
       <c r="J558" s="4" t="n">
         <v>-1.529</v>
       </c>
-      <c r="K558" s="2" t="inlineStr"/>
+      <c r="K558" s="2" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L558" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST KATILIM TÜM</t>
@@ -22577,7 +24785,11 @@
       <c r="J559" s="8" t="n">
         <v>0.5811999999999999</v>
       </c>
-      <c r="K559" s="6" t="inlineStr"/>
+      <c r="K559" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L559" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
@@ -22616,7 +24828,11 @@
       <c r="J560" s="4" t="n">
         <v>-4.3494</v>
       </c>
-      <c r="K560" s="2" t="inlineStr"/>
+      <c r="K560" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L560" s="2" t="inlineStr"/>
       <c r="M560" s="2" t="inlineStr"/>
     </row>
@@ -22653,7 +24869,11 @@
       <c r="J561" s="8" t="n">
         <v>0.3524</v>
       </c>
-      <c r="K561" s="6" t="inlineStr"/>
+      <c r="K561" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L561" s="6" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST MALİ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU, BIST KATILIM 50, BIST KATILIM 30, BIST KATILIM TEMETTU, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
@@ -22692,7 +24912,11 @@
       <c r="J562" s="4" t="n">
         <v>-4.018899999999999</v>
       </c>
-      <c r="K562" s="2" t="inlineStr"/>
+      <c r="K562" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L562" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İNŞAAT, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST 50-30, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
@@ -22731,7 +24955,11 @@
       <c r="J563" s="8" t="n">
         <v>-0.6609</v>
       </c>
-      <c r="K563" s="6" t="inlineStr"/>
+      <c r="K563" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L563" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ, STOXX Emerging Markets 1500</t>
@@ -22772,7 +25000,11 @@
       <c r="J564" s="4" t="n">
         <v>30.5521</v>
       </c>
-      <c r="K564" s="2" t="inlineStr"/>
+      <c r="K564" s="2" t="inlineStr">
+        <is>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
       <c r="L564" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST ULASTIRMA, BIST TÜM, BIST 50, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST 50-30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10, STOXX Emerging Markets 1500</t>
@@ -22811,7 +25043,11 @@
         <v>0.2442</v>
       </c>
       <c r="J565" s="6" t="inlineStr"/>
-      <c r="K565" s="6" t="inlineStr"/>
+      <c r="K565" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L565" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
@@ -22848,7 +25084,11 @@
         <v>-0.1302</v>
       </c>
       <c r="J566" s="2" t="inlineStr"/>
-      <c r="K566" s="2" t="inlineStr"/>
+      <c r="K566" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L566" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST KATILIM 50, BIST KOBİ SANAYİ, BIST İZMİR</t>
@@ -22889,7 +25129,11 @@
       <c r="J567" s="8" t="n">
         <v>-0.2499</v>
       </c>
-      <c r="K567" s="6" t="inlineStr"/>
+      <c r="K567" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L567" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST YILDIZ, BIST BURSA</t>
@@ -22926,7 +25170,11 @@
         <v>-0.2336</v>
       </c>
       <c r="J568" s="2" t="inlineStr"/>
-      <c r="K568" s="2" t="inlineStr"/>
+      <c r="K568" s="2" t="inlineStr">
+        <is>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
       <c r="L568" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST ANA</t>
@@ -22963,7 +25211,11 @@
         <v>-0.4094</v>
       </c>
       <c r="J569" s="6" t="inlineStr"/>
-      <c r="K569" s="6" t="inlineStr"/>
+      <c r="K569" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L569" s="6" t="inlineStr"/>
       <c r="M569" s="6" t="inlineStr"/>
     </row>
@@ -22998,7 +25250,11 @@
       <c r="J570" s="4" t="n">
         <v>-0.6534</v>
       </c>
-      <c r="K570" s="2" t="inlineStr"/>
+      <c r="K570" s="2" t="inlineStr">
+        <is>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
       <c r="L570" s="2" t="inlineStr">
         <is>
           <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST MANİSA</t>
@@ -23039,7 +25295,11 @@
       <c r="J571" s="8" t="n">
         <v>0.9841</v>
       </c>
-      <c r="K571" s="6" t="inlineStr"/>
+      <c r="K571" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L571" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA, STOXX Emerging Markets 1500</t>
@@ -23078,7 +25338,11 @@
         <v>0.2047</v>
       </c>
       <c r="J572" s="2" t="inlineStr"/>
-      <c r="K572" s="2" t="inlineStr"/>
+      <c r="K572" s="2" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L572" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
@@ -23117,7 +25381,11 @@
       <c r="J573" s="8" t="n">
         <v>-5.8214</v>
       </c>
-      <c r="K573" s="6" t="inlineStr"/>
+      <c r="K573" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L573" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST İSTANBUL, BIST YILDIZ, BIST KOBİ SANAYİ</t>
@@ -23154,7 +25422,11 @@
       <c r="J574" s="4" t="n">
         <v>-0.3896</v>
       </c>
-      <c r="K574" s="2" t="inlineStr"/>
+      <c r="K574" s="2" t="inlineStr">
+        <is>
+          <t>Enerji-dışı mineraller</t>
+        </is>
+      </c>
       <c r="L574" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST KOBİ SANAYİ</t>
@@ -23195,7 +25467,11 @@
       <c r="J575" s="8" t="n">
         <v>-0.9891</v>
       </c>
-      <c r="K575" s="6" t="inlineStr"/>
+      <c r="K575" s="6" t="inlineStr">
+        <is>
+          <t>Tüketici hizmetleri</t>
+        </is>
+      </c>
       <c r="L575" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST TURİZM, BIST HİZMETLER, BIST ANA, BIST ANTALYA</t>
@@ -23236,7 +25512,11 @@
       <c r="J576" s="4" t="n">
         <v>0.09619999999999999</v>
       </c>
-      <c r="K576" s="2" t="inlineStr"/>
+      <c r="K576" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L576" s="2" t="inlineStr">
         <is>
           <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST HALKA ARZ, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
@@ -23277,7 +25557,11 @@
       <c r="J577" s="8" t="n">
         <v>0.6855</v>
       </c>
-      <c r="K577" s="6" t="inlineStr"/>
+      <c r="K577" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L577" s="6" t="inlineStr">
         <is>
           <t>BIST BANKA, BIST TUM-100, BIST TÜM, BIST MALİ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK</t>
@@ -23316,7 +25600,11 @@
       <c r="J578" s="4" t="n">
         <v>0.4335</v>
       </c>
-      <c r="K578" s="2" t="inlineStr"/>
+      <c r="K578" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L578" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST KOBİ SANAYİ, BIST BURSA</t>
@@ -23355,7 +25643,11 @@
       <c r="J579" s="8" t="n">
         <v>-2.8801</v>
       </c>
-      <c r="K579" s="6" t="inlineStr"/>
+      <c r="K579" s="6" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
       <c r="L579" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST KATILIM TÜM, BIST ANA, BIST ANKARA</t>
@@ -23396,7 +25688,11 @@
       <c r="J580" s="4" t="n">
         <v>-0.7746999999999999</v>
       </c>
-      <c r="K580" s="2" t="inlineStr"/>
+      <c r="K580" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L580" s="2" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL</t>
@@ -23437,74 +25733,72 @@
       <c r="J581" s="8" t="n">
         <v>0.6855</v>
       </c>
-      <c r="K581" s="6" t="inlineStr"/>
+      <c r="K581" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L581" s="6" t="inlineStr"/>
       <c r="M581" s="6" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B582" s="3" t="n">
-        <v>19.01</v>
+        <v>80.53</v>
       </c>
       <c r="C582" s="4" t="n">
-        <v>-0.0031</v>
+        <v>0.0176</v>
       </c>
       <c r="D582" s="5" t="n">
-        <v>62410000</v>
+        <v>10440000</v>
       </c>
       <c r="E582" s="2" t="inlineStr"/>
       <c r="F582" s="3" t="n">
-        <v>29.07</v>
+        <v>43.51</v>
       </c>
       <c r="G582" s="2" t="inlineStr"/>
       <c r="H582" s="2" t="inlineStr"/>
       <c r="I582" s="2" t="inlineStr"/>
       <c r="J582" s="2" t="inlineStr"/>
       <c r="K582" s="2" t="inlineStr"/>
-      <c r="L582" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
-        </is>
-      </c>
+      <c r="L582" s="2" t="inlineStr"/>
       <c r="M582" s="2" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B583" s="7" t="n">
-        <v>140.3</v>
+        <v>40.58</v>
       </c>
       <c r="C583" s="8" t="n">
-        <v>0.0316</v>
-      </c>
-      <c r="D583" s="9" t="n">
-        <v>2340000</v>
-      </c>
-      <c r="E583" s="8" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>-0.0117</v>
+      </c>
+      <c r="D583" s="7" t="n">
+        <v>8380000.000000001</v>
+      </c>
+      <c r="E583" s="6" t="inlineStr"/>
       <c r="F583" s="7" t="n">
-        <v>46.39</v>
+        <v>54.32</v>
       </c>
       <c r="G583" s="6" t="inlineStr"/>
       <c r="H583" s="6" t="inlineStr"/>
-      <c r="I583" s="8" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J583" s="8" t="n">
-        <v>-0.4897</v>
-      </c>
-      <c r="K583" s="6" t="inlineStr"/>
+      <c r="I583" s="6" t="inlineStr"/>
+      <c r="J583" s="6" t="inlineStr"/>
+      <c r="K583" s="6" t="inlineStr">
+        <is>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
       <c r="L583" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M583" s="6" t="inlineStr"/>
@@ -23512,30 +25806,34 @@
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>33.06</v>
+        <v>21.46</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.0999</v>
       </c>
       <c r="D584" s="5" t="n">
-        <v>4310000</v>
+        <v>86600000</v>
       </c>
       <c r="E584" s="2" t="inlineStr"/>
       <c r="F584" s="3" t="n">
-        <v>48.1</v>
+        <v>68.67</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
       <c r="I584" s="2" t="inlineStr"/>
       <c r="J584" s="2" t="inlineStr"/>
-      <c r="K584" s="2" t="inlineStr"/>
+      <c r="K584" s="2" t="inlineStr">
+        <is>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
       <c r="L584" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M584" s="2" t="inlineStr"/>
@@ -23543,38 +25841,40 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>17.05</v>
+        <v>2.68</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>0.0137</v>
+        <v>0</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>11180000</v>
+        <v>90400000</v>
       </c>
       <c r="E585" s="8" t="n">
-        <v>0.9246</v>
+        <v>0.7119</v>
       </c>
       <c r="F585" s="7" t="n">
-        <v>46.47</v>
-      </c>
-      <c r="G585" s="7" t="n">
-        <v>161.15</v>
-      </c>
+        <v>42.36</v>
+      </c>
+      <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
       <c r="I585" s="8" t="n">
-        <v>0.0028</v>
+        <v>-191.6342</v>
       </c>
       <c r="J585" s="8" t="n">
-        <v>-10.3171</v>
-      </c>
-      <c r="K585" s="6" t="inlineStr"/>
+        <v>-0.8093</v>
+      </c>
+      <c r="K585" s="6" t="inlineStr">
+        <is>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
       <c r="L585" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M585" s="6" t="inlineStr"/>
@@ -23582,30 +25882,34 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>38.72</v>
+        <v>17.01</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>0.0031</v>
+        <v>-0.0053</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>10070000</v>
+        <v>72710000</v>
       </c>
       <c r="E586" s="2" t="inlineStr"/>
       <c r="F586" s="3" t="n">
-        <v>48.93</v>
+        <v>52.78</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
       <c r="I586" s="2" t="inlineStr"/>
       <c r="J586" s="2" t="inlineStr"/>
-      <c r="K586" s="2" t="inlineStr"/>
+      <c r="K586" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L586" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M586" s="2" t="inlineStr"/>
@@ -23613,36 +25917,40 @@
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>GRNYO</t>
+          <t>ATAGY</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>17.94</v>
+        <v>13.16</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>0.0022</v>
+        <v>-0.0273</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>1260000</v>
+        <v>272910</v>
       </c>
       <c r="E587" s="8" t="n">
-        <v>0.9869</v>
+        <v>0.6889</v>
       </c>
       <c r="F587" s="7" t="n">
-        <v>58.1</v>
+        <v>56.17</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
       <c r="I587" s="8" t="n">
-        <v>-0.2446</v>
+        <v>-0.0266</v>
       </c>
       <c r="J587" s="8" t="n">
-        <v>0.3246</v>
-      </c>
-      <c r="K587" s="6" t="inlineStr"/>
+        <v>-0.5014999999999999</v>
+      </c>
+      <c r="K587" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L587" s="6" t="inlineStr">
         <is>
-          <t>BIST MENKUL KIYM YO</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ</t>
         </is>
       </c>
       <c r="M587" s="6" t="inlineStr"/>
@@ -23650,63 +25958,71 @@
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>78.5</v>
+        <v>162.5</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>0.07980000000000001</v>
+        <v>0.0037</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>34400</v>
-      </c>
-      <c r="E588" s="4" t="n">
-        <v>0.58</v>
-      </c>
+        <v>6940000</v>
+      </c>
+      <c r="E588" s="2" t="inlineStr"/>
       <c r="F588" s="3" t="n">
-        <v>43.41</v>
+        <v>55.44</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
-      <c r="I588" s="4" t="n">
-        <v>-9.409700000000001</v>
-      </c>
-      <c r="J588" s="4" t="n">
-        <v>-4.155</v>
-      </c>
-      <c r="K588" s="2" t="inlineStr"/>
-      <c r="L588" s="2" t="inlineStr"/>
+      <c r="I588" s="2" t="inlineStr"/>
+      <c r="J588" s="2" t="inlineStr"/>
+      <c r="K588" s="2" t="inlineStr">
+        <is>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L588" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+        </is>
+      </c>
       <c r="M588" s="2" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>17.01</v>
+        <v>28.48</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>-0.0053</v>
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>72710000</v>
-      </c>
-      <c r="E589" s="6" t="inlineStr"/>
+        <v>18800000</v>
+      </c>
+      <c r="E589" s="8" t="n">
+        <v>0.2667</v>
+      </c>
       <c r="F589" s="7" t="n">
-        <v>52.78</v>
+        <v>49.66</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
       <c r="I589" s="6" t="inlineStr"/>
       <c r="J589" s="6" t="inlineStr"/>
-      <c r="K589" s="6" t="inlineStr"/>
+      <c r="K589" s="6" t="inlineStr">
+        <is>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
       <c r="L589" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M589" s="6" t="inlineStr"/>
@@ -23714,100 +26030,106 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>7</v>
+        <v>33.06</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>-0.0182</v>
+        <v>0.0024</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>542950</v>
-      </c>
-      <c r="E590" s="4" t="n">
-        <v>0.95</v>
-      </c>
+        <v>4310000</v>
+      </c>
+      <c r="E590" s="2" t="inlineStr"/>
       <c r="F590" s="3" t="n">
-        <v>37.31</v>
+        <v>48.1</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
-      <c r="I590" s="4" t="n">
-        <v>-23.6291</v>
-      </c>
-      <c r="J590" s="4" t="n">
-        <v>-0.4678</v>
-      </c>
-      <c r="K590" s="2" t="inlineStr"/>
-      <c r="L590" s="2" t="inlineStr"/>
+      <c r="I590" s="2" t="inlineStr"/>
+      <c r="J590" s="2" t="inlineStr"/>
+      <c r="K590" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
+      <c r="L590" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+        </is>
+      </c>
       <c r="M590" s="2" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>ATAGY</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>13.16</v>
+        <v>6.16</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>-0.0273</v>
+        <v>0.0016</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>272910</v>
-      </c>
-      <c r="E591" s="8" t="n">
-        <v>0.6889</v>
-      </c>
+        <v>7690000</v>
+      </c>
+      <c r="E591" s="6" t="inlineStr"/>
       <c r="F591" s="7" t="n">
-        <v>56.17</v>
+        <v>62.72</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="8" t="n">
-        <v>-0.0266</v>
-      </c>
-      <c r="J591" s="8" t="n">
-        <v>-0.5014999999999999</v>
-      </c>
-      <c r="K591" s="6" t="inlineStr"/>
-      <c r="L591" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ</t>
-        </is>
-      </c>
+      <c r="I591" s="6" t="inlineStr"/>
+      <c r="J591" s="6" t="inlineStr"/>
+      <c r="K591" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L591" s="6" t="inlineStr"/>
       <c r="M591" s="6" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>GRNYO</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>189.5</v>
+        <v>17.94</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>0.0706</v>
+        <v>0.0022</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>18010000</v>
-      </c>
-      <c r="E592" s="2" t="inlineStr"/>
+        <v>1260000</v>
+      </c>
+      <c r="E592" s="4" t="n">
+        <v>0.9869</v>
+      </c>
       <c r="F592" s="3" t="n">
-        <v>44.94</v>
+        <v>58.1</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
-      <c r="I592" s="2" t="inlineStr"/>
-      <c r="J592" s="2" t="inlineStr"/>
-      <c r="K592" s="2" t="inlineStr"/>
+      <c r="I592" s="4" t="n">
+        <v>-0.2446</v>
+      </c>
+      <c r="J592" s="4" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="K592" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L592" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M592" s="2" t="inlineStr"/>
@@ -23815,30 +26137,38 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>13.98</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>0.0138</v>
+        <v>-0.0106</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>32400000</v>
-      </c>
-      <c r="E593" s="6" t="inlineStr"/>
+        <v>665180</v>
+      </c>
+      <c r="E593" s="8" t="n">
+        <v>0.3695000000000001</v>
+      </c>
       <c r="F593" s="7" t="n">
-        <v>54.25</v>
+        <v>58.93</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
       <c r="I593" s="6" t="inlineStr"/>
-      <c r="J593" s="6" t="inlineStr"/>
-      <c r="K593" s="6" t="inlineStr"/>
+      <c r="J593" s="8" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="K593" s="6" t="inlineStr">
+        <is>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
       <c r="L593" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M593" s="6" t="inlineStr"/>
@@ -23846,30 +26176,34 @@
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>21.46</v>
+        <v>27.16</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>0.0999</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>86600000</v>
+        <v>17070000</v>
       </c>
       <c r="E594" s="2" t="inlineStr"/>
       <c r="F594" s="3" t="n">
-        <v>68.67</v>
+        <v>63.67</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
       <c r="I594" s="2" t="inlineStr"/>
       <c r="J594" s="2" t="inlineStr"/>
-      <c r="K594" s="2" t="inlineStr"/>
+      <c r="K594" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
       <c r="L594" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M594" s="2" t="inlineStr"/>
@@ -23877,57 +26211,71 @@
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>80.53</v>
+        <v>7</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>0.0176</v>
+        <v>-0.0182</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>10440000</v>
-      </c>
-      <c r="E595" s="6" t="inlineStr"/>
+        <v>542950</v>
+      </c>
+      <c r="E595" s="8" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F595" s="7" t="n">
-        <v>43.51</v>
+        <v>37.31</v>
       </c>
       <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
-      <c r="I595" s="6" t="inlineStr"/>
-      <c r="J595" s="6" t="inlineStr"/>
-      <c r="K595" s="6" t="inlineStr"/>
+      <c r="I595" s="8" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J595" s="8" t="n">
+        <v>-0.4678</v>
+      </c>
+      <c r="K595" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L595" s="6" t="inlineStr"/>
       <c r="M595" s="6" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>162.5</v>
+        <v>19.01</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>0.0037</v>
+        <v>-0.0031</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>6940000</v>
+        <v>62410000</v>
       </c>
       <c r="E596" s="2" t="inlineStr"/>
       <c r="F596" s="3" t="n">
-        <v>55.44</v>
+        <v>29.07</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
       <c r="I596" s="2" t="inlineStr"/>
       <c r="J596" s="2" t="inlineStr"/>
-      <c r="K596" s="2" t="inlineStr"/>
+      <c r="K596" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L596" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M596" s="2" t="inlineStr"/>
@@ -23935,32 +26283,40 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>28.48</v>
+        <v>7.62</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>18800000</v>
+        <v>122010000</v>
       </c>
       <c r="E597" s="8" t="n">
-        <v>0.2667</v>
+        <v>0.1672</v>
       </c>
       <c r="F597" s="7" t="n">
-        <v>49.66</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
-      <c r="I597" s="6" t="inlineStr"/>
-      <c r="J597" s="6" t="inlineStr"/>
-      <c r="K597" s="6" t="inlineStr"/>
+      <c r="I597" s="8" t="n">
+        <v>-5.3262</v>
+      </c>
+      <c r="J597" s="8" t="n">
+        <v>-4.2562</v>
+      </c>
+      <c r="K597" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L597" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M597" s="6" t="inlineStr"/>
@@ -23968,30 +26324,34 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>2.94</v>
+        <v>38.72</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>0.09699999999999999</v>
+        <v>0.0031</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>240000000</v>
+        <v>10070000</v>
       </c>
       <c r="E598" s="2" t="inlineStr"/>
       <c r="F598" s="3" t="n">
-        <v>55.79</v>
+        <v>48.93</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
       <c r="I598" s="2" t="inlineStr"/>
       <c r="J598" s="2" t="inlineStr"/>
-      <c r="K598" s="2" t="inlineStr"/>
+      <c r="K598" s="2" t="inlineStr">
+        <is>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
       <c r="L598" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M598" s="2" t="inlineStr"/>
@@ -23999,90 +26359,112 @@
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>92.09999999999999</v>
+        <v>2.94</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>0.0071</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>255560</v>
+        <v>240000000</v>
       </c>
       <c r="E599" s="6" t="inlineStr"/>
       <c r="F599" s="7" t="n">
-        <v>11.8</v>
+        <v>55.79</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
       <c r="I599" s="6" t="inlineStr"/>
       <c r="J599" s="6" t="inlineStr"/>
-      <c r="K599" s="6" t="inlineStr"/>
-      <c r="L599" s="6" t="inlineStr"/>
+      <c r="K599" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L599" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+        </is>
+      </c>
       <c r="M599" s="6" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>6.16</v>
+        <v>17.05</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>0.0016</v>
+        <v>0.0137</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>7690000</v>
-      </c>
-      <c r="E600" s="2" t="inlineStr"/>
+        <v>11180000</v>
+      </c>
+      <c r="E600" s="4" t="n">
+        <v>0.9246</v>
+      </c>
       <c r="F600" s="3" t="n">
-        <v>62.72</v>
-      </c>
-      <c r="G600" s="2" t="inlineStr"/>
+        <v>46.47</v>
+      </c>
+      <c r="G600" s="3" t="n">
+        <v>161.15</v>
+      </c>
       <c r="H600" s="2" t="inlineStr"/>
-      <c r="I600" s="2" t="inlineStr"/>
-      <c r="J600" s="2" t="inlineStr"/>
-      <c r="K600" s="2" t="inlineStr"/>
-      <c r="L600" s="2" t="inlineStr"/>
+      <c r="I600" s="4" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="J600" s="4" t="n">
+        <v>-10.3171</v>
+      </c>
+      <c r="K600" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
+      <c r="L600" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+        </is>
+      </c>
       <c r="M600" s="2" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>2.68</v>
+        <v>13.98</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>0</v>
+        <v>0.0138</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>90400000</v>
-      </c>
-      <c r="E601" s="8" t="n">
-        <v>0.7119</v>
-      </c>
+        <v>32400000</v>
+      </c>
+      <c r="E601" s="6" t="inlineStr"/>
       <c r="F601" s="7" t="n">
-        <v>42.36</v>
+        <v>54.25</v>
       </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
-      <c r="I601" s="8" t="n">
-        <v>-191.6342</v>
-      </c>
-      <c r="J601" s="8" t="n">
-        <v>-0.8093</v>
-      </c>
-      <c r="K601" s="6" t="inlineStr"/>
+      <c r="I601" s="6" t="inlineStr"/>
+      <c r="J601" s="6" t="inlineStr"/>
+      <c r="K601" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L601" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M601" s="6" t="inlineStr"/>
@@ -24090,67 +26472,69 @@
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>40.58</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>-0.0117</v>
-      </c>
-      <c r="D602" s="3" t="n">
-        <v>8380000.000000001</v>
+        <v>0.0071</v>
+      </c>
+      <c r="D602" s="5" t="n">
+        <v>255560</v>
       </c>
       <c r="E602" s="2" t="inlineStr"/>
       <c r="F602" s="3" t="n">
-        <v>54.32</v>
+        <v>11.8</v>
       </c>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
       <c r="I602" s="2" t="inlineStr"/>
       <c r="J602" s="2" t="inlineStr"/>
-      <c r="K602" s="2" t="inlineStr"/>
-      <c r="L602" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
-        </is>
-      </c>
+      <c r="K602" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L602" s="2" t="inlineStr"/>
       <c r="M602" s="2" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>65.34999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>-0.0106</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>665180</v>
+        <v>34400</v>
       </c>
       <c r="E603" s="8" t="n">
-        <v>0.3695000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="F603" s="7" t="n">
-        <v>58.93</v>
+        <v>43.41</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
-      <c r="I603" s="6" t="inlineStr"/>
+      <c r="I603" s="8" t="n">
+        <v>-9.409700000000001</v>
+      </c>
       <c r="J603" s="8" t="n">
-        <v>0.4139</v>
-      </c>
-      <c r="K603" s="6" t="inlineStr"/>
-      <c r="L603" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
-        </is>
-      </c>
+        <v>-4.155</v>
+      </c>
+      <c r="K603" s="6" t="inlineStr">
+        <is>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L603" s="6" t="inlineStr"/>
       <c r="M603" s="6" t="inlineStr"/>
     </row>
     <row r="604">
@@ -24178,7 +26562,11 @@
       <c r="H604" s="2" t="inlineStr"/>
       <c r="I604" s="2" t="inlineStr"/>
       <c r="J604" s="2" t="inlineStr"/>
-      <c r="K604" s="2" t="inlineStr"/>
+      <c r="K604" s="2" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L604" s="2" t="inlineStr"/>
       <c r="M604" s="2" t="inlineStr"/>
     </row>
@@ -24207,7 +26595,11 @@
       <c r="H605" s="6" t="inlineStr"/>
       <c r="I605" s="6" t="inlineStr"/>
       <c r="J605" s="6" t="inlineStr"/>
-      <c r="K605" s="6" t="inlineStr"/>
+      <c r="K605" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
       <c r="L605" s="6" t="inlineStr">
         <is>
           <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
@@ -24218,30 +26610,40 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>27.16</v>
+        <v>140.3</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>0.09960000000000001</v>
+        <v>0.0316</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>17070000</v>
-      </c>
-      <c r="E606" s="2" t="inlineStr"/>
+        <v>2340000</v>
+      </c>
+      <c r="E606" s="4" t="n">
+        <v>0.1071</v>
+      </c>
       <c r="F606" s="3" t="n">
-        <v>63.67</v>
+        <v>46.39</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
-      <c r="I606" s="2" t="inlineStr"/>
-      <c r="J606" s="2" t="inlineStr"/>
-      <c r="K606" s="2" t="inlineStr"/>
+      <c r="I606" s="4" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="J606" s="4" t="n">
+        <v>-0.4897</v>
+      </c>
+      <c r="K606" s="2" t="inlineStr">
+        <is>
+          <t>Perakende satış</t>
+        </is>
+      </c>
       <c r="L606" s="2" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M606" s="2" t="inlineStr"/>
@@ -24249,36 +26651,34 @@
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>7.62</v>
+        <v>189.5</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>0.09960000000000001</v>
+        <v>0.0706</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>122010000</v>
-      </c>
-      <c r="E607" s="8" t="n">
-        <v>0.1672</v>
-      </c>
+        <v>18010000</v>
+      </c>
+      <c r="E607" s="6" t="inlineStr"/>
       <c r="F607" s="7" t="n">
-        <v>70.51000000000001</v>
+        <v>44.94</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
-      <c r="I607" s="8" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J607" s="8" t="n">
-        <v>-4.2562</v>
-      </c>
-      <c r="K607" s="6" t="inlineStr"/>
+      <c r="I607" s="6" t="inlineStr"/>
+      <c r="J607" s="6" t="inlineStr"/>
+      <c r="K607" s="6" t="inlineStr">
+        <is>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
       <c r="L607" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M607" s="6" t="inlineStr"/>
@@ -24305,7 +26705,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>01.05.2026 07:30</t>
+          <t>01.05.2026 08:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-05-01.xlsx
+++ b/data/bist_screener_2026-05-01.xlsx
@@ -25744,48 +25744,58 @@
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B582" s="3" t="n">
-        <v>80.53</v>
+        <v>5.68</v>
       </c>
       <c r="C582" s="4" t="n">
-        <v>0.0176</v>
+        <v>-0.0018</v>
       </c>
       <c r="D582" s="5" t="n">
-        <v>10440000</v>
-      </c>
-      <c r="E582" s="2" t="inlineStr"/>
+        <v>56180000</v>
+      </c>
+      <c r="E582" s="4" t="n">
+        <v>0.8667</v>
+      </c>
       <c r="F582" s="3" t="n">
-        <v>43.51</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="G582" s="2" t="inlineStr"/>
       <c r="H582" s="2" t="inlineStr"/>
       <c r="I582" s="2" t="inlineStr"/>
       <c r="J582" s="2" t="inlineStr"/>
-      <c r="K582" s="2" t="inlineStr"/>
-      <c r="L582" s="2" t="inlineStr"/>
+      <c r="K582" s="2" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L582" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+        </is>
+      </c>
       <c r="M582" s="2" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B583" s="7" t="n">
-        <v>40.58</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="C583" s="8" t="n">
-        <v>-0.0117</v>
-      </c>
-      <c r="D583" s="7" t="n">
-        <v>8380000.000000001</v>
+        <v>0.0071</v>
+      </c>
+      <c r="D583" s="9" t="n">
+        <v>255560</v>
       </c>
       <c r="E583" s="6" t="inlineStr"/>
       <c r="F583" s="7" t="n">
-        <v>54.32</v>
+        <v>11.8</v>
       </c>
       <c r="G583" s="6" t="inlineStr"/>
       <c r="H583" s="6" t="inlineStr"/>
@@ -25793,47 +25803,49 @@
       <c r="J583" s="6" t="inlineStr"/>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
-        </is>
-      </c>
-      <c r="L583" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L583" s="6" t="inlineStr"/>
       <c r="M583" s="6" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>GRNYO</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>21.46</v>
+        <v>17.94</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>0.0999</v>
+        <v>0.0022</v>
       </c>
       <c r="D584" s="5" t="n">
-        <v>86600000</v>
-      </c>
-      <c r="E584" s="2" t="inlineStr"/>
+        <v>1260000</v>
+      </c>
+      <c r="E584" s="4" t="n">
+        <v>0.9869</v>
+      </c>
       <c r="F584" s="3" t="n">
-        <v>68.67</v>
+        <v>58.1</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
-      <c r="I584" s="2" t="inlineStr"/>
-      <c r="J584" s="2" t="inlineStr"/>
+      <c r="I584" s="4" t="n">
+        <v>-0.2446</v>
+      </c>
+      <c r="J584" s="4" t="n">
+        <v>0.3246</v>
+      </c>
       <c r="K584" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L584" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M584" s="2" t="inlineStr"/>
@@ -25841,40 +25853,34 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>2.68</v>
+        <v>189.5</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>0</v>
+        <v>0.0706</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>90400000</v>
-      </c>
-      <c r="E585" s="8" t="n">
-        <v>0.7119</v>
-      </c>
+        <v>18010000</v>
+      </c>
+      <c r="E585" s="6" t="inlineStr"/>
       <c r="F585" s="7" t="n">
-        <v>42.36</v>
+        <v>44.94</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
-      <c r="I585" s="8" t="n">
-        <v>-191.6342</v>
-      </c>
-      <c r="J585" s="8" t="n">
-        <v>-0.8093</v>
-      </c>
+      <c r="I585" s="6" t="inlineStr"/>
+      <c r="J585" s="6" t="inlineStr"/>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M585" s="6" t="inlineStr"/>
@@ -25882,21 +25888,21 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>17.01</v>
+        <v>6.16</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>-0.0053</v>
+        <v>0.0016</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>72710000</v>
+        <v>7690000</v>
       </c>
       <c r="E586" s="2" t="inlineStr"/>
       <c r="F586" s="3" t="n">
-        <v>52.78</v>
+        <v>62.72</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
@@ -25907,42 +25913,32 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L586" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+      <c r="L586" s="2" t="inlineStr"/>
       <c r="M586" s="2" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>ATAGY</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>13.16</v>
+        <v>2.94</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>-0.0273</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>272910</v>
-      </c>
-      <c r="E587" s="8" t="n">
-        <v>0.6889</v>
-      </c>
+        <v>240000000</v>
+      </c>
+      <c r="E587" s="6" t="inlineStr"/>
       <c r="F587" s="7" t="n">
-        <v>56.17</v>
+        <v>55.79</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
-      <c r="I587" s="8" t="n">
-        <v>-0.0266</v>
-      </c>
-      <c r="J587" s="8" t="n">
-        <v>-0.5014999999999999</v>
-      </c>
+      <c r="I587" s="6" t="inlineStr"/>
+      <c r="J587" s="6" t="inlineStr"/>
       <c r="K587" s="6" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -25950,7 +25946,7 @@
       </c>
       <c r="L587" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M587" s="6" t="inlineStr"/>
@@ -25958,34 +25954,42 @@
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>162.5</v>
+        <v>17.05</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>0.0037</v>
+        <v>0.0137</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>6940000</v>
-      </c>
-      <c r="E588" s="2" t="inlineStr"/>
+        <v>11180000</v>
+      </c>
+      <c r="E588" s="4" t="n">
+        <v>0.9246</v>
+      </c>
       <c r="F588" s="3" t="n">
-        <v>55.44</v>
-      </c>
-      <c r="G588" s="2" t="inlineStr"/>
+        <v>46.47</v>
+      </c>
+      <c r="G588" s="3" t="n">
+        <v>161.15</v>
+      </c>
       <c r="H588" s="2" t="inlineStr"/>
-      <c r="I588" s="2" t="inlineStr"/>
-      <c r="J588" s="2" t="inlineStr"/>
+      <c r="I588" s="4" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="J588" s="4" t="n">
+        <v>-10.3171</v>
+      </c>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L588" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
         </is>
       </c>
       <c r="M588" s="2" t="inlineStr"/>
@@ -25993,23 +25997,21 @@
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>28.48</v>
+        <v>40.58</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>-0.0007000000000000001</v>
-      </c>
-      <c r="D589" s="9" t="n">
-        <v>18800000</v>
-      </c>
-      <c r="E589" s="8" t="n">
-        <v>0.2667</v>
-      </c>
+        <v>-0.0117</v>
+      </c>
+      <c r="D589" s="7" t="n">
+        <v>8380000.000000001</v>
+      </c>
+      <c r="E589" s="6" t="inlineStr"/>
       <c r="F589" s="7" t="n">
-        <v>49.66</v>
+        <v>54.32</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
@@ -26017,12 +26019,12 @@
       <c r="J589" s="6" t="inlineStr"/>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M589" s="6" t="inlineStr"/>
@@ -26030,56 +26032,58 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>33.06</v>
+        <v>78.5</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>4310000</v>
-      </c>
-      <c r="E590" s="2" t="inlineStr"/>
+        <v>34400</v>
+      </c>
+      <c r="E590" s="4" t="n">
+        <v>0.58</v>
+      </c>
       <c r="F590" s="3" t="n">
-        <v>48.1</v>
+        <v>43.41</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
-      <c r="I590" s="2" t="inlineStr"/>
-      <c r="J590" s="2" t="inlineStr"/>
+      <c r="I590" s="4" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J590" s="4" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
-        </is>
-      </c>
-      <c r="L590" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L590" s="2" t="inlineStr"/>
       <c r="M590" s="2" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>6.16</v>
+        <v>162.5</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>0.0016</v>
+        <v>0.0037</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>7690000</v>
+        <v>6940000</v>
       </c>
       <c r="E591" s="6" t="inlineStr"/>
       <c r="F591" s="7" t="n">
-        <v>62.72</v>
+        <v>55.44</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
@@ -26087,41 +26091,39 @@
       <c r="J591" s="6" t="inlineStr"/>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L591" s="6" t="inlineStr"/>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L591" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+        </is>
+      </c>
       <c r="M591" s="6" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>GRNYO</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>17.94</v>
+        <v>17.01</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>0.0022</v>
+        <v>-0.0053</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>1260000</v>
-      </c>
-      <c r="E592" s="4" t="n">
-        <v>0.9869</v>
-      </c>
+        <v>72710000</v>
+      </c>
+      <c r="E592" s="2" t="inlineStr"/>
       <c r="F592" s="3" t="n">
-        <v>58.1</v>
+        <v>52.78</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
-      <c r="I592" s="4" t="n">
-        <v>-0.2446</v>
-      </c>
-      <c r="J592" s="4" t="n">
-        <v>0.3246</v>
-      </c>
+      <c r="I592" s="2" t="inlineStr"/>
+      <c r="J592" s="2" t="inlineStr"/>
       <c r="K592" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -26129,7 +26131,7 @@
       </c>
       <c r="L592" s="2" t="inlineStr">
         <is>
-          <t>BIST MENKUL KIYM YO</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M592" s="2" t="inlineStr"/>
@@ -26137,38 +26139,40 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>65.34999999999999</v>
+        <v>7.62</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>-0.0106</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>665180</v>
+        <v>122010000</v>
       </c>
       <c r="E593" s="8" t="n">
-        <v>0.3695000000000001</v>
+        <v>0.1672</v>
       </c>
       <c r="F593" s="7" t="n">
-        <v>58.93</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
-      <c r="I593" s="6" t="inlineStr"/>
+      <c r="I593" s="8" t="n">
+        <v>-5.3262</v>
+      </c>
       <c r="J593" s="8" t="n">
-        <v>0.4139</v>
+        <v>-4.2562</v>
       </c>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M593" s="6" t="inlineStr"/>
@@ -26176,34 +26180,40 @@
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>27.16</v>
+        <v>140.3</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>0.09960000000000001</v>
+        <v>0.0316</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>17070000</v>
-      </c>
-      <c r="E594" s="2" t="inlineStr"/>
+        <v>2340000</v>
+      </c>
+      <c r="E594" s="4" t="n">
+        <v>0.1071</v>
+      </c>
       <c r="F594" s="3" t="n">
-        <v>63.67</v>
+        <v>46.39</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
-      <c r="I594" s="2" t="inlineStr"/>
-      <c r="J594" s="2" t="inlineStr"/>
+      <c r="I594" s="4" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="J594" s="4" t="n">
+        <v>-0.4897</v>
+      </c>
       <c r="K594" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L594" s="2" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M594" s="2" t="inlineStr"/>
@@ -26248,75 +26258,67 @@
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>19.01</v>
+        <v>80.53</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>-0.0031</v>
+        <v>0.0176</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>62410000</v>
+        <v>10440000</v>
       </c>
       <c r="E596" s="2" t="inlineStr"/>
       <c r="F596" s="3" t="n">
-        <v>29.07</v>
+        <v>43.51</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
       <c r="I596" s="2" t="inlineStr"/>
       <c r="J596" s="2" t="inlineStr"/>
-      <c r="K596" s="2" t="inlineStr">
-        <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L596" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
-        </is>
-      </c>
+      <c r="K596" s="2" t="inlineStr"/>
+      <c r="L596" s="2" t="inlineStr"/>
       <c r="M596" s="2" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>7.62</v>
+        <v>2.68</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>0.09960000000000001</v>
+        <v>0</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>122010000</v>
+        <v>90400000</v>
       </c>
       <c r="E597" s="8" t="n">
-        <v>0.1672</v>
+        <v>0.7119</v>
       </c>
       <c r="F597" s="7" t="n">
-        <v>70.51000000000001</v>
+        <v>42.36</v>
       </c>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
       <c r="I597" s="8" t="n">
-        <v>-5.3262</v>
+        <v>-191.6342</v>
       </c>
       <c r="J597" s="8" t="n">
-        <v>-4.2562</v>
+        <v>-0.8093</v>
       </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M597" s="6" t="inlineStr"/>
@@ -26324,21 +26326,23 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>38.72</v>
+        <v>242</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>0.0031</v>
+        <v>0</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>10070000</v>
-      </c>
-      <c r="E598" s="2" t="inlineStr"/>
+        <v>7420</v>
+      </c>
+      <c r="E598" s="4" t="n">
+        <v>0.2578</v>
+      </c>
       <c r="F598" s="3" t="n">
-        <v>48.93</v>
+        <v>41.93</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
@@ -26346,39 +26350,41 @@
       <c r="J598" s="2" t="inlineStr"/>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
-        </is>
-      </c>
-      <c r="L598" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L598" s="2" t="inlineStr"/>
       <c r="M598" s="2" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>ATAGY</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>2.94</v>
+        <v>13.16</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>0.09699999999999999</v>
+        <v>-0.0273</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>240000000</v>
-      </c>
-      <c r="E599" s="6" t="inlineStr"/>
+        <v>272910</v>
+      </c>
+      <c r="E599" s="8" t="n">
+        <v>0.6889</v>
+      </c>
       <c r="F599" s="7" t="n">
-        <v>55.79</v>
+        <v>56.17</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
-      <c r="I599" s="6" t="inlineStr"/>
-      <c r="J599" s="6" t="inlineStr"/>
+      <c r="I599" s="8" t="n">
+        <v>-0.0266</v>
+      </c>
+      <c r="J599" s="8" t="n">
+        <v>-0.5014999999999999</v>
+      </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -26386,7 +26392,7 @@
       </c>
       <c r="L599" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ</t>
         </is>
       </c>
       <c r="M599" s="6" t="inlineStr"/>
@@ -26394,34 +26400,26 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>17.05</v>
+        <v>33.06</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>0.0137</v>
+        <v>0.0024</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>11180000</v>
-      </c>
-      <c r="E600" s="4" t="n">
-        <v>0.9246</v>
-      </c>
+        <v>4310000</v>
+      </c>
+      <c r="E600" s="2" t="inlineStr"/>
       <c r="F600" s="3" t="n">
-        <v>46.47</v>
-      </c>
-      <c r="G600" s="3" t="n">
-        <v>161.15</v>
-      </c>
+        <v>48.1</v>
+      </c>
+      <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
-      <c r="I600" s="4" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J600" s="4" t="n">
-        <v>-10.3171</v>
-      </c>
+      <c r="I600" s="2" t="inlineStr"/>
+      <c r="J600" s="2" t="inlineStr"/>
       <c r="K600" s="2" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -26429,7 +26427,7 @@
       </c>
       <c r="L600" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M600" s="2" t="inlineStr"/>
@@ -26472,21 +26470,21 @@
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>38.72</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>0.0071</v>
+        <v>0.0031</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>255560</v>
+        <v>10070000</v>
       </c>
       <c r="E602" s="2" t="inlineStr"/>
       <c r="F602" s="3" t="n">
-        <v>11.8</v>
+        <v>48.93</v>
       </c>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
@@ -26494,69 +26492,71 @@
       <c r="J602" s="2" t="inlineStr"/>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L602" s="2" t="inlineStr"/>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
+      <c r="L602" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+        </is>
+      </c>
       <c r="M602" s="2" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>78.5</v>
+        <v>28.48</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>0.07980000000000001</v>
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>34400</v>
+        <v>18800000</v>
       </c>
       <c r="E603" s="8" t="n">
-        <v>0.58</v>
+        <v>0.2667</v>
       </c>
       <c r="F603" s="7" t="n">
-        <v>43.41</v>
+        <v>49.66</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
-      <c r="I603" s="8" t="n">
-        <v>-9.409700000000001</v>
-      </c>
-      <c r="J603" s="8" t="n">
-        <v>-4.155</v>
-      </c>
+      <c r="I603" s="6" t="inlineStr"/>
+      <c r="J603" s="6" t="inlineStr"/>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L603" s="6" t="inlineStr"/>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
+      <c r="L603" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M603" s="6" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>242</v>
+        <v>27.16</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>0</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>7420</v>
-      </c>
-      <c r="E604" s="4" t="n">
-        <v>0.2578</v>
-      </c>
+        <v>17070000</v>
+      </c>
+      <c r="E604" s="2" t="inlineStr"/>
       <c r="F604" s="3" t="n">
-        <v>41.93</v>
+        <v>63.67</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
@@ -26564,45 +26564,51 @@
       <c r="J604" s="2" t="inlineStr"/>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L604" s="2" t="inlineStr"/>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
+      <c r="L604" s="2" t="inlineStr">
+        <is>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M604" s="2" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>5.68</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>-0.0018</v>
+        <v>-0.0106</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>56180000</v>
+        <v>665180</v>
       </c>
       <c r="E605" s="8" t="n">
-        <v>0.8667</v>
+        <v>0.3695000000000001</v>
       </c>
       <c r="F605" s="7" t="n">
-        <v>85.04000000000001</v>
+        <v>58.93</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
       <c r="I605" s="6" t="inlineStr"/>
-      <c r="J605" s="6" t="inlineStr"/>
+      <c r="J605" s="8" t="n">
+        <v>0.4139</v>
+      </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M605" s="6" t="inlineStr"/>
@@ -26610,40 +26616,34 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>140.3</v>
+        <v>19.01</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>0.0316</v>
+        <v>-0.0031</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>2340000</v>
-      </c>
-      <c r="E606" s="4" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>62410000</v>
+      </c>
+      <c r="E606" s="2" t="inlineStr"/>
       <c r="F606" s="3" t="n">
-        <v>46.39</v>
+        <v>29.07</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
-      <c r="I606" s="4" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J606" s="4" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I606" s="2" t="inlineStr"/>
+      <c r="J606" s="2" t="inlineStr"/>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L606" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M606" s="2" t="inlineStr"/>
@@ -26651,21 +26651,21 @@
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>189.5</v>
+        <v>21.46</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>0.0706</v>
+        <v>0.0999</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>18010000</v>
+        <v>86600000</v>
       </c>
       <c r="E607" s="6" t="inlineStr"/>
       <c r="F607" s="7" t="n">
-        <v>44.94</v>
+        <v>68.67</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
@@ -26673,12 +26673,12 @@
       <c r="J607" s="6" t="inlineStr"/>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M607" s="6" t="inlineStr"/>
@@ -26705,7 +26705,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>01.05.2026 08:30</t>
+          <t>01.05.2026 09:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-05-01.xlsx
+++ b/data/bist_screener_2026-05-01.xlsx
@@ -25787,38 +25787,34 @@
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B583" s="7" t="n">
-        <v>65.34999999999999</v>
+        <v>27.16</v>
       </c>
       <c r="C583" s="8" t="n">
-        <v>-0.0106</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D583" s="9" t="n">
-        <v>665180</v>
-      </c>
-      <c r="E583" s="8" t="n">
-        <v>0.3695000000000001</v>
-      </c>
+        <v>17070000</v>
+      </c>
+      <c r="E583" s="6" t="inlineStr"/>
       <c r="F583" s="7" t="n">
-        <v>58.93</v>
+        <v>63.67</v>
       </c>
       <c r="G583" s="6" t="inlineStr"/>
       <c r="H583" s="6" t="inlineStr"/>
       <c r="I583" s="6" t="inlineStr"/>
-      <c r="J583" s="8" t="n">
-        <v>0.4139</v>
-      </c>
+      <c r="J583" s="6" t="inlineStr"/>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M583" s="6" t="inlineStr"/>
@@ -25826,21 +25822,21 @@
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>162.5</v>
+        <v>17.01</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>0.0037</v>
+        <v>-0.0053</v>
       </c>
       <c r="D584" s="5" t="n">
-        <v>6940000</v>
+        <v>72710000</v>
       </c>
       <c r="E584" s="2" t="inlineStr"/>
       <c r="F584" s="3" t="n">
-        <v>55.44</v>
+        <v>52.78</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
@@ -25848,12 +25844,12 @@
       <c r="J584" s="2" t="inlineStr"/>
       <c r="K584" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L584" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M584" s="2" t="inlineStr"/>
@@ -25861,112 +25857,106 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>33.06</v>
+        <v>78.5</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>0.0024</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>4310000</v>
-      </c>
-      <c r="E585" s="6" t="inlineStr"/>
+        <v>34400</v>
+      </c>
+      <c r="E585" s="8" t="n">
+        <v>0.58</v>
+      </c>
       <c r="F585" s="7" t="n">
-        <v>48.1</v>
+        <v>43.41</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
-      <c r="I585" s="6" t="inlineStr"/>
-      <c r="J585" s="6" t="inlineStr"/>
+      <c r="I585" s="8" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J585" s="8" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
-        </is>
-      </c>
-      <c r="L585" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L585" s="6" t="inlineStr"/>
       <c r="M585" s="6" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>78.5</v>
+        <v>189.5</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>0.07980000000000001</v>
+        <v>0.0706</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>34400</v>
-      </c>
-      <c r="E586" s="4" t="n">
-        <v>0.58</v>
-      </c>
+        <v>18010000</v>
+      </c>
+      <c r="E586" s="2" t="inlineStr"/>
       <c r="F586" s="3" t="n">
-        <v>43.41</v>
+        <v>44.94</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
-      <c r="I586" s="4" t="n">
-        <v>-9.409700000000001</v>
-      </c>
-      <c r="J586" s="4" t="n">
-        <v>-4.155</v>
-      </c>
+      <c r="I586" s="2" t="inlineStr"/>
+      <c r="J586" s="2" t="inlineStr"/>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L586" s="2" t="inlineStr"/>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
+      <c r="L586" s="2" t="inlineStr">
+        <is>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+        </is>
+      </c>
       <c r="M586" s="2" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>7.62</v>
+        <v>21.46</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>0.09960000000000001</v>
+        <v>0.0999</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>122010000</v>
-      </c>
-      <c r="E587" s="8" t="n">
-        <v>0.1672</v>
-      </c>
+        <v>86600000</v>
+      </c>
+      <c r="E587" s="6" t="inlineStr"/>
       <c r="F587" s="7" t="n">
-        <v>70.51000000000001</v>
+        <v>68.67</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
-      <c r="I587" s="8" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J587" s="8" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I587" s="6" t="inlineStr"/>
+      <c r="J587" s="6" t="inlineStr"/>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M587" s="6" t="inlineStr"/>
@@ -25974,23 +25964,21 @@
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>28.48</v>
+        <v>19.01</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>-0.0031</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>18800000</v>
-      </c>
-      <c r="E588" s="4" t="n">
-        <v>0.2667</v>
-      </c>
+        <v>62410000</v>
+      </c>
+      <c r="E588" s="2" t="inlineStr"/>
       <c r="F588" s="3" t="n">
-        <v>49.66</v>
+        <v>29.07</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
@@ -25998,12 +25986,12 @@
       <c r="J588" s="2" t="inlineStr"/>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L588" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M588" s="2" t="inlineStr"/>
@@ -26011,23 +25999,21 @@
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>242</v>
+        <v>33.06</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>0</v>
+        <v>0.0024</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>7420</v>
-      </c>
-      <c r="E589" s="8" t="n">
-        <v>0.2578</v>
-      </c>
+        <v>4310000</v>
+      </c>
+      <c r="E589" s="6" t="inlineStr"/>
       <c r="F589" s="7" t="n">
-        <v>41.93</v>
+        <v>48.1</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
@@ -26035,32 +26021,34 @@
       <c r="J589" s="6" t="inlineStr"/>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L589" s="6" t="inlineStr"/>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
+      <c r="L589" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+        </is>
+      </c>
       <c r="M589" s="6" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>5.68</v>
+        <v>13.98</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>-0.0018</v>
+        <v>0.0138</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>56180000</v>
-      </c>
-      <c r="E590" s="4" t="n">
-        <v>0.8667</v>
-      </c>
+        <v>32400000</v>
+      </c>
+      <c r="E590" s="2" t="inlineStr"/>
       <c r="F590" s="3" t="n">
-        <v>85.04000000000001</v>
+        <v>54.25</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
@@ -26068,12 +26056,12 @@
       <c r="J590" s="2" t="inlineStr"/>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L590" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M590" s="2" t="inlineStr"/>
@@ -26081,34 +26069,40 @@
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>GRNYO</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>13.98</v>
+        <v>17.94</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>0.0138</v>
+        <v>0.0022</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>32400000</v>
-      </c>
-      <c r="E591" s="6" t="inlineStr"/>
+        <v>1260000</v>
+      </c>
+      <c r="E591" s="8" t="n">
+        <v>0.9869</v>
+      </c>
       <c r="F591" s="7" t="n">
-        <v>54.25</v>
+        <v>58.1</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="6" t="inlineStr"/>
-      <c r="J591" s="6" t="inlineStr"/>
+      <c r="I591" s="8" t="n">
+        <v>-0.2446</v>
+      </c>
+      <c r="J591" s="8" t="n">
+        <v>0.3246</v>
+      </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M591" s="6" t="inlineStr"/>
@@ -26116,40 +26110,34 @@
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>2.68</v>
+        <v>162.5</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>0</v>
+        <v>0.0037</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>90400000</v>
-      </c>
-      <c r="E592" s="4" t="n">
-        <v>0.7119</v>
-      </c>
+        <v>6940000</v>
+      </c>
+      <c r="E592" s="2" t="inlineStr"/>
       <c r="F592" s="3" t="n">
-        <v>42.36</v>
+        <v>55.44</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
-      <c r="I592" s="4" t="n">
-        <v>-191.6342</v>
-      </c>
-      <c r="J592" s="4" t="n">
-        <v>-0.8093</v>
-      </c>
+      <c r="I592" s="2" t="inlineStr"/>
+      <c r="J592" s="2" t="inlineStr"/>
       <c r="K592" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L592" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M592" s="2" t="inlineStr"/>
@@ -26157,34 +26145,42 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>2.94</v>
+        <v>17.05</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>0.09699999999999999</v>
+        <v>0.0137</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>240000000</v>
-      </c>
-      <c r="E593" s="6" t="inlineStr"/>
+        <v>11180000</v>
+      </c>
+      <c r="E593" s="8" t="n">
+        <v>0.9246</v>
+      </c>
       <c r="F593" s="7" t="n">
-        <v>55.79</v>
-      </c>
-      <c r="G593" s="6" t="inlineStr"/>
+        <v>46.47</v>
+      </c>
+      <c r="G593" s="7" t="n">
+        <v>161.15</v>
+      </c>
       <c r="H593" s="6" t="inlineStr"/>
-      <c r="I593" s="6" t="inlineStr"/>
-      <c r="J593" s="6" t="inlineStr"/>
+      <c r="I593" s="8" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="J593" s="8" t="n">
+        <v>-10.3171</v>
+      </c>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
         </is>
       </c>
       <c r="M593" s="6" t="inlineStr"/>
@@ -26192,21 +26188,21 @@
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>21.46</v>
+        <v>2.94</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>0.0999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>86600000</v>
+        <v>240000000</v>
       </c>
       <c r="E594" s="2" t="inlineStr"/>
       <c r="F594" s="3" t="n">
-        <v>68.67</v>
+        <v>55.79</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
@@ -26214,12 +26210,12 @@
       <c r="J594" s="2" t="inlineStr"/>
       <c r="K594" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L594" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M594" s="2" t="inlineStr"/>
@@ -26227,122 +26223,124 @@
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>189.5</v>
+        <v>7</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>0.0706</v>
+        <v>-0.0182</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>18010000</v>
-      </c>
-      <c r="E595" s="6" t="inlineStr"/>
+        <v>542950</v>
+      </c>
+      <c r="E595" s="8" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F595" s="7" t="n">
-        <v>44.94</v>
+        <v>37.31</v>
       </c>
       <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
-      <c r="I595" s="6" t="inlineStr"/>
-      <c r="J595" s="6" t="inlineStr"/>
+      <c r="I595" s="8" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J595" s="8" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
-        </is>
-      </c>
-      <c r="L595" s="6" t="inlineStr">
-        <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L595" s="6" t="inlineStr"/>
       <c r="M595" s="6" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>6.16</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>0.0016</v>
+        <v>-0.0106</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>7690000</v>
-      </c>
-      <c r="E596" s="2" t="inlineStr"/>
+        <v>665180</v>
+      </c>
+      <c r="E596" s="4" t="n">
+        <v>0.3695000000000001</v>
+      </c>
       <c r="F596" s="3" t="n">
-        <v>62.72</v>
+        <v>58.93</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
       <c r="I596" s="2" t="inlineStr"/>
-      <c r="J596" s="2" t="inlineStr"/>
+      <c r="J596" s="4" t="n">
+        <v>0.4139</v>
+      </c>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L596" s="2" t="inlineStr"/>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
+      <c r="L596" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+        </is>
+      </c>
       <c r="M596" s="2" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>19.01</v>
+        <v>80.53</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>-0.0031</v>
+        <v>0.0176</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>62410000</v>
+        <v>10440000</v>
       </c>
       <c r="E597" s="6" t="inlineStr"/>
       <c r="F597" s="7" t="n">
-        <v>29.07</v>
+        <v>43.51</v>
       </c>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
       <c r="I597" s="6" t="inlineStr"/>
       <c r="J597" s="6" t="inlineStr"/>
-      <c r="K597" s="6" t="inlineStr">
-        <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L597" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
-        </is>
-      </c>
+      <c r="K597" s="6" t="inlineStr"/>
+      <c r="L597" s="6" t="inlineStr"/>
       <c r="M597" s="6" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>40.58</v>
+        <v>6.16</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>-0.0117</v>
-      </c>
-      <c r="D598" s="3" t="n">
-        <v>8380000.000000001</v>
+        <v>0.0016</v>
+      </c>
+      <c r="D598" s="5" t="n">
+        <v>7690000</v>
       </c>
       <c r="E598" s="2" t="inlineStr"/>
       <c r="F598" s="3" t="n">
-        <v>54.32</v>
+        <v>62.72</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
@@ -26350,61 +26348,67 @@
       <c r="J598" s="2" t="inlineStr"/>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
-        </is>
-      </c>
-      <c r="L598" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L598" s="2" t="inlineStr"/>
       <c r="M598" s="2" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>80.53</v>
+        <v>28.48</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>0.0176</v>
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>10440000</v>
-      </c>
-      <c r="E599" s="6" t="inlineStr"/>
+        <v>18800000</v>
+      </c>
+      <c r="E599" s="8" t="n">
+        <v>0.2667</v>
+      </c>
       <c r="F599" s="7" t="n">
-        <v>43.51</v>
+        <v>49.66</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
       <c r="I599" s="6" t="inlineStr"/>
       <c r="J599" s="6" t="inlineStr"/>
-      <c r="K599" s="6" t="inlineStr"/>
-      <c r="L599" s="6" t="inlineStr"/>
+      <c r="K599" s="6" t="inlineStr">
+        <is>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
+      <c r="L599" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M599" s="6" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>27.16</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>0.09960000000000001</v>
+        <v>0.0071</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>17070000</v>
+        <v>255560</v>
       </c>
       <c r="E600" s="2" t="inlineStr"/>
       <c r="F600" s="3" t="n">
-        <v>63.67</v>
+        <v>11.8</v>
       </c>
       <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
@@ -26412,47 +26416,49 @@
       <c r="J600" s="2" t="inlineStr"/>
       <c r="K600" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
-        </is>
-      </c>
-      <c r="L600" s="2" t="inlineStr">
-        <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L600" s="2" t="inlineStr"/>
       <c r="M600" s="2" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>17.01</v>
+        <v>2.68</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>-0.0053</v>
+        <v>0</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>72710000</v>
-      </c>
-      <c r="E601" s="6" t="inlineStr"/>
+        <v>90400000</v>
+      </c>
+      <c r="E601" s="8" t="n">
+        <v>0.7119</v>
+      </c>
       <c r="F601" s="7" t="n">
-        <v>52.78</v>
+        <v>42.36</v>
       </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
-      <c r="I601" s="6" t="inlineStr"/>
-      <c r="J601" s="6" t="inlineStr"/>
+      <c r="I601" s="8" t="n">
+        <v>-191.6342</v>
+      </c>
+      <c r="J601" s="8" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M601" s="6" t="inlineStr"/>
@@ -26460,40 +26466,34 @@
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>GRNYO</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>17.94</v>
+        <v>40.58</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="D602" s="5" t="n">
-        <v>1260000</v>
-      </c>
-      <c r="E602" s="4" t="n">
-        <v>0.9869</v>
-      </c>
+        <v>-0.0117</v>
+      </c>
+      <c r="D602" s="3" t="n">
+        <v>8380000.000000001</v>
+      </c>
+      <c r="E602" s="2" t="inlineStr"/>
       <c r="F602" s="3" t="n">
-        <v>58.1</v>
+        <v>54.32</v>
       </c>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
-      <c r="I602" s="4" t="n">
-        <v>-0.2446</v>
-      </c>
-      <c r="J602" s="4" t="n">
-        <v>0.3246</v>
-      </c>
+      <c r="I602" s="2" t="inlineStr"/>
+      <c r="J602" s="2" t="inlineStr"/>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L602" s="2" t="inlineStr">
         <is>
-          <t>BIST MENKUL KIYM YO</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M602" s="2" t="inlineStr"/>
@@ -26501,21 +26501,23 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>92.09999999999999</v>
+        <v>5.68</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>0.0071</v>
+        <v>-0.0018</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>255560</v>
-      </c>
-      <c r="E603" s="6" t="inlineStr"/>
+        <v>56180000</v>
+      </c>
+      <c r="E603" s="8" t="n">
+        <v>0.8667</v>
+      </c>
       <c r="F603" s="7" t="n">
-        <v>11.8</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
@@ -26526,27 +26528,33 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L603" s="6" t="inlineStr"/>
+      <c r="L603" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+        </is>
+      </c>
       <c r="M603" s="6" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>38.72</v>
+        <v>242</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>0.0031</v>
+        <v>0</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>10070000</v>
-      </c>
-      <c r="E604" s="2" t="inlineStr"/>
+        <v>7420</v>
+      </c>
+      <c r="E604" s="4" t="n">
+        <v>0.2578</v>
+      </c>
       <c r="F604" s="3" t="n">
-        <v>48.93</v>
+        <v>41.93</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
@@ -26554,55 +26562,49 @@
       <c r="J604" s="2" t="inlineStr"/>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
-        </is>
-      </c>
-      <c r="L604" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L604" s="2" t="inlineStr"/>
       <c r="M604" s="2" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>17.05</v>
+        <v>140.3</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>0.0137</v>
+        <v>0.0316</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>11180000</v>
+        <v>2340000</v>
       </c>
       <c r="E605" s="8" t="n">
-        <v>0.9246</v>
+        <v>0.1071</v>
       </c>
       <c r="F605" s="7" t="n">
-        <v>46.47</v>
-      </c>
-      <c r="G605" s="7" t="n">
-        <v>161.15</v>
-      </c>
+        <v>46.39</v>
+      </c>
+      <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
       <c r="I605" s="8" t="n">
-        <v>0.0028</v>
+        <v>-3.6635</v>
       </c>
       <c r="J605" s="8" t="n">
-        <v>-10.3171</v>
+        <v>-0.4897</v>
       </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M605" s="6" t="inlineStr"/>
@@ -26610,40 +26612,34 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>140.3</v>
+        <v>38.72</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>0.0316</v>
+        <v>0.0031</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>2340000</v>
-      </c>
-      <c r="E606" s="4" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>10070000</v>
+      </c>
+      <c r="E606" s="2" t="inlineStr"/>
       <c r="F606" s="3" t="n">
-        <v>46.39</v>
+        <v>48.93</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
-      <c r="I606" s="4" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J606" s="4" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I606" s="2" t="inlineStr"/>
+      <c r="J606" s="2" t="inlineStr"/>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L606" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M606" s="2" t="inlineStr"/>
@@ -26651,38 +26647,42 @@
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>7</v>
+        <v>7.62</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>-0.0182</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>542950</v>
+        <v>122010000</v>
       </c>
       <c r="E607" s="8" t="n">
-        <v>0.95</v>
+        <v>0.1672</v>
       </c>
       <c r="F607" s="7" t="n">
-        <v>37.31</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
       <c r="I607" s="8" t="n">
-        <v>-23.6291</v>
+        <v>-5.3262</v>
       </c>
       <c r="J607" s="8" t="n">
-        <v>-0.4678</v>
+        <v>-4.2562</v>
       </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L607" s="6" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L607" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+        </is>
+      </c>
       <c r="M607" s="6" t="inlineStr"/>
     </row>
   </sheetData>
@@ -26707,7 +26707,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>01.05.2026 10:30</t>
+          <t>01.05.2026 11:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-05-01.xlsx
+++ b/data/bist_screener_2026-05-01.xlsx
@@ -25787,34 +25787,40 @@
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B583" s="7" t="n">
-        <v>27.16</v>
+        <v>2.68</v>
       </c>
       <c r="C583" s="8" t="n">
-        <v>0.09960000000000001</v>
+        <v>0</v>
       </c>
       <c r="D583" s="9" t="n">
-        <v>17070000</v>
-      </c>
-      <c r="E583" s="6" t="inlineStr"/>
+        <v>90400000</v>
+      </c>
+      <c r="E583" s="8" t="n">
+        <v>0.7119</v>
+      </c>
       <c r="F583" s="7" t="n">
-        <v>63.67</v>
+        <v>42.36</v>
       </c>
       <c r="G583" s="6" t="inlineStr"/>
       <c r="H583" s="6" t="inlineStr"/>
-      <c r="I583" s="6" t="inlineStr"/>
-      <c r="J583" s="6" t="inlineStr"/>
+      <c r="I583" s="8" t="n">
+        <v>-191.6342</v>
+      </c>
+      <c r="J583" s="8" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M583" s="6" t="inlineStr"/>
@@ -25822,34 +25828,38 @@
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>17.01</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>-0.0053</v>
+        <v>-0.0106</v>
       </c>
       <c r="D584" s="5" t="n">
-        <v>72710000</v>
-      </c>
-      <c r="E584" s="2" t="inlineStr"/>
+        <v>665180</v>
+      </c>
+      <c r="E584" s="4" t="n">
+        <v>0.3695000000000001</v>
+      </c>
       <c r="F584" s="3" t="n">
-        <v>52.78</v>
+        <v>58.93</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
       <c r="I584" s="2" t="inlineStr"/>
-      <c r="J584" s="2" t="inlineStr"/>
+      <c r="J584" s="4" t="n">
+        <v>0.4139</v>
+      </c>
       <c r="K584" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L584" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M584" s="2" t="inlineStr"/>
@@ -25857,58 +25867,64 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>78.5</v>
+        <v>17.05</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>0.07980000000000001</v>
+        <v>0.0137</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>34400</v>
+        <v>11180000</v>
       </c>
       <c r="E585" s="8" t="n">
-        <v>0.58</v>
+        <v>0.9246</v>
       </c>
       <c r="F585" s="7" t="n">
-        <v>43.41</v>
-      </c>
-      <c r="G585" s="6" t="inlineStr"/>
+        <v>46.47</v>
+      </c>
+      <c r="G585" s="7" t="n">
+        <v>161.15</v>
+      </c>
       <c r="H585" s="6" t="inlineStr"/>
       <c r="I585" s="8" t="n">
-        <v>-9.409700000000001</v>
+        <v>0.0028</v>
       </c>
       <c r="J585" s="8" t="n">
-        <v>-4.155</v>
+        <v>-10.3171</v>
       </c>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L585" s="6" t="inlineStr"/>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
+      <c r="L585" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+        </is>
+      </c>
       <c r="M585" s="6" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>189.5</v>
+        <v>162.5</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>0.0706</v>
+        <v>0.0037</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>18010000</v>
+        <v>6940000</v>
       </c>
       <c r="E586" s="2" t="inlineStr"/>
       <c r="F586" s="3" t="n">
-        <v>44.94</v>
+        <v>55.44</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
@@ -25916,12 +25932,12 @@
       <c r="J586" s="2" t="inlineStr"/>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L586" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M586" s="2" t="inlineStr"/>
@@ -25929,56 +25945,60 @@
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>21.46</v>
+        <v>78.5</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>0.0999</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>86600000</v>
-      </c>
-      <c r="E587" s="6" t="inlineStr"/>
+        <v>34400</v>
+      </c>
+      <c r="E587" s="8" t="n">
+        <v>0.58</v>
+      </c>
       <c r="F587" s="7" t="n">
-        <v>68.67</v>
+        <v>43.41</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
-      <c r="I587" s="6" t="inlineStr"/>
-      <c r="J587" s="6" t="inlineStr"/>
+      <c r="I587" s="8" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J587" s="8" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
-        </is>
-      </c>
-      <c r="L587" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L587" s="6" t="inlineStr"/>
       <c r="M587" s="6" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>19.01</v>
+        <v>5.68</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>-0.0031</v>
+        <v>-0.0018</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>62410000</v>
-      </c>
-      <c r="E588" s="2" t="inlineStr"/>
+        <v>56180000</v>
+      </c>
+      <c r="E588" s="4" t="n">
+        <v>0.8667</v>
+      </c>
       <c r="F588" s="3" t="n">
-        <v>29.07</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
@@ -25991,7 +26011,7 @@
       </c>
       <c r="L588" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M588" s="2" t="inlineStr"/>
@@ -25999,21 +26019,21 @@
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>33.06</v>
+        <v>6.16</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>0.0024</v>
+        <v>0.0016</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>4310000</v>
+        <v>7690000</v>
       </c>
       <c r="E589" s="6" t="inlineStr"/>
       <c r="F589" s="7" t="n">
-        <v>48.1</v>
+        <v>62.72</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
@@ -26021,14 +26041,10 @@
       <c r="J589" s="6" t="inlineStr"/>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
-        </is>
-      </c>
-      <c r="L589" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L589" s="6" t="inlineStr"/>
       <c r="M589" s="6" t="inlineStr"/>
     </row>
     <row r="590">
@@ -26069,62 +26085,48 @@
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>GRNYO</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>17.94</v>
+        <v>80.53</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>0.0022</v>
+        <v>0.0176</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>1260000</v>
-      </c>
-      <c r="E591" s="8" t="n">
-        <v>0.9869</v>
-      </c>
+        <v>10440000</v>
+      </c>
+      <c r="E591" s="6" t="inlineStr"/>
       <c r="F591" s="7" t="n">
-        <v>58.1</v>
+        <v>43.51</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="8" t="n">
-        <v>-0.2446</v>
-      </c>
-      <c r="J591" s="8" t="n">
-        <v>0.3246</v>
-      </c>
-      <c r="K591" s="6" t="inlineStr">
-        <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L591" s="6" t="inlineStr">
-        <is>
-          <t>BIST MENKUL KIYM YO</t>
-        </is>
-      </c>
+      <c r="I591" s="6" t="inlineStr"/>
+      <c r="J591" s="6" t="inlineStr"/>
+      <c r="K591" s="6" t="inlineStr"/>
+      <c r="L591" s="6" t="inlineStr"/>
       <c r="M591" s="6" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>162.5</v>
+        <v>17.01</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>0.0037</v>
+        <v>-0.0053</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>6940000</v>
+        <v>72710000</v>
       </c>
       <c r="E592" s="2" t="inlineStr"/>
       <c r="F592" s="3" t="n">
-        <v>55.44</v>
+        <v>52.78</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
@@ -26132,12 +26134,12 @@
       <c r="J592" s="2" t="inlineStr"/>
       <c r="K592" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L592" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M592" s="2" t="inlineStr"/>
@@ -26145,42 +26147,34 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>17.05</v>
+        <v>2.94</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>0.0137</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>11180000</v>
-      </c>
-      <c r="E593" s="8" t="n">
-        <v>0.9246</v>
-      </c>
+        <v>240000000</v>
+      </c>
+      <c r="E593" s="6" t="inlineStr"/>
       <c r="F593" s="7" t="n">
-        <v>46.47</v>
-      </c>
-      <c r="G593" s="7" t="n">
-        <v>161.15</v>
-      </c>
+        <v>55.79</v>
+      </c>
+      <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
-      <c r="I593" s="8" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J593" s="8" t="n">
-        <v>-10.3171</v>
-      </c>
+      <c r="I593" s="6" t="inlineStr"/>
+      <c r="J593" s="6" t="inlineStr"/>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M593" s="6" t="inlineStr"/>
@@ -26188,21 +26182,23 @@
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>2.94</v>
+        <v>242</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>0.09699999999999999</v>
+        <v>0</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>240000000</v>
-      </c>
-      <c r="E594" s="2" t="inlineStr"/>
+        <v>7420</v>
+      </c>
+      <c r="E594" s="4" t="n">
+        <v>0.2578</v>
+      </c>
       <c r="F594" s="3" t="n">
-        <v>55.79</v>
+        <v>41.93</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
@@ -26210,88 +26206,90 @@
       <c r="J594" s="2" t="inlineStr"/>
       <c r="K594" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L594" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L594" s="2" t="inlineStr"/>
       <c r="M594" s="2" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>GRNYO</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>7</v>
+        <v>17.94</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>-0.0182</v>
+        <v>0.0022</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>542950</v>
+        <v>1260000</v>
       </c>
       <c r="E595" s="8" t="n">
-        <v>0.95</v>
+        <v>0.9869</v>
       </c>
       <c r="F595" s="7" t="n">
-        <v>37.31</v>
+        <v>58.1</v>
       </c>
       <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
       <c r="I595" s="8" t="n">
-        <v>-23.6291</v>
+        <v>-0.2446</v>
       </c>
       <c r="J595" s="8" t="n">
-        <v>-0.4678</v>
+        <v>0.3246</v>
       </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L595" s="6" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L595" s="6" t="inlineStr">
+        <is>
+          <t>BIST MENKUL KIYM YO</t>
+        </is>
+      </c>
       <c r="M595" s="6" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>65.34999999999999</v>
+        <v>7.62</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>-0.0106</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>665180</v>
+        <v>122010000</v>
       </c>
       <c r="E596" s="4" t="n">
-        <v>0.3695000000000001</v>
+        <v>0.1672</v>
       </c>
       <c r="F596" s="3" t="n">
-        <v>58.93</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
-      <c r="I596" s="2" t="inlineStr"/>
+      <c r="I596" s="4" t="n">
+        <v>-5.3262</v>
+      </c>
       <c r="J596" s="4" t="n">
-        <v>0.4139</v>
+        <v>-4.2562</v>
       </c>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L596" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M596" s="2" t="inlineStr"/>
@@ -26299,48 +26297,62 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>80.53</v>
+        <v>140.3</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>0.0176</v>
+        <v>0.0316</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>10440000</v>
-      </c>
-      <c r="E597" s="6" t="inlineStr"/>
+        <v>2340000</v>
+      </c>
+      <c r="E597" s="8" t="n">
+        <v>0.1071</v>
+      </c>
       <c r="F597" s="7" t="n">
-        <v>43.51</v>
+        <v>46.39</v>
       </c>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
-      <c r="I597" s="6" t="inlineStr"/>
-      <c r="J597" s="6" t="inlineStr"/>
-      <c r="K597" s="6" t="inlineStr"/>
-      <c r="L597" s="6" t="inlineStr"/>
+      <c r="I597" s="8" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="J597" s="8" t="n">
+        <v>-0.4897</v>
+      </c>
+      <c r="K597" s="6" t="inlineStr">
+        <is>
+          <t>Perakende satış</t>
+        </is>
+      </c>
+      <c r="L597" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+        </is>
+      </c>
       <c r="M597" s="6" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>6.16</v>
+        <v>189.5</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>0.0016</v>
+        <v>0.0706</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>7690000</v>
+        <v>18010000</v>
       </c>
       <c r="E598" s="2" t="inlineStr"/>
       <c r="F598" s="3" t="n">
-        <v>62.72</v>
+        <v>44.94</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
@@ -26348,32 +26360,34 @@
       <c r="J598" s="2" t="inlineStr"/>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L598" s="2" t="inlineStr"/>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
+      <c r="L598" s="2" t="inlineStr">
+        <is>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+        </is>
+      </c>
       <c r="M598" s="2" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>28.48</v>
+        <v>38.72</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>0.0031</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>18800000</v>
-      </c>
-      <c r="E599" s="8" t="n">
-        <v>0.2667</v>
-      </c>
+        <v>10070000</v>
+      </c>
+      <c r="E599" s="6" t="inlineStr"/>
       <c r="F599" s="7" t="n">
-        <v>49.66</v>
+        <v>48.93</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
@@ -26381,12 +26395,12 @@
       <c r="J599" s="6" t="inlineStr"/>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M599" s="6" t="inlineStr"/>
@@ -26425,40 +26439,36 @@
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>2.68</v>
+        <v>28.48</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>0</v>
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>90400000</v>
+        <v>18800000</v>
       </c>
       <c r="E601" s="8" t="n">
-        <v>0.7119</v>
+        <v>0.2667</v>
       </c>
       <c r="F601" s="7" t="n">
-        <v>42.36</v>
+        <v>49.66</v>
       </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
-      <c r="I601" s="8" t="n">
-        <v>-191.6342</v>
-      </c>
-      <c r="J601" s="8" t="n">
-        <v>-0.8093</v>
-      </c>
+      <c r="I601" s="6" t="inlineStr"/>
+      <c r="J601" s="6" t="inlineStr"/>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M601" s="6" t="inlineStr"/>
@@ -26501,23 +26511,21 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>5.68</v>
+        <v>19.01</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>-0.0018</v>
+        <v>-0.0031</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>56180000</v>
-      </c>
-      <c r="E603" s="8" t="n">
-        <v>0.8667</v>
-      </c>
+        <v>62410000</v>
+      </c>
+      <c r="E603" s="6" t="inlineStr"/>
       <c r="F603" s="7" t="n">
-        <v>85.04000000000001</v>
+        <v>29.07</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
@@ -26530,7 +26538,7 @@
       </c>
       <c r="L603" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M603" s="6" t="inlineStr"/>
@@ -26538,28 +26546,32 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>242</v>
+        <v>7</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>0</v>
+        <v>-0.0182</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>7420</v>
+        <v>542950</v>
       </c>
       <c r="E604" s="4" t="n">
-        <v>0.2578</v>
+        <v>0.95</v>
       </c>
       <c r="F604" s="3" t="n">
-        <v>41.93</v>
+        <v>37.31</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
-      <c r="I604" s="2" t="inlineStr"/>
-      <c r="J604" s="2" t="inlineStr"/>
+      <c r="I604" s="4" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J604" s="4" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K604" s="2" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -26571,40 +26583,34 @@
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>140.3</v>
+        <v>33.06</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>0.0316</v>
+        <v>0.0024</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>2340000</v>
-      </c>
-      <c r="E605" s="8" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>4310000</v>
+      </c>
+      <c r="E605" s="6" t="inlineStr"/>
       <c r="F605" s="7" t="n">
-        <v>46.39</v>
+        <v>48.1</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
-      <c r="I605" s="8" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J605" s="8" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I605" s="6" t="inlineStr"/>
+      <c r="J605" s="6" t="inlineStr"/>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M605" s="6" t="inlineStr"/>
@@ -26612,21 +26618,21 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>38.72</v>
+        <v>27.16</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>0.0031</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>10070000</v>
+        <v>17070000</v>
       </c>
       <c r="E606" s="2" t="inlineStr"/>
       <c r="F606" s="3" t="n">
-        <v>48.93</v>
+        <v>63.67</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
@@ -26634,12 +26640,12 @@
       <c r="J606" s="2" t="inlineStr"/>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L606" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M606" s="2" t="inlineStr"/>
@@ -26647,40 +26653,34 @@
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>7.62</v>
+        <v>21.46</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>0.09960000000000001</v>
+        <v>0.0999</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>122010000</v>
-      </c>
-      <c r="E607" s="8" t="n">
-        <v>0.1672</v>
-      </c>
+        <v>86600000</v>
+      </c>
+      <c r="E607" s="6" t="inlineStr"/>
       <c r="F607" s="7" t="n">
-        <v>70.51000000000001</v>
+        <v>68.67</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
-      <c r="I607" s="8" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J607" s="8" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I607" s="6" t="inlineStr"/>
+      <c r="J607" s="6" t="inlineStr"/>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M607" s="6" t="inlineStr"/>
@@ -26707,7 +26707,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>01.05.2026 11:30</t>
+          <t>01.05.2026 12:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-05-01.xlsx
+++ b/data/bist_screener_2026-05-01.xlsx
@@ -25787,40 +25787,36 @@
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B583" s="7" t="n">
-        <v>2.68</v>
+        <v>5.68</v>
       </c>
       <c r="C583" s="8" t="n">
-        <v>0</v>
+        <v>-0.0018</v>
       </c>
       <c r="D583" s="9" t="n">
-        <v>90400000</v>
+        <v>56180000</v>
       </c>
       <c r="E583" s="8" t="n">
-        <v>0.7119</v>
+        <v>0.8667</v>
       </c>
       <c r="F583" s="7" t="n">
-        <v>42.36</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="G583" s="6" t="inlineStr"/>
       <c r="H583" s="6" t="inlineStr"/>
-      <c r="I583" s="8" t="n">
-        <v>-191.6342</v>
-      </c>
-      <c r="J583" s="8" t="n">
-        <v>-0.8093</v>
-      </c>
+      <c r="I583" s="6" t="inlineStr"/>
+      <c r="J583" s="6" t="inlineStr"/>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M583" s="6" t="inlineStr"/>
@@ -25828,81 +25824,69 @@
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>65.34999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>-0.0106</v>
+        <v>0.0071</v>
       </c>
       <c r="D584" s="5" t="n">
-        <v>665180</v>
-      </c>
-      <c r="E584" s="4" t="n">
-        <v>0.3695000000000001</v>
-      </c>
+        <v>255560</v>
+      </c>
+      <c r="E584" s="2" t="inlineStr"/>
       <c r="F584" s="3" t="n">
-        <v>58.93</v>
+        <v>11.8</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
       <c r="I584" s="2" t="inlineStr"/>
-      <c r="J584" s="4" t="n">
-        <v>0.4139</v>
-      </c>
+      <c r="J584" s="2" t="inlineStr"/>
       <c r="K584" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
-        </is>
-      </c>
-      <c r="L584" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L584" s="2" t="inlineStr"/>
       <c r="M584" s="2" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>17.05</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>0.0137</v>
+        <v>-0.0106</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>11180000</v>
+        <v>665180</v>
       </c>
       <c r="E585" s="8" t="n">
-        <v>0.9246</v>
+        <v>0.3695000000000001</v>
       </c>
       <c r="F585" s="7" t="n">
-        <v>46.47</v>
-      </c>
-      <c r="G585" s="7" t="n">
-        <v>161.15</v>
-      </c>
+        <v>58.93</v>
+      </c>
+      <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
-      <c r="I585" s="8" t="n">
-        <v>0.0028</v>
-      </c>
+      <c r="I585" s="6" t="inlineStr"/>
       <c r="J585" s="8" t="n">
-        <v>-10.3171</v>
+        <v>0.4139</v>
       </c>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M585" s="6" t="inlineStr"/>
@@ -25910,130 +25894,122 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>162.5</v>
+        <v>80.53</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>0.0037</v>
+        <v>0.0176</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>6940000</v>
+        <v>10440000</v>
       </c>
       <c r="E586" s="2" t="inlineStr"/>
       <c r="F586" s="3" t="n">
-        <v>55.44</v>
+        <v>43.51</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
       <c r="I586" s="2" t="inlineStr"/>
       <c r="J586" s="2" t="inlineStr"/>
-      <c r="K586" s="2" t="inlineStr">
-        <is>
-          <t>Ticari hizmetler</t>
-        </is>
-      </c>
-      <c r="L586" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
-        </is>
-      </c>
+      <c r="K586" s="2" t="inlineStr"/>
+      <c r="L586" s="2" t="inlineStr"/>
       <c r="M586" s="2" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>78.5</v>
+        <v>17.01</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>0.07980000000000001</v>
+        <v>-0.0053</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>34400</v>
-      </c>
-      <c r="E587" s="8" t="n">
-        <v>0.58</v>
-      </c>
+        <v>72710000</v>
+      </c>
+      <c r="E587" s="6" t="inlineStr"/>
       <c r="F587" s="7" t="n">
-        <v>43.41</v>
+        <v>52.78</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
-      <c r="I587" s="8" t="n">
-        <v>-9.409700000000001</v>
-      </c>
-      <c r="J587" s="8" t="n">
-        <v>-4.155</v>
-      </c>
+      <c r="I587" s="6" t="inlineStr"/>
+      <c r="J587" s="6" t="inlineStr"/>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L587" s="6" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L587" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M587" s="6" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>5.68</v>
+        <v>78.5</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>-0.0018</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>56180000</v>
+        <v>34400</v>
       </c>
       <c r="E588" s="4" t="n">
-        <v>0.8667</v>
+        <v>0.58</v>
       </c>
       <c r="F588" s="3" t="n">
-        <v>85.04000000000001</v>
+        <v>43.41</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
-      <c r="I588" s="2" t="inlineStr"/>
-      <c r="J588" s="2" t="inlineStr"/>
+      <c r="I588" s="4" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J588" s="4" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L588" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L588" s="2" t="inlineStr"/>
       <c r="M588" s="2" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>6.16</v>
+        <v>28.48</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>0.0016</v>
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>7690000</v>
-      </c>
-      <c r="E589" s="6" t="inlineStr"/>
+        <v>18800000</v>
+      </c>
+      <c r="E589" s="8" t="n">
+        <v>0.2667</v>
+      </c>
       <c r="F589" s="7" t="n">
-        <v>62.72</v>
+        <v>49.66</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
@@ -26041,92 +26017,106 @@
       <c r="J589" s="6" t="inlineStr"/>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L589" s="6" t="inlineStr"/>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
+      <c r="L589" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M589" s="6" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>13.98</v>
+        <v>7</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>0.0138</v>
+        <v>-0.0182</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>32400000</v>
-      </c>
-      <c r="E590" s="2" t="inlineStr"/>
+        <v>542950</v>
+      </c>
+      <c r="E590" s="4" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F590" s="3" t="n">
-        <v>54.25</v>
+        <v>37.31</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
-      <c r="I590" s="2" t="inlineStr"/>
-      <c r="J590" s="2" t="inlineStr"/>
+      <c r="I590" s="4" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J590" s="4" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
         </is>
       </c>
-      <c r="L590" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
-        </is>
-      </c>
+      <c r="L590" s="2" t="inlineStr"/>
       <c r="M590" s="2" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>80.53</v>
+        <v>2.94</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>0.0176</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>10440000</v>
+        <v>240000000</v>
       </c>
       <c r="E591" s="6" t="inlineStr"/>
       <c r="F591" s="7" t="n">
-        <v>43.51</v>
+        <v>55.79</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
       <c r="I591" s="6" t="inlineStr"/>
       <c r="J591" s="6" t="inlineStr"/>
-      <c r="K591" s="6" t="inlineStr"/>
-      <c r="L591" s="6" t="inlineStr"/>
+      <c r="K591" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L591" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+        </is>
+      </c>
       <c r="M591" s="6" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>17.01</v>
+        <v>21.46</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>-0.0053</v>
+        <v>0.0999</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>72710000</v>
+        <v>86600000</v>
       </c>
       <c r="E592" s="2" t="inlineStr"/>
       <c r="F592" s="3" t="n">
-        <v>52.78</v>
+        <v>68.67</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
@@ -26134,12 +26124,12 @@
       <c r="J592" s="2" t="inlineStr"/>
       <c r="K592" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L592" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M592" s="2" t="inlineStr"/>
@@ -26147,21 +26137,21 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>2.94</v>
+        <v>27.16</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>0.09699999999999999</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>240000000</v>
+        <v>17070000</v>
       </c>
       <c r="E593" s="6" t="inlineStr"/>
       <c r="F593" s="7" t="n">
-        <v>55.79</v>
+        <v>63.67</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
@@ -26169,12 +26159,12 @@
       <c r="J593" s="6" t="inlineStr"/>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M593" s="6" t="inlineStr"/>
@@ -26182,23 +26172,21 @@
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>242</v>
+        <v>40.58</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D594" s="5" t="n">
-        <v>7420</v>
-      </c>
-      <c r="E594" s="4" t="n">
-        <v>0.2578</v>
-      </c>
+        <v>-0.0117</v>
+      </c>
+      <c r="D594" s="3" t="n">
+        <v>8380000.000000001</v>
+      </c>
+      <c r="E594" s="2" t="inlineStr"/>
       <c r="F594" s="3" t="n">
-        <v>41.93</v>
+        <v>54.32</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
@@ -26206,49 +26194,55 @@
       <c r="J594" s="2" t="inlineStr"/>
       <c r="K594" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L594" s="2" t="inlineStr"/>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
+      <c r="L594" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+        </is>
+      </c>
       <c r="M594" s="2" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>GRNYO</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>17.94</v>
+        <v>17.05</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>0.0022</v>
+        <v>0.0137</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>1260000</v>
+        <v>11180000</v>
       </c>
       <c r="E595" s="8" t="n">
-        <v>0.9869</v>
+        <v>0.9246</v>
       </c>
       <c r="F595" s="7" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="G595" s="6" t="inlineStr"/>
+        <v>46.47</v>
+      </c>
+      <c r="G595" s="7" t="n">
+        <v>161.15</v>
+      </c>
       <c r="H595" s="6" t="inlineStr"/>
       <c r="I595" s="8" t="n">
-        <v>-0.2446</v>
+        <v>0.0028</v>
       </c>
       <c r="J595" s="8" t="n">
-        <v>0.3246</v>
+        <v>-10.3171</v>
       </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr">
         <is>
-          <t>BIST MENKUL KIYM YO</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
         </is>
       </c>
       <c r="M595" s="6" t="inlineStr"/>
@@ -26256,40 +26250,34 @@
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>7.62</v>
+        <v>162.5</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>0.09960000000000001</v>
+        <v>0.0037</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>122010000</v>
-      </c>
-      <c r="E596" s="4" t="n">
-        <v>0.1672</v>
-      </c>
+        <v>6940000</v>
+      </c>
+      <c r="E596" s="2" t="inlineStr"/>
       <c r="F596" s="3" t="n">
-        <v>70.51000000000001</v>
+        <v>55.44</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
-      <c r="I596" s="4" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J596" s="4" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I596" s="2" t="inlineStr"/>
+      <c r="J596" s="2" t="inlineStr"/>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L596" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M596" s="2" t="inlineStr"/>
@@ -26297,40 +26285,34 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>140.3</v>
+        <v>13.98</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>0.0316</v>
+        <v>0.0138</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>2340000</v>
-      </c>
-      <c r="E597" s="8" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>32400000</v>
+      </c>
+      <c r="E597" s="6" t="inlineStr"/>
       <c r="F597" s="7" t="n">
-        <v>46.39</v>
+        <v>54.25</v>
       </c>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
-      <c r="I597" s="8" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J597" s="8" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I597" s="6" t="inlineStr"/>
+      <c r="J597" s="6" t="inlineStr"/>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M597" s="6" t="inlineStr"/>
@@ -26338,21 +26320,21 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>189.5</v>
+        <v>38.72</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>0.0706</v>
+        <v>0.0031</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>18010000</v>
+        <v>10070000</v>
       </c>
       <c r="E598" s="2" t="inlineStr"/>
       <c r="F598" s="3" t="n">
-        <v>44.94</v>
+        <v>48.93</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
@@ -26360,12 +26342,12 @@
       <c r="J598" s="2" t="inlineStr"/>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L598" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M598" s="2" t="inlineStr"/>
@@ -26373,34 +26355,40 @@
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>GRNYO</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>38.72</v>
+        <v>17.94</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>0.0031</v>
+        <v>0.0022</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>10070000</v>
-      </c>
-      <c r="E599" s="6" t="inlineStr"/>
+        <v>1260000</v>
+      </c>
+      <c r="E599" s="8" t="n">
+        <v>0.9869</v>
+      </c>
       <c r="F599" s="7" t="n">
-        <v>48.93</v>
+        <v>58.1</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
-      <c r="I599" s="6" t="inlineStr"/>
-      <c r="J599" s="6" t="inlineStr"/>
+      <c r="I599" s="8" t="n">
+        <v>-0.2446</v>
+      </c>
+      <c r="J599" s="8" t="n">
+        <v>0.3246</v>
+      </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M599" s="6" t="inlineStr"/>
@@ -26408,21 +26396,21 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>19.01</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>0.0071</v>
+        <v>-0.0031</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>255560</v>
+        <v>62410000</v>
       </c>
       <c r="E600" s="2" t="inlineStr"/>
       <c r="F600" s="3" t="n">
-        <v>11.8</v>
+        <v>29.07</v>
       </c>
       <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
@@ -26433,42 +26421,50 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L600" s="2" t="inlineStr"/>
+      <c r="L600" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+        </is>
+      </c>
       <c r="M600" s="2" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>28.48</v>
+        <v>7.62</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>18800000</v>
+        <v>122010000</v>
       </c>
       <c r="E601" s="8" t="n">
-        <v>0.2667</v>
+        <v>0.1672</v>
       </c>
       <c r="F601" s="7" t="n">
-        <v>49.66</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
-      <c r="I601" s="6" t="inlineStr"/>
-      <c r="J601" s="6" t="inlineStr"/>
+      <c r="I601" s="8" t="n">
+        <v>-5.3262</v>
+      </c>
+      <c r="J601" s="8" t="n">
+        <v>-4.2562</v>
+      </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M601" s="6" t="inlineStr"/>
@@ -26476,34 +26472,40 @@
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>40.58</v>
+        <v>2.68</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>-0.0117</v>
-      </c>
-      <c r="D602" s="3" t="n">
-        <v>8380000.000000001</v>
-      </c>
-      <c r="E602" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D602" s="5" t="n">
+        <v>90400000</v>
+      </c>
+      <c r="E602" s="4" t="n">
+        <v>0.7119</v>
+      </c>
       <c r="F602" s="3" t="n">
-        <v>54.32</v>
+        <v>42.36</v>
       </c>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
-      <c r="I602" s="2" t="inlineStr"/>
-      <c r="J602" s="2" t="inlineStr"/>
+      <c r="I602" s="4" t="n">
+        <v>-191.6342</v>
+      </c>
+      <c r="J602" s="4" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L602" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M602" s="2" t="inlineStr"/>
@@ -26511,21 +26513,23 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>19.01</v>
+        <v>242</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>-0.0031</v>
+        <v>0</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>62410000</v>
-      </c>
-      <c r="E603" s="6" t="inlineStr"/>
+        <v>7420</v>
+      </c>
+      <c r="E603" s="8" t="n">
+        <v>0.2578</v>
+      </c>
       <c r="F603" s="7" t="n">
-        <v>29.07</v>
+        <v>41.93</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
@@ -26533,71 +26537,65 @@
       <c r="J603" s="6" t="inlineStr"/>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L603" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L603" s="6" t="inlineStr"/>
       <c r="M603" s="6" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>7</v>
+        <v>33.06</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>-0.0182</v>
+        <v>0.0024</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>542950</v>
-      </c>
-      <c r="E604" s="4" t="n">
-        <v>0.95</v>
-      </c>
+        <v>4310000</v>
+      </c>
+      <c r="E604" s="2" t="inlineStr"/>
       <c r="F604" s="3" t="n">
-        <v>37.31</v>
+        <v>48.1</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
-      <c r="I604" s="4" t="n">
-        <v>-23.6291</v>
-      </c>
-      <c r="J604" s="4" t="n">
-        <v>-0.4678</v>
-      </c>
+      <c r="I604" s="2" t="inlineStr"/>
+      <c r="J604" s="2" t="inlineStr"/>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L604" s="2" t="inlineStr"/>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
+      <c r="L604" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+        </is>
+      </c>
       <c r="M604" s="2" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>33.06</v>
+        <v>6.16</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>0.0024</v>
+        <v>0.0016</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>4310000</v>
+        <v>7690000</v>
       </c>
       <c r="E605" s="6" t="inlineStr"/>
       <c r="F605" s="7" t="n">
-        <v>48.1</v>
+        <v>62.72</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
@@ -26605,47 +26603,49 @@
       <c r="J605" s="6" t="inlineStr"/>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
-        </is>
-      </c>
-      <c r="L605" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L605" s="6" t="inlineStr"/>
       <c r="M605" s="6" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>27.16</v>
+        <v>140.3</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>0.09960000000000001</v>
+        <v>0.0316</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>17070000</v>
-      </c>
-      <c r="E606" s="2" t="inlineStr"/>
+        <v>2340000</v>
+      </c>
+      <c r="E606" s="4" t="n">
+        <v>0.1071</v>
+      </c>
       <c r="F606" s="3" t="n">
-        <v>63.67</v>
+        <v>46.39</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
-      <c r="I606" s="2" t="inlineStr"/>
-      <c r="J606" s="2" t="inlineStr"/>
+      <c r="I606" s="4" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="J606" s="4" t="n">
+        <v>-0.4897</v>
+      </c>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L606" s="2" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M606" s="2" t="inlineStr"/>
@@ -26653,21 +26653,21 @@
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>21.46</v>
+        <v>189.5</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>0.0999</v>
+        <v>0.0706</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>86600000</v>
+        <v>18010000</v>
       </c>
       <c r="E607" s="6" t="inlineStr"/>
       <c r="F607" s="7" t="n">
-        <v>68.67</v>
+        <v>44.94</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
@@ -26675,12 +26675,12 @@
       <c r="J607" s="6" t="inlineStr"/>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M607" s="6" t="inlineStr"/>
@@ -26707,7 +26707,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>01.05.2026 12:30</t>
+          <t>01.05.2026 13:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-05-01.xlsx
+++ b/data/bist_screener_2026-05-01.xlsx
@@ -25787,36 +25787,40 @@
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B583" s="7" t="n">
-        <v>5.68</v>
+        <v>140.3</v>
       </c>
       <c r="C583" s="8" t="n">
-        <v>-0.0018</v>
+        <v>0.0316</v>
       </c>
       <c r="D583" s="9" t="n">
-        <v>56180000</v>
+        <v>2340000</v>
       </c>
       <c r="E583" s="8" t="n">
-        <v>0.8667</v>
+        <v>0.1071</v>
       </c>
       <c r="F583" s="7" t="n">
-        <v>85.04000000000001</v>
+        <v>46.39</v>
       </c>
       <c r="G583" s="6" t="inlineStr"/>
       <c r="H583" s="6" t="inlineStr"/>
-      <c r="I583" s="6" t="inlineStr"/>
-      <c r="J583" s="6" t="inlineStr"/>
+      <c r="I583" s="8" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="J583" s="8" t="n">
+        <v>-0.4897</v>
+      </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M583" s="6" t="inlineStr"/>
@@ -25824,69 +25828,75 @@
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>7.62</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>0.0071</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D584" s="5" t="n">
-        <v>255560</v>
-      </c>
-      <c r="E584" s="2" t="inlineStr"/>
+        <v>122010000</v>
+      </c>
+      <c r="E584" s="4" t="n">
+        <v>0.1672</v>
+      </c>
       <c r="F584" s="3" t="n">
-        <v>11.8</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
-      <c r="I584" s="2" t="inlineStr"/>
-      <c r="J584" s="2" t="inlineStr"/>
+      <c r="I584" s="4" t="n">
+        <v>-5.3262</v>
+      </c>
+      <c r="J584" s="4" t="n">
+        <v>-4.2562</v>
+      </c>
       <c r="K584" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
         </is>
       </c>
-      <c r="L584" s="2" t="inlineStr"/>
+      <c r="L584" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+        </is>
+      </c>
       <c r="M584" s="2" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>65.34999999999999</v>
+        <v>27.16</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>-0.0106</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>665180</v>
-      </c>
-      <c r="E585" s="8" t="n">
-        <v>0.3695000000000001</v>
-      </c>
+        <v>17070000</v>
+      </c>
+      <c r="E585" s="6" t="inlineStr"/>
       <c r="F585" s="7" t="n">
-        <v>58.93</v>
+        <v>63.67</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
       <c r="I585" s="6" t="inlineStr"/>
-      <c r="J585" s="8" t="n">
-        <v>0.4139</v>
-      </c>
+      <c r="J585" s="6" t="inlineStr"/>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M585" s="6" t="inlineStr"/>
@@ -25921,21 +25931,21 @@
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>17.01</v>
+        <v>19.01</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>-0.0053</v>
+        <v>-0.0031</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>72710000</v>
+        <v>62410000</v>
       </c>
       <c r="E587" s="6" t="inlineStr"/>
       <c r="F587" s="7" t="n">
-        <v>52.78</v>
+        <v>29.07</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
@@ -25948,7 +25958,7 @@
       </c>
       <c r="L587" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M587" s="6" t="inlineStr"/>
@@ -25956,73 +25966,75 @@
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>78.5</v>
+        <v>17.01</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>0.07980000000000001</v>
+        <v>-0.0053</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>34400</v>
-      </c>
-      <c r="E588" s="4" t="n">
-        <v>0.58</v>
-      </c>
+        <v>72710000</v>
+      </c>
+      <c r="E588" s="2" t="inlineStr"/>
       <c r="F588" s="3" t="n">
-        <v>43.41</v>
+        <v>52.78</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
-      <c r="I588" s="4" t="n">
-        <v>-9.409700000000001</v>
-      </c>
-      <c r="J588" s="4" t="n">
-        <v>-4.155</v>
-      </c>
+      <c r="I588" s="2" t="inlineStr"/>
+      <c r="J588" s="2" t="inlineStr"/>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L588" s="2" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L588" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M588" s="2" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>GRNYO</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>28.48</v>
+        <v>17.94</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>0.0022</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>18800000</v>
+        <v>1260000</v>
       </c>
       <c r="E589" s="8" t="n">
-        <v>0.2667</v>
+        <v>0.9869</v>
       </c>
       <c r="F589" s="7" t="n">
-        <v>49.66</v>
+        <v>58.1</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
-      <c r="I589" s="6" t="inlineStr"/>
-      <c r="J589" s="6" t="inlineStr"/>
+      <c r="I589" s="8" t="n">
+        <v>-0.2446</v>
+      </c>
+      <c r="J589" s="8" t="n">
+        <v>0.3246</v>
+      </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M589" s="6" t="inlineStr"/>
@@ -26030,35 +26042,29 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>7</v>
+        <v>6.16</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>-0.0182</v>
+        <v>0.0016</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>542950</v>
-      </c>
-      <c r="E590" s="4" t="n">
-        <v>0.95</v>
-      </c>
+        <v>7690000</v>
+      </c>
+      <c r="E590" s="2" t="inlineStr"/>
       <c r="F590" s="3" t="n">
-        <v>37.31</v>
+        <v>62.72</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
-      <c r="I590" s="4" t="n">
-        <v>-23.6291</v>
-      </c>
-      <c r="J590" s="4" t="n">
-        <v>-0.4678</v>
-      </c>
+      <c r="I590" s="2" t="inlineStr"/>
+      <c r="J590" s="2" t="inlineStr"/>
       <c r="K590" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L590" s="2" t="inlineStr"/>
@@ -26067,36 +26073,38 @@
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>2.94</v>
+        <v>7</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>0.09699999999999999</v>
+        <v>-0.0182</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>240000000</v>
-      </c>
-      <c r="E591" s="6" t="inlineStr"/>
+        <v>542950</v>
+      </c>
+      <c r="E591" s="8" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F591" s="7" t="n">
-        <v>55.79</v>
+        <v>37.31</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="6" t="inlineStr"/>
-      <c r="J591" s="6" t="inlineStr"/>
+      <c r="I591" s="8" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J591" s="8" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L591" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L591" s="6" t="inlineStr"/>
       <c r="M591" s="6" t="inlineStr"/>
     </row>
     <row r="592">
@@ -26137,21 +26145,23 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>27.16</v>
+        <v>28.48</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>0.09960000000000001</v>
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>17070000</v>
-      </c>
-      <c r="E593" s="6" t="inlineStr"/>
+        <v>18800000</v>
+      </c>
+      <c r="E593" s="8" t="n">
+        <v>0.2667</v>
+      </c>
       <c r="F593" s="7" t="n">
-        <v>63.67</v>
+        <v>49.66</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
@@ -26159,12 +26169,12 @@
       <c r="J593" s="6" t="inlineStr"/>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M593" s="6" t="inlineStr"/>
@@ -26207,42 +26217,34 @@
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>17.05</v>
+        <v>162.5</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>0.0137</v>
+        <v>0.0037</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>11180000</v>
-      </c>
-      <c r="E595" s="8" t="n">
-        <v>0.9246</v>
-      </c>
+        <v>6940000</v>
+      </c>
+      <c r="E595" s="6" t="inlineStr"/>
       <c r="F595" s="7" t="n">
-        <v>46.47</v>
-      </c>
-      <c r="G595" s="7" t="n">
-        <v>161.15</v>
-      </c>
+        <v>55.44</v>
+      </c>
+      <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
-      <c r="I595" s="8" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J595" s="8" t="n">
-        <v>-10.3171</v>
-      </c>
+      <c r="I595" s="6" t="inlineStr"/>
+      <c r="J595" s="6" t="inlineStr"/>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M595" s="6" t="inlineStr"/>
@@ -26250,21 +26252,21 @@
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>162.5</v>
+        <v>13.98</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>0.0037</v>
+        <v>0.0138</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>6940000</v>
+        <v>32400000</v>
       </c>
       <c r="E596" s="2" t="inlineStr"/>
       <c r="F596" s="3" t="n">
-        <v>55.44</v>
+        <v>54.25</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
@@ -26272,12 +26274,12 @@
       <c r="J596" s="2" t="inlineStr"/>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L596" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M596" s="2" t="inlineStr"/>
@@ -26285,21 +26287,23 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>13.98</v>
+        <v>5.68</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>0.0138</v>
+        <v>-0.0018</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>32400000</v>
-      </c>
-      <c r="E597" s="6" t="inlineStr"/>
+        <v>56180000</v>
+      </c>
+      <c r="E597" s="8" t="n">
+        <v>0.8667</v>
+      </c>
       <c r="F597" s="7" t="n">
-        <v>54.25</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
@@ -26307,12 +26311,12 @@
       <c r="J597" s="6" t="inlineStr"/>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M597" s="6" t="inlineStr"/>
@@ -26355,40 +26359,34 @@
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>GRNYO</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>17.94</v>
+        <v>33.06</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>0.0022</v>
+        <v>0.0024</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>1260000</v>
-      </c>
-      <c r="E599" s="8" t="n">
-        <v>0.9869</v>
-      </c>
+        <v>4310000</v>
+      </c>
+      <c r="E599" s="6" t="inlineStr"/>
       <c r="F599" s="7" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
-      <c r="I599" s="8" t="n">
-        <v>-0.2446</v>
-      </c>
-      <c r="J599" s="8" t="n">
-        <v>0.3246</v>
-      </c>
+      <c r="I599" s="6" t="inlineStr"/>
+      <c r="J599" s="6" t="inlineStr"/>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr">
         <is>
-          <t>BIST MENKUL KIYM YO</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M599" s="6" t="inlineStr"/>
@@ -26396,21 +26394,21 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>19.01</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>-0.0031</v>
+        <v>0.0071</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>62410000</v>
+        <v>255560</v>
       </c>
       <c r="E600" s="2" t="inlineStr"/>
       <c r="F600" s="3" t="n">
-        <v>29.07</v>
+        <v>11.8</v>
       </c>
       <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
@@ -26421,52 +26419,40 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L600" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
-        </is>
-      </c>
+      <c r="L600" s="2" t="inlineStr"/>
       <c r="M600" s="2" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>7.62</v>
+        <v>242</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>0.09960000000000001</v>
+        <v>0</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>122010000</v>
+        <v>7420</v>
       </c>
       <c r="E601" s="8" t="n">
-        <v>0.1672</v>
+        <v>0.2578</v>
       </c>
       <c r="F601" s="7" t="n">
-        <v>70.51000000000001</v>
+        <v>41.93</v>
       </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
-      <c r="I601" s="8" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J601" s="8" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I601" s="6" t="inlineStr"/>
+      <c r="J601" s="6" t="inlineStr"/>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L601" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L601" s="6" t="inlineStr"/>
       <c r="M601" s="6" t="inlineStr"/>
     </row>
     <row r="602">
@@ -26513,54 +26499,64 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>242</v>
+        <v>17.05</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>0</v>
+        <v>0.0137</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>7420</v>
+        <v>11180000</v>
       </c>
       <c r="E603" s="8" t="n">
-        <v>0.2578</v>
+        <v>0.9246</v>
       </c>
       <c r="F603" s="7" t="n">
-        <v>41.93</v>
-      </c>
-      <c r="G603" s="6" t="inlineStr"/>
+        <v>46.47</v>
+      </c>
+      <c r="G603" s="7" t="n">
+        <v>161.15</v>
+      </c>
       <c r="H603" s="6" t="inlineStr"/>
-      <c r="I603" s="6" t="inlineStr"/>
-      <c r="J603" s="6" t="inlineStr"/>
+      <c r="I603" s="8" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="J603" s="8" t="n">
+        <v>-10.3171</v>
+      </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L603" s="6" t="inlineStr"/>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
+      <c r="L603" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+        </is>
+      </c>
       <c r="M603" s="6" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>33.06</v>
+        <v>189.5</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.0706</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>4310000</v>
+        <v>18010000</v>
       </c>
       <c r="E604" s="2" t="inlineStr"/>
       <c r="F604" s="3" t="n">
-        <v>48.1</v>
+        <v>44.94</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
@@ -26568,12 +26564,12 @@
       <c r="J604" s="2" t="inlineStr"/>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L604" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M604" s="2" t="inlineStr"/>
@@ -26581,93 +26577,97 @@
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>6.16</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>0.0016</v>
+        <v>-0.0106</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>7690000</v>
-      </c>
-      <c r="E605" s="6" t="inlineStr"/>
+        <v>665180</v>
+      </c>
+      <c r="E605" s="8" t="n">
+        <v>0.3695000000000001</v>
+      </c>
       <c r="F605" s="7" t="n">
-        <v>62.72</v>
+        <v>58.93</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
       <c r="I605" s="6" t="inlineStr"/>
-      <c r="J605" s="6" t="inlineStr"/>
+      <c r="J605" s="8" t="n">
+        <v>0.4139</v>
+      </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L605" s="6" t="inlineStr"/>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
+      <c r="L605" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+        </is>
+      </c>
       <c r="M605" s="6" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>140.3</v>
+        <v>78.5</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>0.0316</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>2340000</v>
+        <v>34400</v>
       </c>
       <c r="E606" s="4" t="n">
-        <v>0.1071</v>
+        <v>0.58</v>
       </c>
       <c r="F606" s="3" t="n">
-        <v>46.39</v>
+        <v>43.41</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
       <c r="I606" s="4" t="n">
-        <v>-3.6635</v>
+        <v>-9.409700000000001</v>
       </c>
       <c r="J606" s="4" t="n">
-        <v>-0.4897</v>
+        <v>-4.155</v>
       </c>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
-        </is>
-      </c>
-      <c r="L606" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L606" s="2" t="inlineStr"/>
       <c r="M606" s="2" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>189.5</v>
+        <v>2.94</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>0.0706</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>18010000</v>
+        <v>240000000</v>
       </c>
       <c r="E607" s="6" t="inlineStr"/>
       <c r="F607" s="7" t="n">
-        <v>44.94</v>
+        <v>55.79</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
@@ -26675,12 +26675,12 @@
       <c r="J607" s="6" t="inlineStr"/>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M607" s="6" t="inlineStr"/>
@@ -26707,7 +26707,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>01.05.2026 13:30</t>
+          <t>01.05.2026 14:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-05-01.xlsx
+++ b/data/bist_screener_2026-05-01.xlsx
@@ -25787,81 +25787,67 @@
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B583" s="7" t="n">
-        <v>140.3</v>
+        <v>242</v>
       </c>
       <c r="C583" s="8" t="n">
-        <v>0.0316</v>
+        <v>0</v>
       </c>
       <c r="D583" s="9" t="n">
-        <v>2340000</v>
+        <v>7420</v>
       </c>
       <c r="E583" s="8" t="n">
-        <v>0.1071</v>
+        <v>0.2578</v>
       </c>
       <c r="F583" s="7" t="n">
-        <v>46.39</v>
+        <v>41.93</v>
       </c>
       <c r="G583" s="6" t="inlineStr"/>
       <c r="H583" s="6" t="inlineStr"/>
-      <c r="I583" s="8" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J583" s="8" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I583" s="6" t="inlineStr"/>
+      <c r="J583" s="6" t="inlineStr"/>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
-        </is>
-      </c>
-      <c r="L583" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L583" s="6" t="inlineStr"/>
       <c r="M583" s="6" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>7.62</v>
+        <v>40.58</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>0.09960000000000001</v>
-      </c>
-      <c r="D584" s="5" t="n">
-        <v>122010000</v>
-      </c>
-      <c r="E584" s="4" t="n">
-        <v>0.1672</v>
-      </c>
+        <v>-0.0117</v>
+      </c>
+      <c r="D584" s="3" t="n">
+        <v>8380000.000000001</v>
+      </c>
+      <c r="E584" s="2" t="inlineStr"/>
       <c r="F584" s="3" t="n">
-        <v>70.51000000000001</v>
+        <v>54.32</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
-      <c r="I584" s="4" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J584" s="4" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I584" s="2" t="inlineStr"/>
+      <c r="J584" s="2" t="inlineStr"/>
       <c r="K584" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L584" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M584" s="2" t="inlineStr"/>
@@ -25869,21 +25855,21 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>27.16</v>
+        <v>6.16</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>0.09960000000000001</v>
+        <v>0.0016</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>17070000</v>
+        <v>7690000</v>
       </c>
       <c r="E585" s="6" t="inlineStr"/>
       <c r="F585" s="7" t="n">
-        <v>63.67</v>
+        <v>62.72</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
@@ -25891,61 +25877,65 @@
       <c r="J585" s="6" t="inlineStr"/>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
-        </is>
-      </c>
-      <c r="L585" s="6" t="inlineStr">
-        <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L585" s="6" t="inlineStr"/>
       <c r="M585" s="6" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>80.53</v>
+        <v>27.16</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>0.0176</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>10440000</v>
+        <v>17070000</v>
       </c>
       <c r="E586" s="2" t="inlineStr"/>
       <c r="F586" s="3" t="n">
-        <v>43.51</v>
+        <v>63.67</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
       <c r="I586" s="2" t="inlineStr"/>
       <c r="J586" s="2" t="inlineStr"/>
-      <c r="K586" s="2" t="inlineStr"/>
-      <c r="L586" s="2" t="inlineStr"/>
+      <c r="K586" s="2" t="inlineStr">
+        <is>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
+        </is>
+      </c>
+      <c r="L586" s="2" t="inlineStr">
+        <is>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+        </is>
+      </c>
       <c r="M586" s="2" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>19.01</v>
+        <v>17.01</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>-0.0031</v>
+        <v>-0.0053</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>62410000</v>
+        <v>72710000</v>
       </c>
       <c r="E587" s="6" t="inlineStr"/>
       <c r="F587" s="7" t="n">
-        <v>29.07</v>
+        <v>52.78</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
@@ -25958,7 +25948,7 @@
       </c>
       <c r="L587" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M587" s="6" t="inlineStr"/>
@@ -25966,21 +25956,21 @@
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>17.01</v>
+        <v>21.46</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>-0.0053</v>
+        <v>0.0999</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>72710000</v>
+        <v>86600000</v>
       </c>
       <c r="E588" s="2" t="inlineStr"/>
       <c r="F588" s="3" t="n">
-        <v>52.78</v>
+        <v>68.67</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
@@ -25988,12 +25978,12 @@
       <c r="J588" s="2" t="inlineStr"/>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L588" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M588" s="2" t="inlineStr"/>
@@ -26001,31 +25991,31 @@
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>GRNYO</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>17.94</v>
+        <v>7.62</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>0.0022</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>1260000</v>
+        <v>122010000</v>
       </c>
       <c r="E589" s="8" t="n">
-        <v>0.9869</v>
+        <v>0.1672</v>
       </c>
       <c r="F589" s="7" t="n">
-        <v>58.1</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
       <c r="I589" s="8" t="n">
-        <v>-0.2446</v>
+        <v>-5.3262</v>
       </c>
       <c r="J589" s="8" t="n">
-        <v>0.3246</v>
+        <v>-4.2562</v>
       </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
@@ -26034,7 +26024,7 @@
       </c>
       <c r="L589" s="6" t="inlineStr">
         <is>
-          <t>BIST MENKUL KIYM YO</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M589" s="6" t="inlineStr"/>
@@ -26042,21 +26032,21 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>6.16</v>
+        <v>19.01</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>0.0016</v>
+        <v>-0.0031</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>7690000</v>
+        <v>62410000</v>
       </c>
       <c r="E590" s="2" t="inlineStr"/>
       <c r="F590" s="3" t="n">
-        <v>62.72</v>
+        <v>29.07</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
@@ -26067,101 +26057,103 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L590" s="2" t="inlineStr"/>
+      <c r="L590" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+        </is>
+      </c>
       <c r="M590" s="2" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>7</v>
+        <v>162.5</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>-0.0182</v>
+        <v>0.0037</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>542950</v>
-      </c>
-      <c r="E591" s="8" t="n">
-        <v>0.95</v>
-      </c>
+        <v>6940000</v>
+      </c>
+      <c r="E591" s="6" t="inlineStr"/>
       <c r="F591" s="7" t="n">
-        <v>37.31</v>
+        <v>55.44</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="8" t="n">
-        <v>-23.6291</v>
-      </c>
-      <c r="J591" s="8" t="n">
-        <v>-0.4678</v>
-      </c>
+      <c r="I591" s="6" t="inlineStr"/>
+      <c r="J591" s="6" t="inlineStr"/>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L591" s="6" t="inlineStr"/>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L591" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+        </is>
+      </c>
       <c r="M591" s="6" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>21.46</v>
+        <v>7</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>0.0999</v>
+        <v>-0.0182</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>86600000</v>
-      </c>
-      <c r="E592" s="2" t="inlineStr"/>
+        <v>542950</v>
+      </c>
+      <c r="E592" s="4" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F592" s="3" t="n">
-        <v>68.67</v>
+        <v>37.31</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
-      <c r="I592" s="2" t="inlineStr"/>
-      <c r="J592" s="2" t="inlineStr"/>
+      <c r="I592" s="4" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J592" s="4" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K592" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
-        </is>
-      </c>
-      <c r="L592" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L592" s="2" t="inlineStr"/>
       <c r="M592" s="2" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>28.48</v>
+        <v>38.72</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>0.0031</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>18800000</v>
-      </c>
-      <c r="E593" s="8" t="n">
-        <v>0.2667</v>
-      </c>
+        <v>10070000</v>
+      </c>
+      <c r="E593" s="6" t="inlineStr"/>
       <c r="F593" s="7" t="n">
-        <v>49.66</v>
+        <v>48.93</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
@@ -26169,12 +26161,12 @@
       <c r="J593" s="6" t="inlineStr"/>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M593" s="6" t="inlineStr"/>
@@ -26182,21 +26174,23 @@
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>40.58</v>
+        <v>5.68</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>-0.0117</v>
-      </c>
-      <c r="D594" s="3" t="n">
-        <v>8380000.000000001</v>
-      </c>
-      <c r="E594" s="2" t="inlineStr"/>
+        <v>-0.0018</v>
+      </c>
+      <c r="D594" s="5" t="n">
+        <v>56180000</v>
+      </c>
+      <c r="E594" s="4" t="n">
+        <v>0.8667</v>
+      </c>
       <c r="F594" s="3" t="n">
-        <v>54.32</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
@@ -26204,12 +26198,12 @@
       <c r="J594" s="2" t="inlineStr"/>
       <c r="K594" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L594" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M594" s="2" t="inlineStr"/>
@@ -26217,21 +26211,23 @@
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>162.5</v>
+        <v>28.48</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>0.0037</v>
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>6940000</v>
-      </c>
-      <c r="E595" s="6" t="inlineStr"/>
+        <v>18800000</v>
+      </c>
+      <c r="E595" s="8" t="n">
+        <v>0.2667</v>
+      </c>
       <c r="F595" s="7" t="n">
-        <v>55.44</v>
+        <v>49.66</v>
       </c>
       <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
@@ -26239,12 +26235,12 @@
       <c r="J595" s="6" t="inlineStr"/>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M595" s="6" t="inlineStr"/>
@@ -26287,23 +26283,21 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>5.68</v>
+        <v>33.06</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>-0.0018</v>
+        <v>0.0024</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>56180000</v>
-      </c>
-      <c r="E597" s="8" t="n">
-        <v>0.8667</v>
-      </c>
+        <v>4310000</v>
+      </c>
+      <c r="E597" s="6" t="inlineStr"/>
       <c r="F597" s="7" t="n">
-        <v>85.04000000000001</v>
+        <v>48.1</v>
       </c>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
@@ -26311,12 +26305,12 @@
       <c r="J597" s="6" t="inlineStr"/>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M597" s="6" t="inlineStr"/>
@@ -26324,34 +26318,40 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>38.72</v>
+        <v>140.3</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>0.0031</v>
+        <v>0.0316</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>10070000</v>
-      </c>
-      <c r="E598" s="2" t="inlineStr"/>
+        <v>2340000</v>
+      </c>
+      <c r="E598" s="4" t="n">
+        <v>0.1071</v>
+      </c>
       <c r="F598" s="3" t="n">
-        <v>48.93</v>
+        <v>46.39</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
-      <c r="I598" s="2" t="inlineStr"/>
-      <c r="J598" s="2" t="inlineStr"/>
+      <c r="I598" s="4" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="J598" s="4" t="n">
+        <v>-0.4897</v>
+      </c>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L598" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M598" s="2" t="inlineStr"/>
@@ -26359,34 +26359,40 @@
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>33.06</v>
+        <v>2.68</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>0.0024</v>
+        <v>0</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>4310000</v>
-      </c>
-      <c r="E599" s="6" t="inlineStr"/>
+        <v>90400000</v>
+      </c>
+      <c r="E599" s="8" t="n">
+        <v>0.7119</v>
+      </c>
       <c r="F599" s="7" t="n">
-        <v>48.1</v>
+        <v>42.36</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
-      <c r="I599" s="6" t="inlineStr"/>
-      <c r="J599" s="6" t="inlineStr"/>
+      <c r="I599" s="8" t="n">
+        <v>-191.6342</v>
+      </c>
+      <c r="J599" s="8" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M599" s="6" t="inlineStr"/>
@@ -26394,21 +26400,21 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>2.94</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>0.0071</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>255560</v>
+        <v>240000000</v>
       </c>
       <c r="E600" s="2" t="inlineStr"/>
       <c r="F600" s="3" t="n">
-        <v>11.8</v>
+        <v>55.79</v>
       </c>
       <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
@@ -26419,29 +26425,31 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L600" s="2" t="inlineStr"/>
+      <c r="L600" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+        </is>
+      </c>
       <c r="M600" s="2" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>242</v>
+        <v>189.5</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>0</v>
+        <v>0.0706</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>7420</v>
-      </c>
-      <c r="E601" s="8" t="n">
-        <v>0.2578</v>
-      </c>
+        <v>18010000</v>
+      </c>
+      <c r="E601" s="6" t="inlineStr"/>
       <c r="F601" s="7" t="n">
-        <v>41.93</v>
+        <v>44.94</v>
       </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
@@ -26449,49 +26457,55 @@
       <c r="J601" s="6" t="inlineStr"/>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L601" s="6" t="inlineStr"/>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
+      <c r="L601" s="6" t="inlineStr">
+        <is>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+        </is>
+      </c>
       <c r="M601" s="6" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>2.68</v>
+        <v>17.05</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>0</v>
+        <v>0.0137</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>90400000</v>
+        <v>11180000</v>
       </c>
       <c r="E602" s="4" t="n">
-        <v>0.7119</v>
+        <v>0.9246</v>
       </c>
       <c r="F602" s="3" t="n">
-        <v>42.36</v>
-      </c>
-      <c r="G602" s="2" t="inlineStr"/>
+        <v>46.47</v>
+      </c>
+      <c r="G602" s="3" t="n">
+        <v>161.15</v>
+      </c>
       <c r="H602" s="2" t="inlineStr"/>
       <c r="I602" s="4" t="n">
-        <v>-191.6342</v>
+        <v>0.0028</v>
       </c>
       <c r="J602" s="4" t="n">
-        <v>-0.8093</v>
+        <v>-10.3171</v>
       </c>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L602" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
         </is>
       </c>
       <c r="M602" s="2" t="inlineStr"/>
@@ -26499,64 +26513,48 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>17.05</v>
+        <v>80.53</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>0.0137</v>
+        <v>0.0176</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>11180000</v>
-      </c>
-      <c r="E603" s="8" t="n">
-        <v>0.9246</v>
-      </c>
+        <v>10440000</v>
+      </c>
+      <c r="E603" s="6" t="inlineStr"/>
       <c r="F603" s="7" t="n">
-        <v>46.47</v>
-      </c>
-      <c r="G603" s="7" t="n">
-        <v>161.15</v>
-      </c>
+        <v>43.51</v>
+      </c>
+      <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
-      <c r="I603" s="8" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J603" s="8" t="n">
-        <v>-10.3171</v>
-      </c>
-      <c r="K603" s="6" t="inlineStr">
-        <is>
-          <t>Üretici imalatı</t>
-        </is>
-      </c>
-      <c r="L603" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
-        </is>
-      </c>
+      <c r="I603" s="6" t="inlineStr"/>
+      <c r="J603" s="6" t="inlineStr"/>
+      <c r="K603" s="6" t="inlineStr"/>
+      <c r="L603" s="6" t="inlineStr"/>
       <c r="M603" s="6" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>189.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>0.0706</v>
+        <v>0.0071</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>18010000</v>
+        <v>255560</v>
       </c>
       <c r="E604" s="2" t="inlineStr"/>
       <c r="F604" s="3" t="n">
-        <v>44.94</v>
+        <v>11.8</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
@@ -26564,51 +26562,49 @@
       <c r="J604" s="2" t="inlineStr"/>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
-        </is>
-      </c>
-      <c r="L604" s="2" t="inlineStr">
-        <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L604" s="2" t="inlineStr"/>
       <c r="M604" s="2" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>GRNYO</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>65.34999999999999</v>
+        <v>17.94</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>-0.0106</v>
+        <v>0.0022</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>665180</v>
+        <v>1260000</v>
       </c>
       <c r="E605" s="8" t="n">
-        <v>0.3695000000000001</v>
+        <v>0.9869</v>
       </c>
       <c r="F605" s="7" t="n">
-        <v>58.93</v>
+        <v>58.1</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
-      <c r="I605" s="6" t="inlineStr"/>
+      <c r="I605" s="8" t="n">
+        <v>-0.2446</v>
+      </c>
       <c r="J605" s="8" t="n">
-        <v>0.4139</v>
+        <v>0.3246</v>
       </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M605" s="6" t="inlineStr"/>
@@ -26616,73 +26612,77 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>78.5</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>0.07980000000000001</v>
+        <v>-0.0106</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>34400</v>
+        <v>665180</v>
       </c>
       <c r="E606" s="4" t="n">
-        <v>0.58</v>
+        <v>0.3695000000000001</v>
       </c>
       <c r="F606" s="3" t="n">
-        <v>43.41</v>
+        <v>58.93</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
-      <c r="I606" s="4" t="n">
-        <v>-9.409700000000001</v>
-      </c>
+      <c r="I606" s="2" t="inlineStr"/>
       <c r="J606" s="4" t="n">
-        <v>-4.155</v>
+        <v>0.4139</v>
       </c>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L606" s="2" t="inlineStr"/>
+          <t>Teknoloji hizmetleri</t>
+        </is>
+      </c>
+      <c r="L606" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+        </is>
+      </c>
       <c r="M606" s="2" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>2.94</v>
+        <v>78.5</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>0.09699999999999999</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>240000000</v>
-      </c>
-      <c r="E607" s="6" t="inlineStr"/>
+        <v>34400</v>
+      </c>
+      <c r="E607" s="8" t="n">
+        <v>0.58</v>
+      </c>
       <c r="F607" s="7" t="n">
-        <v>55.79</v>
+        <v>43.41</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
-      <c r="I607" s="6" t="inlineStr"/>
-      <c r="J607" s="6" t="inlineStr"/>
+      <c r="I607" s="8" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J607" s="8" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L607" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L607" s="6" t="inlineStr"/>
       <c r="M607" s="6" t="inlineStr"/>
     </row>
   </sheetData>
@@ -26707,7 +26707,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>01.05.2026 14:30</t>
+          <t>01.05.2026 15:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-05-01.xlsx
+++ b/data/bist_screener_2026-05-01.xlsx
@@ -25787,23 +25787,21 @@
     <row r="583">
       <c r="A583" s="6" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B583" s="7" t="n">
-        <v>242</v>
+        <v>40.58</v>
       </c>
       <c r="C583" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D583" s="9" t="n">
-        <v>7420</v>
-      </c>
-      <c r="E583" s="8" t="n">
-        <v>0.2578</v>
-      </c>
+        <v>-0.0117</v>
+      </c>
+      <c r="D583" s="7" t="n">
+        <v>8380000.000000001</v>
+      </c>
+      <c r="E583" s="6" t="inlineStr"/>
       <c r="F583" s="7" t="n">
-        <v>41.93</v>
+        <v>54.32</v>
       </c>
       <c r="G583" s="6" t="inlineStr"/>
       <c r="H583" s="6" t="inlineStr"/>
@@ -25811,30 +25809,34 @@
       <c r="J583" s="6" t="inlineStr"/>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L583" s="6" t="inlineStr"/>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
+      <c r="L583" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+        </is>
+      </c>
       <c r="M583" s="6" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B584" s="3" t="n">
-        <v>40.58</v>
+        <v>38.72</v>
       </c>
       <c r="C584" s="4" t="n">
-        <v>-0.0117</v>
-      </c>
-      <c r="D584" s="3" t="n">
-        <v>8380000.000000001</v>
+        <v>0.0031</v>
+      </c>
+      <c r="D584" s="5" t="n">
+        <v>10070000</v>
       </c>
       <c r="E584" s="2" t="inlineStr"/>
       <c r="F584" s="3" t="n">
-        <v>54.32</v>
+        <v>48.93</v>
       </c>
       <c r="G584" s="2" t="inlineStr"/>
       <c r="H584" s="2" t="inlineStr"/>
@@ -25842,12 +25844,12 @@
       <c r="J584" s="2" t="inlineStr"/>
       <c r="K584" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L584" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M584" s="2" t="inlineStr"/>
@@ -25855,21 +25857,21 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>6.16</v>
+        <v>189.5</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>0.0016</v>
+        <v>0.0706</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>7690000</v>
+        <v>18010000</v>
       </c>
       <c r="E585" s="6" t="inlineStr"/>
       <c r="F585" s="7" t="n">
-        <v>62.72</v>
+        <v>44.94</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
@@ -25877,30 +25879,34 @@
       <c r="J585" s="6" t="inlineStr"/>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L585" s="6" t="inlineStr"/>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
+      <c r="L585" s="6" t="inlineStr">
+        <is>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+        </is>
+      </c>
       <c r="M585" s="6" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>27.16</v>
+        <v>19.01</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>0.09960000000000001</v>
+        <v>-0.0031</v>
       </c>
       <c r="D586" s="5" t="n">
-        <v>17070000</v>
+        <v>62410000</v>
       </c>
       <c r="E586" s="2" t="inlineStr"/>
       <c r="F586" s="3" t="n">
-        <v>63.67</v>
+        <v>29.07</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
@@ -25908,12 +25914,12 @@
       <c r="J586" s="2" t="inlineStr"/>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L586" s="2" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M586" s="2" t="inlineStr"/>
@@ -26032,21 +26038,21 @@
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>19.01</v>
+        <v>6.16</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>-0.0031</v>
+        <v>0.0016</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>62410000</v>
+        <v>7690000</v>
       </c>
       <c r="E590" s="2" t="inlineStr"/>
       <c r="F590" s="3" t="n">
-        <v>29.07</v>
+        <v>62.72</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
@@ -26057,44 +26063,46 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L590" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
-        </is>
-      </c>
+      <c r="L590" s="2" t="inlineStr"/>
       <c r="M590" s="2" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>162.5</v>
+        <v>140.3</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>0.0037</v>
+        <v>0.0316</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>6940000</v>
-      </c>
-      <c r="E591" s="6" t="inlineStr"/>
+        <v>2340000</v>
+      </c>
+      <c r="E591" s="8" t="n">
+        <v>0.1071</v>
+      </c>
       <c r="F591" s="7" t="n">
-        <v>55.44</v>
+        <v>46.39</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="6" t="inlineStr"/>
-      <c r="J591" s="6" t="inlineStr"/>
+      <c r="I591" s="8" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="J591" s="8" t="n">
+        <v>-0.4897</v>
+      </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M591" s="6" t="inlineStr"/>
@@ -26102,32 +26110,28 @@
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>7</v>
+        <v>242</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>-0.0182</v>
+        <v>0</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>542950</v>
+        <v>7420</v>
       </c>
       <c r="E592" s="4" t="n">
-        <v>0.95</v>
+        <v>0.2578</v>
       </c>
       <c r="F592" s="3" t="n">
-        <v>37.31</v>
+        <v>41.93</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
-      <c r="I592" s="4" t="n">
-        <v>-23.6291</v>
-      </c>
-      <c r="J592" s="4" t="n">
-        <v>-0.4678</v>
-      </c>
+      <c r="I592" s="2" t="inlineStr"/>
+      <c r="J592" s="2" t="inlineStr"/>
       <c r="K592" s="2" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
@@ -26139,21 +26143,21 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>38.72</v>
+        <v>162.5</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>0.0031</v>
+        <v>0.0037</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>10070000</v>
+        <v>6940000</v>
       </c>
       <c r="E593" s="6" t="inlineStr"/>
       <c r="F593" s="7" t="n">
-        <v>48.93</v>
+        <v>55.44</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
@@ -26161,7 +26165,7 @@
       <c r="J593" s="6" t="inlineStr"/>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr">
@@ -26174,60 +26178,58 @@
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>5.68</v>
+        <v>7</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>-0.0018</v>
+        <v>-0.0182</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>56180000</v>
+        <v>542950</v>
       </c>
       <c r="E594" s="4" t="n">
-        <v>0.8667</v>
+        <v>0.95</v>
       </c>
       <c r="F594" s="3" t="n">
-        <v>85.04000000000001</v>
+        <v>37.31</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
-      <c r="I594" s="2" t="inlineStr"/>
-      <c r="J594" s="2" t="inlineStr"/>
+      <c r="I594" s="4" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J594" s="4" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K594" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L594" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L594" s="2" t="inlineStr"/>
       <c r="M594" s="2" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>28.48</v>
+        <v>13.98</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>0.0138</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>18800000</v>
-      </c>
-      <c r="E595" s="8" t="n">
-        <v>0.2667</v>
-      </c>
+        <v>32400000</v>
+      </c>
+      <c r="E595" s="6" t="inlineStr"/>
       <c r="F595" s="7" t="n">
-        <v>49.66</v>
+        <v>54.25</v>
       </c>
       <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
@@ -26235,12 +26237,12 @@
       <c r="J595" s="6" t="inlineStr"/>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M595" s="6" t="inlineStr"/>
@@ -26248,34 +26250,40 @@
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>13.98</v>
+        <v>2.68</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>0.0138</v>
+        <v>0</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>32400000</v>
-      </c>
-      <c r="E596" s="2" t="inlineStr"/>
+        <v>90400000</v>
+      </c>
+      <c r="E596" s="4" t="n">
+        <v>0.7119</v>
+      </c>
       <c r="F596" s="3" t="n">
-        <v>54.25</v>
+        <v>42.36</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
-      <c r="I596" s="2" t="inlineStr"/>
-      <c r="J596" s="2" t="inlineStr"/>
+      <c r="I596" s="4" t="n">
+        <v>-191.6342</v>
+      </c>
+      <c r="J596" s="4" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L596" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M596" s="2" t="inlineStr"/>
@@ -26283,34 +26291,40 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>GRNYO</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>33.06</v>
+        <v>17.94</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>0.0024</v>
+        <v>0.0022</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>4310000</v>
-      </c>
-      <c r="E597" s="6" t="inlineStr"/>
+        <v>1260000</v>
+      </c>
+      <c r="E597" s="8" t="n">
+        <v>0.9869</v>
+      </c>
       <c r="F597" s="7" t="n">
-        <v>48.1</v>
+        <v>58.1</v>
       </c>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
-      <c r="I597" s="6" t="inlineStr"/>
-      <c r="J597" s="6" t="inlineStr"/>
+      <c r="I597" s="8" t="n">
+        <v>-0.2446</v>
+      </c>
+      <c r="J597" s="8" t="n">
+        <v>0.3246</v>
+      </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M597" s="6" t="inlineStr"/>
@@ -26318,40 +26332,34 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>140.3</v>
+        <v>2.94</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>0.0316</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>2340000</v>
-      </c>
-      <c r="E598" s="4" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>240000000</v>
+      </c>
+      <c r="E598" s="2" t="inlineStr"/>
       <c r="F598" s="3" t="n">
-        <v>46.39</v>
+        <v>55.79</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
-      <c r="I598" s="4" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J598" s="4" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I598" s="2" t="inlineStr"/>
+      <c r="J598" s="2" t="inlineStr"/>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L598" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M598" s="2" t="inlineStr"/>
@@ -26359,40 +26367,38 @@
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>2.68</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>0</v>
+        <v>-0.0106</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>90400000</v>
+        <v>665180</v>
       </c>
       <c r="E599" s="8" t="n">
-        <v>0.7119</v>
+        <v>0.3695000000000001</v>
       </c>
       <c r="F599" s="7" t="n">
-        <v>42.36</v>
+        <v>58.93</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
-      <c r="I599" s="8" t="n">
-        <v>-191.6342</v>
-      </c>
+      <c r="I599" s="6" t="inlineStr"/>
       <c r="J599" s="8" t="n">
-        <v>-0.8093</v>
+        <v>0.4139</v>
       </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M599" s="6" t="inlineStr"/>
@@ -26400,56 +26406,48 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>2.94</v>
+        <v>80.53</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>0.09699999999999999</v>
+        <v>0.0176</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>240000000</v>
+        <v>10440000</v>
       </c>
       <c r="E600" s="2" t="inlineStr"/>
       <c r="F600" s="3" t="n">
-        <v>55.79</v>
+        <v>43.51</v>
       </c>
       <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
       <c r="I600" s="2" t="inlineStr"/>
       <c r="J600" s="2" t="inlineStr"/>
-      <c r="K600" s="2" t="inlineStr">
-        <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L600" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
-        </is>
-      </c>
+      <c r="K600" s="2" t="inlineStr"/>
+      <c r="L600" s="2" t="inlineStr"/>
       <c r="M600" s="2" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>189.5</v>
+        <v>27.16</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>0.0706</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>18010000</v>
+        <v>17070000</v>
       </c>
       <c r="E601" s="6" t="inlineStr"/>
       <c r="F601" s="7" t="n">
-        <v>44.94</v>
+        <v>63.67</v>
       </c>
       <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
@@ -26457,12 +26455,12 @@
       <c r="J601" s="6" t="inlineStr"/>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M601" s="6" t="inlineStr"/>
@@ -26470,34 +26468,26 @@
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>17.05</v>
+        <v>33.06</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>0.0137</v>
+        <v>0.0024</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>11180000</v>
-      </c>
-      <c r="E602" s="4" t="n">
-        <v>0.9246</v>
-      </c>
+        <v>4310000</v>
+      </c>
+      <c r="E602" s="2" t="inlineStr"/>
       <c r="F602" s="3" t="n">
-        <v>46.47</v>
-      </c>
-      <c r="G602" s="3" t="n">
-        <v>161.15</v>
-      </c>
+        <v>48.1</v>
+      </c>
+      <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
-      <c r="I602" s="4" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J602" s="4" t="n">
-        <v>-10.3171</v>
-      </c>
+      <c r="I602" s="2" t="inlineStr"/>
+      <c r="J602" s="2" t="inlineStr"/>
       <c r="K602" s="2" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -26505,7 +26495,7 @@
       </c>
       <c r="L602" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M602" s="2" t="inlineStr"/>
@@ -26513,98 +26503,116 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>80.53</v>
+        <v>78.5</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>0.0176</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>10440000</v>
-      </c>
-      <c r="E603" s="6" t="inlineStr"/>
+        <v>34400</v>
+      </c>
+      <c r="E603" s="8" t="n">
+        <v>0.58</v>
+      </c>
       <c r="F603" s="7" t="n">
-        <v>43.51</v>
+        <v>43.41</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
-      <c r="I603" s="6" t="inlineStr"/>
-      <c r="J603" s="6" t="inlineStr"/>
-      <c r="K603" s="6" t="inlineStr"/>
+      <c r="I603" s="8" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J603" s="8" t="n">
+        <v>-4.155</v>
+      </c>
+      <c r="K603" s="6" t="inlineStr">
+        <is>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
       <c r="L603" s="6" t="inlineStr"/>
       <c r="M603" s="6" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>17.05</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>0.0071</v>
+        <v>0.0137</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>255560</v>
-      </c>
-      <c r="E604" s="2" t="inlineStr"/>
+        <v>11180000</v>
+      </c>
+      <c r="E604" s="4" t="n">
+        <v>0.9246</v>
+      </c>
       <c r="F604" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="G604" s="2" t="inlineStr"/>
+        <v>46.47</v>
+      </c>
+      <c r="G604" s="3" t="n">
+        <v>161.15</v>
+      </c>
       <c r="H604" s="2" t="inlineStr"/>
-      <c r="I604" s="2" t="inlineStr"/>
-      <c r="J604" s="2" t="inlineStr"/>
+      <c r="I604" s="4" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="J604" s="4" t="n">
+        <v>-10.3171</v>
+      </c>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L604" s="2" t="inlineStr"/>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
+      <c r="L604" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+        </is>
+      </c>
       <c r="M604" s="2" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>GRNYO</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>17.94</v>
+        <v>28.48</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>0.0022</v>
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>1260000</v>
+        <v>18800000</v>
       </c>
       <c r="E605" s="8" t="n">
-        <v>0.9869</v>
+        <v>0.2667</v>
       </c>
       <c r="F605" s="7" t="n">
-        <v>58.1</v>
+        <v>49.66</v>
       </c>
       <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
-      <c r="I605" s="8" t="n">
-        <v>-0.2446</v>
-      </c>
-      <c r="J605" s="8" t="n">
-        <v>0.3246</v>
-      </c>
+      <c r="I605" s="6" t="inlineStr"/>
+      <c r="J605" s="6" t="inlineStr"/>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr">
         <is>
-          <t>BIST MENKUL KIYM YO</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M605" s="6" t="inlineStr"/>
@@ -26612,77 +26620,69 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>65.34999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>-0.0106</v>
+        <v>0.0071</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>665180</v>
-      </c>
-      <c r="E606" s="4" t="n">
-        <v>0.3695000000000001</v>
-      </c>
+        <v>255560</v>
+      </c>
+      <c r="E606" s="2" t="inlineStr"/>
       <c r="F606" s="3" t="n">
-        <v>58.93</v>
+        <v>11.8</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
       <c r="I606" s="2" t="inlineStr"/>
-      <c r="J606" s="4" t="n">
-        <v>0.4139</v>
-      </c>
+      <c r="J606" s="2" t="inlineStr"/>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
-        </is>
-      </c>
-      <c r="L606" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L606" s="2" t="inlineStr"/>
       <c r="M606" s="2" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>78.5</v>
+        <v>5.68</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>0.07980000000000001</v>
+        <v>-0.0018</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>34400</v>
+        <v>56180000</v>
       </c>
       <c r="E607" s="8" t="n">
-        <v>0.58</v>
+        <v>0.8667</v>
       </c>
       <c r="F607" s="7" t="n">
-        <v>43.41</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
-      <c r="I607" s="8" t="n">
-        <v>-9.409700000000001</v>
-      </c>
-      <c r="J607" s="8" t="n">
-        <v>-4.155</v>
-      </c>
+      <c r="I607" s="6" t="inlineStr"/>
+      <c r="J607" s="6" t="inlineStr"/>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L607" s="6" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L607" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+        </is>
+      </c>
       <c r="M607" s="6" t="inlineStr"/>
     </row>
   </sheetData>
@@ -26707,7 +26707,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>01.05.2026 15:30</t>
+          <t>01.05.2026 16:30</t>
         </is>
       </c>
     </row>
